--- a/Autotransformer_UnUn_AirCore_Calculator.xlsx
+++ b/Autotransformer_UnUn_AirCore_Calculator.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="137">
   <si>
     <t xml:space="preserve">✦  AIR-CORE AUTOTRANSFORMER UnUn CALCULATOR  ✦</t>
   </si>
@@ -357,6 +357,101 @@
   </si>
   <si>
     <t xml:space="preserve">Compare L vs L_min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✦  COMPENSATION NETWORK CALCULATOR  ✦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series &amp; Shunt L/C to cancel residual reactance at each tap — referenced to 50Ω system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOW TO READ THIS TABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series L/C: place component in series with the feed line at the tap — cancels reflected reactance seen at that tap port.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shunt L/C:  place component to ground at the tap — cancels the susceptance seen at that tap port.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive X (inductive load): series C or shunt C cancels.  Negative X (capacitive load): series L or shunt L cancels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Values are computed for the tap frequency shown. Component Q and self-resonance should be verified for your operating frequency.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap 1 (X = 0): no compensation needed — values show "—" automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freq
+(MHz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R_tap
+(Ω)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X_tap
+(Ω)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase
+(°)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series L
+(µH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series C
+(pF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shunt L
+(µH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shunt C
+(pF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPONENT SELECTION GUIDE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Series topology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component placed in series with the line at the tap port. Best when source impedance is known and fixed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shunt topology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component placed from tap port to ground. Best when line Z is nearly correct but susceptance must be tuned out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X = 0 (— shown)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load is purely resistive — autotransformer alone provides a perfect match. No compensation required.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolerance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use ±5% or better components. At HF, stray lead inductance (~5–20 nH) may need to be subtracted from L values.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitor type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use NP0/C0G ceramic or silver-mica capacitors for HF stability. Avoid X7R at RF frequencies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inductor type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use air-core solenoid or toroid (T-material) for series inductors. Ensure SRF &gt;&gt; operating frequency.</t>
   </si>
 </sst>
 </file>
@@ -375,7 +470,7 @@
     <numFmt numFmtId="172" formatCode="0.00"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -452,8 +547,61 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFFFD700"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF8EA9C1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -463,19 +611,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1A2D40"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F5C8B"/>
-        <bgColor rgb="FF008080"/>
+        <bgColor rgb="FF2E4A6B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF0F8FF"/>
+        <bgColor rgb="FFEAF0FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -499,13 +647,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD6E8F5"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFEAF0FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8A020"/>
-        <bgColor rgb="FFFFCC00"/>
+        <bgColor rgb="FFFF8080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1A2D40"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4A6B"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF0FB"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -558,7 +724,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -643,55 +809,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -711,14 +845,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -733,6 +859,54 @@
     </xf>
     <xf numFmtId="171" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -762,7 +936,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF8EA9C1"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF9E6"/>
       <rgbColor rgb="FFD6E8F5"/>
@@ -779,9 +953,9 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFEAF0FB"/>
+      <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FFF0F8FF"/>
-      <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -789,19 +963,19 @@
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFFD700"/>
       <rgbColor rgb="FFE8A020"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF555555"/>
       <rgbColor rgb="FFAAAAAA"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF1A2D40"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1A2D40"/>
+      <rgbColor rgb="FF2E4A6B"/>
+      <rgbColor rgb="FF404040"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1503,98 +1677,98 @@
       <c r="D30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C31" s="21" t="n">
         <f aca="false">C7</f>
         <v>50</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C32" s="21" t="n">
         <f aca="false">IFERROR(aggregate(15,6,C15:C25*(1/(H15:H25="YES")),1),MIN(C15:C25))</f>
         <v>7.2</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="21" t="n">
         <f aca="false">C8</f>
         <v>0.45</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="21" t="n">
         <f aca="false">C11</f>
         <v>20</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C35" s="21" t="n">
         <f aca="false">C10</f>
         <v>4</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="23" t="n">
+      <c r="C36" s="22" t="n">
         <f aca="false">I71</f>
         <v>4134.33593212417</v>
       </c>
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="24" t="n">
+      <c r="C37" s="23" t="n">
         <f aca="false">IFERROR(C115,"—")</f>
         <v>35.9977335339286</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C38" s="21" t="str">
         <f aca="false">IFERROR(C118,"—")</f>
         <v>✔ YES</v>
       </c>
-      <c r="D38" s="22"/>
+      <c r="D38" s="8"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
@@ -1639,408 +1813,408 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="25" t="n">
+      <c r="B42" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="26" t="n">
+      <c r="C42" s="18" t="n">
         <f aca="false">C15</f>
         <v>7.2</v>
       </c>
-      <c r="D42" s="27" t="n">
+      <c r="D42" s="16" t="n">
         <f aca="false">F15</f>
         <v>200</v>
       </c>
-      <c r="E42" s="28" t="n">
+      <c r="E42" s="17" t="n">
         <f aca="false">G15</f>
         <v>0</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="19" t="n">
         <f aca="false">D59</f>
         <v>2</v>
       </c>
-      <c r="G42" s="30" t="n">
+      <c r="G42" s="11" t="n">
         <f aca="false">E59</f>
         <v>40</v>
       </c>
-      <c r="H42" s="31" t="n">
+      <c r="H42" s="24" t="n">
         <f aca="false">F78</f>
         <v>1</v>
       </c>
-      <c r="I42" s="32" t="n">
+      <c r="I42" s="25" t="n">
         <f aca="false">G78</f>
         <v>180</v>
       </c>
-      <c r="J42" s="31" t="n">
+      <c r="J42" s="24" t="n">
         <f aca="false">I78</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="33" t="n">
+      <c r="B43" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="26" t="n">
+      <c r="C43" s="18" t="n">
         <f aca="false">C16</f>
         <v>10</v>
       </c>
-      <c r="D43" s="27" t="n">
+      <c r="D43" s="16" t="n">
         <f aca="false">F16</f>
         <v>316.227766016838</v>
       </c>
-      <c r="E43" s="28" t="n">
+      <c r="E43" s="17" t="n">
         <f aca="false">G16</f>
         <v>18.434948822922</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="19" t="n">
         <f aca="false">D60</f>
         <v>2.51486685936587</v>
       </c>
-      <c r="G43" s="30" t="n">
+      <c r="G43" s="11" t="n">
         <f aca="false">E60</f>
         <v>50</v>
       </c>
-      <c r="H43" s="31" t="n">
+      <c r="H43" s="24" t="n">
         <f aca="false">F79</f>
         <v>1.38742588672279</v>
       </c>
-      <c r="I43" s="32" t="n">
+      <c r="I43" s="25" t="n">
         <f aca="false">G79</f>
         <v>15.7948252576199</v>
       </c>
-      <c r="J43" s="31" t="n">
+      <c r="J43" s="24" t="n">
         <f aca="false">I79</f>
         <v>2.6334038989724</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="25" t="n">
+      <c r="B44" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="C44" s="26" t="n">
+      <c r="C44" s="18" t="n">
         <f aca="false">C17</f>
         <v>18</v>
       </c>
-      <c r="D44" s="27" t="n">
+      <c r="D44" s="16" t="n">
         <f aca="false">F17</f>
         <v>457.055795281058</v>
       </c>
-      <c r="E44" s="28" t="n">
+      <c r="E44" s="17" t="n">
         <f aca="false">G17</f>
         <v>-10.0805979875423</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="19" t="n">
         <f aca="false">D61</f>
         <v>3.02342784031985</v>
       </c>
-      <c r="G44" s="30" t="n">
+      <c r="G44" s="11" t="n">
         <f aca="false">E61</f>
         <v>60</v>
       </c>
-      <c r="H44" s="31" t="n">
+      <c r="H44" s="24" t="n">
         <f aca="false">F80</f>
         <v>1.19345732284679</v>
       </c>
-      <c r="I44" s="32" t="n">
+      <c r="I44" s="25" t="n">
         <f aca="false">G80</f>
         <v>21.0908803086925</v>
       </c>
-      <c r="J44" s="31" t="n">
+      <c r="J44" s="24" t="n">
         <f aca="false">I80</f>
         <v>0.777878860128034</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="33" t="n">
+      <c r="B45" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="C45" s="26" t="n">
+      <c r="C45" s="18" t="n">
         <f aca="false">C18</f>
         <v>28</v>
       </c>
-      <c r="D45" s="27" t="n">
+      <c r="D45" s="16" t="n">
         <f aca="false">F18</f>
         <v>800</v>
       </c>
-      <c r="E45" s="28" t="n">
+      <c r="E45" s="17" t="n">
         <f aca="false">G18</f>
         <v>0</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="19" t="n">
         <f aca="false">D62</f>
         <v>4</v>
       </c>
-      <c r="G45" s="30" t="n">
+      <c r="G45" s="11" t="n">
         <f aca="false">E62</f>
         <v>80</v>
       </c>
-      <c r="H45" s="31" t="n">
+      <c r="H45" s="24" t="n">
         <f aca="false">F81</f>
         <v>1</v>
       </c>
-      <c r="I45" s="32" t="n">
+      <c r="I45" s="25" t="n">
         <f aca="false">G81</f>
         <v>180</v>
       </c>
-      <c r="J45" s="31" t="n">
+      <c r="J45" s="24" t="n">
         <f aca="false">I81</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="25" t="n">
+      <c r="B46" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="C46" s="26" t="n">
+      <c r="C46" s="18" t="n">
         <f aca="false">C19</f>
         <v>0</v>
       </c>
-      <c r="D46" s="26" t="str">
+      <c r="D46" s="18" t="str">
         <f aca="false">F19</f>
         <v/>
       </c>
-      <c r="E46" s="26" t="str">
+      <c r="E46" s="18" t="str">
         <f aca="false">G19</f>
         <v/>
       </c>
-      <c r="F46" s="26" t="str">
+      <c r="F46" s="18" t="str">
         <f aca="false">D63</f>
         <v/>
       </c>
-      <c r="G46" s="26" t="str">
+      <c r="G46" s="18" t="str">
         <f aca="false">E63</f>
         <v/>
       </c>
-      <c r="H46" s="26" t="str">
+      <c r="H46" s="18" t="str">
         <f aca="false">F82</f>
         <v/>
       </c>
-      <c r="I46" s="26" t="str">
+      <c r="I46" s="18" t="str">
         <f aca="false">G82</f>
         <v/>
       </c>
-      <c r="J46" s="26" t="str">
+      <c r="J46" s="18" t="str">
         <f aca="false">I82</f>
         <v/>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="33" t="n">
+      <c r="B47" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="C47" s="26" t="n">
+      <c r="C47" s="18" t="n">
         <f aca="false">C20</f>
         <v>0</v>
       </c>
-      <c r="D47" s="26" t="str">
+      <c r="D47" s="18" t="str">
         <f aca="false">F20</f>
         <v/>
       </c>
-      <c r="E47" s="26" t="str">
+      <c r="E47" s="18" t="str">
         <f aca="false">G20</f>
         <v/>
       </c>
-      <c r="F47" s="26" t="str">
+      <c r="F47" s="18" t="str">
         <f aca="false">D64</f>
         <v/>
       </c>
-      <c r="G47" s="26" t="str">
+      <c r="G47" s="18" t="str">
         <f aca="false">E64</f>
         <v/>
       </c>
-      <c r="H47" s="26" t="str">
+      <c r="H47" s="18" t="str">
         <f aca="false">F83</f>
         <v/>
       </c>
-      <c r="I47" s="26" t="str">
+      <c r="I47" s="18" t="str">
         <f aca="false">G83</f>
         <v/>
       </c>
-      <c r="J47" s="26" t="str">
+      <c r="J47" s="18" t="str">
         <f aca="false">I83</f>
         <v/>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="25" t="n">
+      <c r="B48" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C48" s="26" t="n">
+      <c r="C48" s="18" t="n">
         <f aca="false">C21</f>
         <v>0</v>
       </c>
-      <c r="D48" s="26" t="str">
+      <c r="D48" s="18" t="str">
         <f aca="false">F21</f>
         <v/>
       </c>
-      <c r="E48" s="26" t="str">
+      <c r="E48" s="18" t="str">
         <f aca="false">G21</f>
         <v/>
       </c>
-      <c r="F48" s="26" t="str">
+      <c r="F48" s="18" t="str">
         <f aca="false">D65</f>
         <v/>
       </c>
-      <c r="G48" s="26" t="str">
+      <c r="G48" s="18" t="str">
         <f aca="false">E65</f>
         <v/>
       </c>
-      <c r="H48" s="26" t="str">
+      <c r="H48" s="18" t="str">
         <f aca="false">F84</f>
         <v/>
       </c>
-      <c r="I48" s="26" t="str">
+      <c r="I48" s="18" t="str">
         <f aca="false">G84</f>
         <v/>
       </c>
-      <c r="J48" s="26" t="str">
+      <c r="J48" s="18" t="str">
         <f aca="false">I84</f>
         <v/>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="33" t="n">
+      <c r="B49" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="C49" s="26" t="n">
+      <c r="C49" s="18" t="n">
         <f aca="false">C22</f>
         <v>0</v>
       </c>
-      <c r="D49" s="26" t="str">
+      <c r="D49" s="18" t="str">
         <f aca="false">F22</f>
         <v/>
       </c>
-      <c r="E49" s="26" t="str">
+      <c r="E49" s="18" t="str">
         <f aca="false">G22</f>
         <v/>
       </c>
-      <c r="F49" s="26" t="str">
+      <c r="F49" s="18" t="str">
         <f aca="false">D66</f>
         <v/>
       </c>
-      <c r="G49" s="26" t="str">
+      <c r="G49" s="18" t="str">
         <f aca="false">E66</f>
         <v/>
       </c>
-      <c r="H49" s="26" t="str">
+      <c r="H49" s="18" t="str">
         <f aca="false">F85</f>
         <v/>
       </c>
-      <c r="I49" s="26" t="str">
+      <c r="I49" s="18" t="str">
         <f aca="false">G85</f>
         <v/>
       </c>
-      <c r="J49" s="26" t="str">
+      <c r="J49" s="18" t="str">
         <f aca="false">I85</f>
         <v/>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="25" t="n">
+      <c r="B50" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C50" s="26" t="n">
+      <c r="C50" s="18" t="n">
         <f aca="false">C23</f>
         <v>0</v>
       </c>
-      <c r="D50" s="26" t="str">
+      <c r="D50" s="18" t="str">
         <f aca="false">F23</f>
         <v/>
       </c>
-      <c r="E50" s="26" t="str">
+      <c r="E50" s="18" t="str">
         <f aca="false">G23</f>
         <v/>
       </c>
-      <c r="F50" s="26" t="str">
+      <c r="F50" s="18" t="str">
         <f aca="false">D67</f>
         <v/>
       </c>
-      <c r="G50" s="26" t="str">
+      <c r="G50" s="18" t="str">
         <f aca="false">E67</f>
         <v/>
       </c>
-      <c r="H50" s="26" t="str">
+      <c r="H50" s="18" t="str">
         <f aca="false">F86</f>
         <v/>
       </c>
-      <c r="I50" s="26" t="str">
+      <c r="I50" s="18" t="str">
         <f aca="false">G86</f>
         <v/>
       </c>
-      <c r="J50" s="26" t="str">
+      <c r="J50" s="18" t="str">
         <f aca="false">I86</f>
         <v/>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="33" t="n">
+      <c r="B51" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="C51" s="26" t="n">
+      <c r="C51" s="18" t="n">
         <f aca="false">C24</f>
         <v>0</v>
       </c>
-      <c r="D51" s="26" t="str">
+      <c r="D51" s="18" t="str">
         <f aca="false">F24</f>
         <v/>
       </c>
-      <c r="E51" s="26" t="str">
+      <c r="E51" s="18" t="str">
         <f aca="false">G24</f>
         <v/>
       </c>
-      <c r="F51" s="26" t="str">
+      <c r="F51" s="18" t="str">
         <f aca="false">D68</f>
         <v/>
       </c>
-      <c r="G51" s="26" t="str">
+      <c r="G51" s="18" t="str">
         <f aca="false">E68</f>
         <v/>
       </c>
-      <c r="H51" s="26" t="str">
+      <c r="H51" s="18" t="str">
         <f aca="false">F87</f>
         <v/>
       </c>
-      <c r="I51" s="26" t="str">
+      <c r="I51" s="18" t="str">
         <f aca="false">G87</f>
         <v/>
       </c>
-      <c r="J51" s="26" t="str">
+      <c r="J51" s="18" t="str">
         <f aca="false">I87</f>
         <v/>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="25" t="n">
+      <c r="B52" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C52" s="26" t="n">
+      <c r="C52" s="18" t="n">
         <f aca="false">C25</f>
         <v>0</v>
       </c>
-      <c r="D52" s="26" t="str">
+      <c r="D52" s="18" t="str">
         <f aca="false">F25</f>
         <v/>
       </c>
-      <c r="E52" s="26" t="str">
+      <c r="E52" s="18" t="str">
         <f aca="false">G25</f>
         <v/>
       </c>
-      <c r="F52" s="26" t="str">
+      <c r="F52" s="18" t="str">
         <f aca="false">D69</f>
         <v/>
       </c>
-      <c r="G52" s="26" t="str">
+      <c r="G52" s="18" t="str">
         <f aca="false">E69</f>
         <v/>
       </c>
-      <c r="H52" s="26" t="str">
+      <c r="H52" s="18" t="str">
         <f aca="false">F88</f>
         <v/>
       </c>
-      <c r="I52" s="26" t="str">
+      <c r="I52" s="18" t="str">
         <f aca="false">G88</f>
         <v/>
       </c>
-      <c r="J52" s="26" t="str">
+      <c r="J52" s="18" t="str">
         <f aca="false">I88</f>
         <v/>
       </c>
@@ -2133,7 +2307,7 @@
         <f aca="false">IF(E59&lt;&gt;"",E59,"")</f>
         <v>40</v>
       </c>
-      <c r="G59" s="34" t="n">
+      <c r="G59" s="26" t="n">
         <f aca="false">IF(F59&lt;&gt;"",F59*PI()*($C$9+$C$8),"")</f>
         <v>2067.16796606208</v>
       </c>
@@ -2141,7 +2315,7 @@
         <f aca="false">IF(G59&lt;&gt;"",G59*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>224.077432098765</v>
       </c>
-      <c r="I59" s="34" t="n">
+      <c r="I59" s="26" t="n">
         <f aca="false">IF(G59&lt;&gt;"",G59,"")</f>
         <v>2067.16796606208</v>
       </c>
@@ -2170,7 +2344,7 @@
         <f aca="false">IF(AND(E60&lt;&gt;"",E59&lt;&gt;""),E60-E59,IF(E60&lt;&gt;"",E60,""))</f>
         <v>10</v>
       </c>
-      <c r="G60" s="34" t="n">
+      <c r="G60" s="26" t="n">
         <f aca="false">IF(F60&lt;&gt;"",F60*PI()*($C$9+$C$8),"")</f>
         <v>516.791991515521</v>
       </c>
@@ -2178,7 +2352,7 @@
         <f aca="false">IF(G60&lt;&gt;"",G60*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>56.0193580246914</v>
       </c>
-      <c r="I60" s="34" t="n">
+      <c r="I60" s="26" t="n">
         <f aca="false">IF(G60&lt;&gt;"",SUM(G59:G60),"")</f>
         <v>2583.9599575776</v>
       </c>
@@ -2207,7 +2381,7 @@
         <f aca="false">IF(AND(E61&lt;&gt;"",E60&lt;&gt;""),E61-E60,IF(E61&lt;&gt;"",E61,""))</f>
         <v>10</v>
       </c>
-      <c r="G61" s="34" t="n">
+      <c r="G61" s="26" t="n">
         <f aca="false">IF(F61&lt;&gt;"",F61*PI()*($C$9+$C$8),"")</f>
         <v>516.791991515521</v>
       </c>
@@ -2215,7 +2389,7 @@
         <f aca="false">IF(G61&lt;&gt;"",G61*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>56.0193580246914</v>
       </c>
-      <c r="I61" s="34" t="n">
+      <c r="I61" s="26" t="n">
         <f aca="false">IF(G61&lt;&gt;"",SUM(G59:G61),"")</f>
         <v>3100.75194909313</v>
       </c>
@@ -2244,7 +2418,7 @@
         <f aca="false">IF(AND(E62&lt;&gt;"",E61&lt;&gt;""),E62-E61,IF(E62&lt;&gt;"",E62,""))</f>
         <v>20</v>
       </c>
-      <c r="G62" s="34" t="n">
+      <c r="G62" s="26" t="n">
         <f aca="false">IF(F62&lt;&gt;"",F62*PI()*($C$9+$C$8),"")</f>
         <v>1033.58398303104</v>
       </c>
@@ -2252,7 +2426,7 @@
         <f aca="false">IF(G62&lt;&gt;"",G62*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>112.038716049383</v>
       </c>
-      <c r="I62" s="34" t="n">
+      <c r="I62" s="26" t="n">
         <f aca="false">IF(G62&lt;&gt;"",SUM(G59:G62),"")</f>
         <v>4134.33593212417</v>
       </c>
@@ -2281,7 +2455,7 @@
         <f aca="false">IF(AND(E63&lt;&gt;"",E62&lt;&gt;""),E63-E62,IF(E63&lt;&gt;"",E63,""))</f>
         <v/>
       </c>
-      <c r="G63" s="34" t="str">
+      <c r="G63" s="26" t="str">
         <f aca="false">IF(F63&lt;&gt;"",F63*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
@@ -2289,7 +2463,7 @@
         <f aca="false">IF(G63&lt;&gt;"",G63*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I63" s="34" t="str">
+      <c r="I63" s="26" t="str">
         <f aca="false">IF(G63&lt;&gt;"",SUM(G59:G63),"")</f>
         <v/>
       </c>
@@ -2318,7 +2492,7 @@
         <f aca="false">IF(AND(E64&lt;&gt;"",E63&lt;&gt;""),E64-E63,IF(E64&lt;&gt;"",E64,""))</f>
         <v/>
       </c>
-      <c r="G64" s="34" t="str">
+      <c r="G64" s="26" t="str">
         <f aca="false">IF(F64&lt;&gt;"",F64*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
@@ -2326,7 +2500,7 @@
         <f aca="false">IF(G64&lt;&gt;"",G64*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I64" s="34" t="str">
+      <c r="I64" s="26" t="str">
         <f aca="false">IF(G64&lt;&gt;"",SUM(G59:G64),"")</f>
         <v/>
       </c>
@@ -2355,7 +2529,7 @@
         <f aca="false">IF(AND(E65&lt;&gt;"",E64&lt;&gt;""),E65-E64,IF(E65&lt;&gt;"",E65,""))</f>
         <v/>
       </c>
-      <c r="G65" s="34" t="str">
+      <c r="G65" s="26" t="str">
         <f aca="false">IF(F65&lt;&gt;"",F65*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
@@ -2363,7 +2537,7 @@
         <f aca="false">IF(G65&lt;&gt;"",G65*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I65" s="34" t="str">
+      <c r="I65" s="26" t="str">
         <f aca="false">IF(G65&lt;&gt;"",SUM(G59:G65),"")</f>
         <v/>
       </c>
@@ -2392,7 +2566,7 @@
         <f aca="false">IF(AND(E66&lt;&gt;"",E65&lt;&gt;""),E66-E65,IF(E66&lt;&gt;"",E66,""))</f>
         <v/>
       </c>
-      <c r="G66" s="34" t="str">
+      <c r="G66" s="26" t="str">
         <f aca="false">IF(F66&lt;&gt;"",F66*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
@@ -2400,7 +2574,7 @@
         <f aca="false">IF(G66&lt;&gt;"",G66*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I66" s="34" t="str">
+      <c r="I66" s="26" t="str">
         <f aca="false">IF(G66&lt;&gt;"",SUM(G59:G66),"")</f>
         <v/>
       </c>
@@ -2429,7 +2603,7 @@
         <f aca="false">IF(AND(E67&lt;&gt;"",E66&lt;&gt;""),E67-E66,IF(E67&lt;&gt;"",E67,""))</f>
         <v/>
       </c>
-      <c r="G67" s="34" t="str">
+      <c r="G67" s="26" t="str">
         <f aca="false">IF(F67&lt;&gt;"",F67*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
@@ -2437,7 +2611,7 @@
         <f aca="false">IF(G67&lt;&gt;"",G67*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I67" s="34" t="str">
+      <c r="I67" s="26" t="str">
         <f aca="false">IF(G67&lt;&gt;"",SUM(G59:G67),"")</f>
         <v/>
       </c>
@@ -2466,7 +2640,7 @@
         <f aca="false">IF(AND(E68&lt;&gt;"",E67&lt;&gt;""),E68-E67,IF(E68&lt;&gt;"",E68,""))</f>
         <v/>
       </c>
-      <c r="G68" s="34" t="str">
+      <c r="G68" s="26" t="str">
         <f aca="false">IF(F68&lt;&gt;"",F68*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
@@ -2474,7 +2648,7 @@
         <f aca="false">IF(G68&lt;&gt;"",G68*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I68" s="34" t="str">
+      <c r="I68" s="26" t="str">
         <f aca="false">IF(G68&lt;&gt;"",SUM(G59:G68),"")</f>
         <v/>
       </c>
@@ -2503,7 +2677,7 @@
         <f aca="false">IF(AND(E69&lt;&gt;"",E68&lt;&gt;""),E69-E68,IF(E69&lt;&gt;"",E69,""))</f>
         <v/>
       </c>
-      <c r="G69" s="34" t="str">
+      <c r="G69" s="26" t="str">
         <f aca="false">IF(F69&lt;&gt;"",F69*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
@@ -2511,7 +2685,7 @@
         <f aca="false">IF(G69&lt;&gt;"",G69*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I69" s="34" t="str">
+      <c r="I69" s="26" t="str">
         <f aca="false">IF(G69&lt;&gt;"",SUM(G59:G69),"")</f>
         <v/>
       </c>
@@ -2521,20 +2695,20 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B71" s="35" t="s">
+      <c r="B71" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C71" s="35"/>
-      <c r="D71" s="35"/>
+      <c r="C71" s="27"/>
+      <c r="D71" s="27"/>
       <c r="E71" s="11" t="n">
         <f aca="false">IFERROR(MAX(E59:E69),"")</f>
         <v>80</v>
       </c>
-      <c r="H71" s="36" t="n">
+      <c r="H71" s="28" t="n">
         <f aca="false">IFERROR(SUM(H59:H69),"")</f>
         <v>448.154864197531</v>
       </c>
-      <c r="I71" s="37" t="n">
+      <c r="I71" s="29" t="n">
         <f aca="false">IFERROR(MAX(I59:I69),"")</f>
         <v>4134.33593212417</v>
       </c>
@@ -2613,23 +2787,23 @@
         <f aca="false">F15</f>
         <v>200</v>
       </c>
-      <c r="E78" s="38" t="n">
+      <c r="E78" s="25" t="n">
         <f aca="false">G15</f>
         <v>0</v>
       </c>
-      <c r="F78" s="39" t="n">
+      <c r="F78" s="24" t="n">
         <f aca="false">IF(F15&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2))),999),"")</f>
         <v>1</v>
       </c>
-      <c r="G78" s="38" t="n">
+      <c r="G78" s="25" t="n">
         <f aca="false">IF(F15&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>180</v>
       </c>
-      <c r="H78" s="39" t="n">
+      <c r="H78" s="24" t="n">
         <f aca="false">IF(F15&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2))),0),"")</f>
         <v>-0</v>
       </c>
-      <c r="I78" s="39" t="n">
+      <c r="I78" s="24" t="n">
         <f aca="false">IF(F15&lt;&gt;"",IFERROR(((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)*100,0),"")</f>
         <v>0</v>
       </c>
@@ -2646,23 +2820,23 @@
         <f aca="false">F16</f>
         <v>316.227766016838</v>
       </c>
-      <c r="E79" s="38" t="n">
+      <c r="E79" s="25" t="n">
         <f aca="false">G16</f>
         <v>18.434948822922</v>
       </c>
-      <c r="F79" s="39" t="n">
+      <c r="F79" s="24" t="n">
         <f aca="false">IF(F16&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2))),999),"")</f>
         <v>1.38742588672279</v>
       </c>
-      <c r="G79" s="38" t="n">
+      <c r="G79" s="25" t="n">
         <f aca="false">IF(F16&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>15.7948252576199</v>
       </c>
-      <c r="H79" s="39" t="n">
+      <c r="H79" s="24" t="n">
         <f aca="false">IF(F16&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2))),0),"")</f>
         <v>0.115900124973496</v>
       </c>
-      <c r="I79" s="39" t="n">
+      <c r="I79" s="24" t="n">
         <f aca="false">IF(F16&lt;&gt;"",IFERROR(((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)*100,0),"")</f>
         <v>2.6334038989724</v>
       </c>
@@ -2679,23 +2853,23 @@
         <f aca="false">F17</f>
         <v>457.055795281058</v>
       </c>
-      <c r="E80" s="38" t="n">
+      <c r="E80" s="25" t="n">
         <f aca="false">G17</f>
         <v>-10.0805979875423</v>
       </c>
-      <c r="F80" s="39" t="n">
+      <c r="F80" s="24" t="n">
         <f aca="false">IF(F17&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2))),999),"")</f>
         <v>1.19345732284679</v>
       </c>
-      <c r="G80" s="38" t="n">
+      <c r="G80" s="25" t="n">
         <f aca="false">IF(F17&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>21.0908803086925</v>
       </c>
-      <c r="H80" s="39" t="n">
+      <c r="H80" s="24" t="n">
         <f aca="false">IF(F17&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2))),0),"")</f>
         <v>0.0339149298724391</v>
       </c>
-      <c r="I80" s="39" t="n">
+      <c r="I80" s="24" t="n">
         <f aca="false">IF(F17&lt;&gt;"",IFERROR(((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)*100,0),"")</f>
         <v>0.777878860128034</v>
       </c>
@@ -2712,23 +2886,23 @@
         <f aca="false">F18</f>
         <v>800</v>
       </c>
-      <c r="E81" s="38" t="n">
+      <c r="E81" s="25" t="n">
         <f aca="false">G18</f>
         <v>0</v>
       </c>
-      <c r="F81" s="39" t="n">
+      <c r="F81" s="24" t="n">
         <f aca="false">IF(F18&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2))),999),"")</f>
         <v>1</v>
       </c>
-      <c r="G81" s="38" t="n">
+      <c r="G81" s="25" t="n">
         <f aca="false">IF(F18&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>180</v>
       </c>
-      <c r="H81" s="39" t="n">
+      <c r="H81" s="24" t="n">
         <f aca="false">IF(F18&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2))),0),"")</f>
         <v>-0</v>
       </c>
-      <c r="I81" s="39" t="n">
+      <c r="I81" s="24" t="n">
         <f aca="false">IF(F18&lt;&gt;"",IFERROR(((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)*100,0),"")</f>
         <v>0</v>
       </c>
@@ -2745,23 +2919,23 @@
         <f aca="false">F19</f>
         <v/>
       </c>
-      <c r="E82" s="38" t="str">
+      <c r="E82" s="25" t="str">
         <f aca="false">G19</f>
         <v/>
       </c>
-      <c r="F82" s="39" t="str">
+      <c r="F82" s="24" t="str">
         <f aca="false">IF(F19&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2))),999),"")</f>
         <v/>
       </c>
-      <c r="G82" s="38" t="str">
+      <c r="G82" s="25" t="str">
         <f aca="false">IF(F19&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v/>
       </c>
-      <c r="H82" s="39" t="str">
+      <c r="H82" s="24" t="str">
         <f aca="false">IF(F19&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2))),0),"")</f>
         <v/>
       </c>
-      <c r="I82" s="39" t="str">
+      <c r="I82" s="24" t="str">
         <f aca="false">IF(F19&lt;&gt;"",IFERROR(((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)*100,0),"")</f>
         <v/>
       </c>
@@ -2778,23 +2952,23 @@
         <f aca="false">F20</f>
         <v/>
       </c>
-      <c r="E83" s="38" t="str">
+      <c r="E83" s="25" t="str">
         <f aca="false">G20</f>
         <v/>
       </c>
-      <c r="F83" s="39" t="str">
+      <c r="F83" s="24" t="str">
         <f aca="false">IF(F20&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2))),999),"")</f>
         <v/>
       </c>
-      <c r="G83" s="38" t="str">
+      <c r="G83" s="25" t="str">
         <f aca="false">IF(F20&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v/>
       </c>
-      <c r="H83" s="39" t="str">
+      <c r="H83" s="24" t="str">
         <f aca="false">IF(F20&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2))),0),"")</f>
         <v/>
       </c>
-      <c r="I83" s="39" t="str">
+      <c r="I83" s="24" t="str">
         <f aca="false">IF(F20&lt;&gt;"",IFERROR(((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)*100,0),"")</f>
         <v/>
       </c>
@@ -2811,23 +2985,23 @@
         <f aca="false">F21</f>
         <v/>
       </c>
-      <c r="E84" s="38" t="str">
+      <c r="E84" s="25" t="str">
         <f aca="false">G21</f>
         <v/>
       </c>
-      <c r="F84" s="39" t="str">
+      <c r="F84" s="24" t="str">
         <f aca="false">IF(F21&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2))),999),"")</f>
         <v/>
       </c>
-      <c r="G84" s="38" t="str">
+      <c r="G84" s="25" t="str">
         <f aca="false">IF(F21&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v/>
       </c>
-      <c r="H84" s="39" t="str">
+      <c r="H84" s="24" t="str">
         <f aca="false">IF(F21&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2))),0),"")</f>
         <v/>
       </c>
-      <c r="I84" s="39" t="str">
+      <c r="I84" s="24" t="str">
         <f aca="false">IF(F21&lt;&gt;"",IFERROR(((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)*100,0),"")</f>
         <v/>
       </c>
@@ -2844,23 +3018,23 @@
         <f aca="false">F22</f>
         <v/>
       </c>
-      <c r="E85" s="38" t="str">
+      <c r="E85" s="25" t="str">
         <f aca="false">G22</f>
         <v/>
       </c>
-      <c r="F85" s="39" t="str">
+      <c r="F85" s="24" t="str">
         <f aca="false">IF(F22&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2))),999),"")</f>
         <v/>
       </c>
-      <c r="G85" s="38" t="str">
+      <c r="G85" s="25" t="str">
         <f aca="false">IF(F22&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v/>
       </c>
-      <c r="H85" s="39" t="str">
+      <c r="H85" s="24" t="str">
         <f aca="false">IF(F22&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2))),0),"")</f>
         <v/>
       </c>
-      <c r="I85" s="39" t="str">
+      <c r="I85" s="24" t="str">
         <f aca="false">IF(F22&lt;&gt;"",IFERROR(((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)*100,0),"")</f>
         <v/>
       </c>
@@ -2877,23 +3051,23 @@
         <f aca="false">F23</f>
         <v/>
       </c>
-      <c r="E86" s="38" t="str">
+      <c r="E86" s="25" t="str">
         <f aca="false">G23</f>
         <v/>
       </c>
-      <c r="F86" s="39" t="str">
+      <c r="F86" s="24" t="str">
         <f aca="false">IF(F23&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2))),999),"")</f>
         <v/>
       </c>
-      <c r="G86" s="38" t="str">
+      <c r="G86" s="25" t="str">
         <f aca="false">IF(F23&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v/>
       </c>
-      <c r="H86" s="39" t="str">
+      <c r="H86" s="24" t="str">
         <f aca="false">IF(F23&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2))),0),"")</f>
         <v/>
       </c>
-      <c r="I86" s="39" t="str">
+      <c r="I86" s="24" t="str">
         <f aca="false">IF(F23&lt;&gt;"",IFERROR(((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)*100,0),"")</f>
         <v/>
       </c>
@@ -2910,23 +3084,23 @@
         <f aca="false">F24</f>
         <v/>
       </c>
-      <c r="E87" s="38" t="str">
+      <c r="E87" s="25" t="str">
         <f aca="false">G24</f>
         <v/>
       </c>
-      <c r="F87" s="39" t="str">
+      <c r="F87" s="24" t="str">
         <f aca="false">IF(F24&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2))),999),"")</f>
         <v/>
       </c>
-      <c r="G87" s="38" t="str">
+      <c r="G87" s="25" t="str">
         <f aca="false">IF(F24&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v/>
       </c>
-      <c r="H87" s="39" t="str">
+      <c r="H87" s="24" t="str">
         <f aca="false">IF(F24&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2))),0),"")</f>
         <v/>
       </c>
-      <c r="I87" s="39" t="str">
+      <c r="I87" s="24" t="str">
         <f aca="false">IF(F24&lt;&gt;"",IFERROR(((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)*100,0),"")</f>
         <v/>
       </c>
@@ -2943,122 +3117,122 @@
         <f aca="false">F25</f>
         <v/>
       </c>
-      <c r="E88" s="38" t="str">
+      <c r="E88" s="25" t="str">
         <f aca="false">G25</f>
         <v/>
       </c>
-      <c r="F88" s="39" t="str">
+      <c r="F88" s="24" t="str">
         <f aca="false">IF(F25&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2))),999),"")</f>
         <v/>
       </c>
-      <c r="G88" s="38" t="str">
+      <c r="G88" s="25" t="str">
         <f aca="false">IF(F25&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v/>
       </c>
-      <c r="H88" s="39" t="str">
+      <c r="H88" s="24" t="str">
         <f aca="false">IF(F25&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2))),0),"")</f>
         <v/>
       </c>
-      <c r="I88" s="39" t="str">
+      <c r="I88" s="24" t="str">
         <f aca="false">IF(F25&lt;&gt;"",IFERROR(((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)*100,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B90" s="40" t="s">
+      <c r="B90" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="C90" s="40"/>
-      <c r="D90" s="40"/>
-      <c r="E90" s="40"/>
-      <c r="F90" s="40"/>
-      <c r="G90" s="40"/>
-      <c r="H90" s="40"/>
-      <c r="I90" s="40"/>
+      <c r="C90" s="30"/>
+      <c r="D90" s="30"/>
+      <c r="E90" s="30"/>
+      <c r="F90" s="30"/>
+      <c r="G90" s="30"/>
+      <c r="H90" s="30"/>
+      <c r="I90" s="30"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B91" s="41" t="s">
+      <c r="B91" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C91" s="41"/>
-      <c r="D91" s="41"/>
-      <c r="E91" s="41"/>
-      <c r="F91" s="41"/>
-      <c r="G91" s="41"/>
-      <c r="H91" s="41"/>
-      <c r="I91" s="41"/>
+      <c r="C91" s="31"/>
+      <c r="D91" s="31"/>
+      <c r="E91" s="31"/>
+      <c r="F91" s="31"/>
+      <c r="G91" s="31"/>
+      <c r="H91" s="31"/>
+      <c r="I91" s="31"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B92" s="41" t="s">
+      <c r="B92" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="C92" s="41"/>
-      <c r="D92" s="41"/>
-      <c r="E92" s="41"/>
-      <c r="F92" s="41"/>
-      <c r="G92" s="41"/>
-      <c r="H92" s="41"/>
-      <c r="I92" s="41"/>
+      <c r="C92" s="31"/>
+      <c r="D92" s="31"/>
+      <c r="E92" s="31"/>
+      <c r="F92" s="31"/>
+      <c r="G92" s="31"/>
+      <c r="H92" s="31"/>
+      <c r="I92" s="31"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B93" s="41" t="s">
+      <c r="B93" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="C93" s="41"/>
-      <c r="D93" s="41"/>
-      <c r="E93" s="41"/>
-      <c r="F93" s="41"/>
-      <c r="G93" s="41"/>
-      <c r="H93" s="41"/>
-      <c r="I93" s="41"/>
+      <c r="C93" s="31"/>
+      <c r="D93" s="31"/>
+      <c r="E93" s="31"/>
+      <c r="F93" s="31"/>
+      <c r="G93" s="31"/>
+      <c r="H93" s="31"/>
+      <c r="I93" s="31"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B94" s="41" t="s">
+      <c r="B94" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="C94" s="41"/>
-      <c r="D94" s="41"/>
-      <c r="E94" s="41"/>
-      <c r="F94" s="41"/>
-      <c r="G94" s="41"/>
-      <c r="H94" s="41"/>
-      <c r="I94" s="41"/>
+      <c r="C94" s="31"/>
+      <c r="D94" s="31"/>
+      <c r="E94" s="31"/>
+      <c r="F94" s="31"/>
+      <c r="G94" s="31"/>
+      <c r="H94" s="31"/>
+      <c r="I94" s="31"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B95" s="41" t="s">
+      <c r="B95" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="C95" s="41"/>
-      <c r="D95" s="41"/>
-      <c r="E95" s="41"/>
-      <c r="F95" s="41"/>
-      <c r="G95" s="41"/>
-      <c r="H95" s="41"/>
-      <c r="I95" s="41"/>
+      <c r="C95" s="31"/>
+      <c r="D95" s="31"/>
+      <c r="E95" s="31"/>
+      <c r="F95" s="31"/>
+      <c r="G95" s="31"/>
+      <c r="H95" s="31"/>
+      <c r="I95" s="31"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B96" s="41" t="s">
+      <c r="B96" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="C96" s="41"/>
-      <c r="D96" s="41"/>
-      <c r="E96" s="41"/>
-      <c r="F96" s="41"/>
-      <c r="G96" s="41"/>
-      <c r="H96" s="41"/>
-      <c r="I96" s="41"/>
+      <c r="C96" s="31"/>
+      <c r="D96" s="31"/>
+      <c r="E96" s="31"/>
+      <c r="F96" s="31"/>
+      <c r="G96" s="31"/>
+      <c r="H96" s="31"/>
+      <c r="I96" s="31"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B97" s="41" t="s">
+      <c r="B97" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="C97" s="41"/>
-      <c r="D97" s="41"/>
-      <c r="E97" s="41"/>
-      <c r="F97" s="41"/>
-      <c r="G97" s="41"/>
-      <c r="H97" s="41"/>
-      <c r="I97" s="41"/>
+      <c r="C97" s="31"/>
+      <c r="D97" s="31"/>
+      <c r="E97" s="31"/>
+      <c r="F97" s="31"/>
+      <c r="G97" s="31"/>
+      <c r="H97" s="31"/>
+      <c r="I97" s="31"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="2" t="s">
@@ -3110,7 +3284,7 @@
       <c r="B104" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C104" s="42" t="n">
+      <c r="C104" s="32" t="n">
         <f aca="false">C9</f>
         <v>16</v>
       </c>
@@ -3127,7 +3301,7 @@
       <c r="B105" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C105" s="42" t="n">
+      <c r="C105" s="32" t="n">
         <f aca="false">C8</f>
         <v>0.45</v>
       </c>
@@ -3144,7 +3318,7 @@
       <c r="B106" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C106" s="42" t="n">
+      <c r="C106" s="32" t="n">
         <f aca="false">MAX(C8*1.1,C8+0.05)</f>
         <v>0.5</v>
       </c>
@@ -3204,7 +3378,7 @@
       <c r="B111" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C111" s="43" t="n">
+      <c r="C111" s="33" t="n">
         <f aca="false">IFERROR(IF(C107&gt;0,(C107-1)*C106+C105,""),"")</f>
         <v>39.95</v>
       </c>
@@ -3221,7 +3395,7 @@
       <c r="B112" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="C112" s="43" t="n">
+      <c r="C112" s="33" t="n">
         <f aca="false">(C104+C105)/2</f>
         <v>8.225</v>
       </c>
@@ -3238,7 +3412,7 @@
       <c r="B113" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C113" s="43" t="n">
+      <c r="C113" s="33" t="n">
         <f aca="false">((C104+C105)/2)/25.4</f>
         <v>0.323818897637795</v>
       </c>
@@ -3255,7 +3429,7 @@
       <c r="B114" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C114" s="43" t="n">
+      <c r="C114" s="33" t="n">
         <f aca="false">IFERROR(C111/25.4,"")</f>
         <v>1.57283464566929</v>
       </c>
@@ -3272,7 +3446,7 @@
       <c r="B115" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C115" s="43" t="n">
+      <c r="C115" s="33" t="n">
         <f aca="false">IFERROR((C113^2*C107^2)/(9*C113+10*C114),"")</f>
         <v>35.9977335339286</v>
       </c>
@@ -3289,7 +3463,7 @@
       <c r="B116" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C116" s="43" t="n">
+      <c r="C116" s="33" t="n">
         <f aca="false">IFERROR(2*PI()*C32*1000000*C115/1000000,"")</f>
         <v>1628.49909911145</v>
       </c>
@@ -3306,7 +3480,7 @@
       <c r="B117" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C117" s="43" t="n">
+      <c r="C117" s="33" t="n">
         <f aca="false">IFERROR(4*MIN(F15:F25)/(2*PI()*C32*1000000)*1000000,"")</f>
         <v>17.6838825657662</v>
       </c>
@@ -3323,7 +3497,7 @@
       <c r="B118" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C118" s="43" t="str">
+      <c r="C118" s="33" t="str">
         <f aca="false">IFERROR(IF(AND(ISNUMBER(C115),ISNUMBER(C117)),IF(C115&gt;=C117,"✔ YES","✘ INCREASE TURNS"),"—"),"")</f>
         <v>✔ YES</v>
       </c>
@@ -3335,6 +3509,649 @@
       </c>
       <c r="F118" s="9"/>
       <c r="G118" s="9"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C121" s="34"/>
+      <c r="D121" s="34"/>
+      <c r="E121" s="34"/>
+      <c r="F121" s="34"/>
+      <c r="G121" s="34"/>
+      <c r="H121" s="34"/>
+      <c r="I121" s="34"/>
+      <c r="J121" s="34"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C122" s="35"/>
+      <c r="D122" s="35"/>
+      <c r="E122" s="35"/>
+      <c r="F122" s="35"/>
+      <c r="G122" s="35"/>
+      <c r="H122" s="35"/>
+      <c r="I122" s="35"/>
+      <c r="J122" s="35"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="C124" s="36"/>
+      <c r="D124" s="36"/>
+      <c r="E124" s="36"/>
+      <c r="F124" s="36"/>
+      <c r="G124" s="36"/>
+      <c r="H124" s="36"/>
+      <c r="I124" s="36"/>
+      <c r="J124" s="36"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="C125" s="37"/>
+      <c r="D125" s="37"/>
+      <c r="E125" s="37"/>
+      <c r="F125" s="37"/>
+      <c r="G125" s="37"/>
+      <c r="H125" s="37"/>
+      <c r="I125" s="37"/>
+      <c r="J125" s="37"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="C126" s="37"/>
+      <c r="D126" s="37"/>
+      <c r="E126" s="37"/>
+      <c r="F126" s="37"/>
+      <c r="G126" s="37"/>
+      <c r="H126" s="37"/>
+      <c r="I126" s="37"/>
+      <c r="J126" s="37"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="C127" s="37"/>
+      <c r="D127" s="37"/>
+      <c r="E127" s="37"/>
+      <c r="F127" s="37"/>
+      <c r="G127" s="37"/>
+      <c r="H127" s="37"/>
+      <c r="I127" s="37"/>
+      <c r="J127" s="37"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B128" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="C128" s="37"/>
+      <c r="D128" s="37"/>
+      <c r="E128" s="37"/>
+      <c r="F128" s="37"/>
+      <c r="G128" s="37"/>
+      <c r="H128" s="37"/>
+      <c r="I128" s="37"/>
+      <c r="J128" s="37"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="C129" s="37"/>
+      <c r="D129" s="37"/>
+      <c r="E129" s="37"/>
+      <c r="F129" s="37"/>
+      <c r="G129" s="37"/>
+      <c r="H129" s="37"/>
+      <c r="I129" s="37"/>
+      <c r="J129" s="37"/>
+    </row>
+    <row r="131" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="C131" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="D131" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="E131" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="F131" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="G131" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="H131" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="I131" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="J131" s="38" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B132" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" s="40" t="n">
+        <f aca="false">C15</f>
+        <v>7.2</v>
+      </c>
+      <c r="D132" s="40" t="n">
+        <f aca="false">D15</f>
+        <v>200</v>
+      </c>
+      <c r="E132" s="40" t="n">
+        <f aca="false">IF(ISNUMBER(E15),E15,"—")</f>
+        <v>0</v>
+      </c>
+      <c r="F132" s="40" t="n">
+        <f aca="false">IF(ISNUMBER(G15),G15,"—")</f>
+        <v>0</v>
+      </c>
+      <c r="G132" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(F15),F15&gt;0,ISNUMBER(D15),D15&gt;0),IF(($C$7*IF(ISNUMBER(E15),E15,0)/F15)&gt;0,($C$7*IF(ISNUMBER(E15),E15,0)/F15)/(2*PI()*C15*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H132" s="40" t="str">
+        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(F15),F15&gt;0,ISNUMBER(D15),D15&gt;0),IF(($C$7*IF(ISNUMBER(E15),E15,0)/F15)&lt;0,1/((2*PI()*C15*1000000)*ABS(($C$7*IF(ISNUMBER(E15),E15,0)/F15)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I132" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(F15),F15&gt;0,ISNUMBER(D15),D15&gt;0),IF((F15*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))&lt;0,-1/((2*PI()*C15*1000000)*(F15*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J132" s="40" t="str">
+        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(F15),F15&gt;0,ISNUMBER(D15),D15&gt;0),IF((F15*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))&gt;0,(F15*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))/(2*PI()*C15*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B133" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C133" s="43" t="n">
+        <f aca="false">C16</f>
+        <v>10</v>
+      </c>
+      <c r="D133" s="43" t="n">
+        <f aca="false">D16</f>
+        <v>300</v>
+      </c>
+      <c r="E133" s="43" t="n">
+        <f aca="false">IF(ISNUMBER(E16),E16,"—")</f>
+        <v>100</v>
+      </c>
+      <c r="F133" s="43" t="n">
+        <f aca="false">IF(ISNUMBER(G16),G16,"—")</f>
+        <v>18.434948822922</v>
+      </c>
+      <c r="G133" s="44" t="n">
+        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(F16),F16&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$7*IF(ISNUMBER(E16),E16,0)/F16)&gt;0,($C$7*IF(ISNUMBER(E16),E16,0)/F16)/(2*PI()*C16*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>0.251646060522435</v>
+      </c>
+      <c r="H133" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(F16),F16&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$7*IF(ISNUMBER(E16),E16,0)/F16)&lt;0,1/((2*PI()*C16*1000000)*ABS(($C$7*IF(ISNUMBER(E16),E16,0)/F16)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I133" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(F16),F16&gt;0,ISNUMBER(D16),D16&gt;0),IF((F16*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&lt;0,-1/((2*PI()*C16*1000000)*(F16*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J133" s="43" t="n">
+        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(F16),F16&gt;0,ISNUMBER(D16),D16&gt;0),IF((F16*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&gt;0,(F16*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))/(2*PI()*C16*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>100.658424208974</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B134" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C134" s="40" t="n">
+        <f aca="false">C17</f>
+        <v>18</v>
+      </c>
+      <c r="D134" s="40" t="n">
+        <f aca="false">D17</f>
+        <v>450</v>
+      </c>
+      <c r="E134" s="40" t="n">
+        <f aca="false">IF(ISNUMBER(E17),E17,"—")</f>
+        <v>-80</v>
+      </c>
+      <c r="F134" s="40" t="n">
+        <f aca="false">IF(ISNUMBER(G17),G17,"—")</f>
+        <v>-10.0805979875423</v>
+      </c>
+      <c r="G134" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(F17),F17&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$7*IF(ISNUMBER(E17),E17,0)/F17)&gt;0,($C$7*IF(ISNUMBER(E17),E17,0)/F17)/(2*PI()*C17*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H134" s="40" t="n">
+        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(F17),F17&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$7*IF(ISNUMBER(E17),E17,0)/F17)&lt;0,1/((2*PI()*C17*1000000)*ABS(($C$7*IF(ISNUMBER(E17),E17,0)/F17)))*1000000000000,"—"),"—"),"—")</f>
+        <v>1010.31512621913</v>
+      </c>
+      <c r="I134" s="41" t="n">
+        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(F17),F17&gt;0,ISNUMBER(D17),D17&gt;0),IF((F17*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&lt;0,-1/((2*PI()*C17*1000000)*(F17*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>2.52578781554784</v>
+      </c>
+      <c r="J134" s="40" t="str">
+        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(F17),F17&gt;0,ISNUMBER(D17),D17&gt;0),IF((F17*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&gt;0,(F17*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))/(2*PI()*C17*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B135" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C135" s="43" t="n">
+        <f aca="false">C18</f>
+        <v>28</v>
+      </c>
+      <c r="D135" s="43" t="n">
+        <f aca="false">D18</f>
+        <v>800</v>
+      </c>
+      <c r="E135" s="43" t="n">
+        <f aca="false">IF(ISNUMBER(E18),E18,"—")</f>
+        <v>0</v>
+      </c>
+      <c r="F135" s="43" t="n">
+        <f aca="false">IF(ISNUMBER(G18),G18,"—")</f>
+        <v>0</v>
+      </c>
+      <c r="G135" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(F18),F18&gt;0,ISNUMBER(D18),D18&gt;0),IF(($C$7*IF(ISNUMBER(E18),E18,0)/F18)&gt;0,($C$7*IF(ISNUMBER(E18),E18,0)/F18)/(2*PI()*C18*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H135" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(F18),F18&gt;0,ISNUMBER(D18),D18&gt;0),IF(($C$7*IF(ISNUMBER(E18),E18,0)/F18)&lt;0,1/((2*PI()*C18*1000000)*ABS(($C$7*IF(ISNUMBER(E18),E18,0)/F18)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I135" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(F18),F18&gt;0,ISNUMBER(D18),D18&gt;0),IF((F18*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))&lt;0,-1/((2*PI()*C18*1000000)*(F18*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J135" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(F18),F18&gt;0,ISNUMBER(D18),D18&gt;0),IF((F18*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))&gt;0,(F18*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))/(2*PI()*C18*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B136" s="39" t="n">
+        <v>5</v>
+      </c>
+      <c r="C136" s="40" t="n">
+        <f aca="false">C19</f>
+        <v>0</v>
+      </c>
+      <c r="D136" s="40" t="n">
+        <f aca="false">D19</f>
+        <v>0</v>
+      </c>
+      <c r="E136" s="40" t="str">
+        <f aca="false">IF(ISNUMBER(E19),E19,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F136" s="40" t="str">
+        <f aca="false">IF(ISNUMBER(G19),G19,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G136" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(F19),F19&gt;0,ISNUMBER(D19),D19&gt;0),IF(($C$7*IF(ISNUMBER(E19),E19,0)/F19)&gt;0,($C$7*IF(ISNUMBER(E19),E19,0)/F19)/(2*PI()*C19*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H136" s="40" t="str">
+        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(F19),F19&gt;0,ISNUMBER(D19),D19&gt;0),IF(($C$7*IF(ISNUMBER(E19),E19,0)/F19)&lt;0,1/((2*PI()*C19*1000000)*ABS(($C$7*IF(ISNUMBER(E19),E19,0)/F19)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I136" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(F19),F19&gt;0,ISNUMBER(D19),D19&gt;0),IF((F19*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))&lt;0,-1/((2*PI()*C19*1000000)*(F19*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J136" s="40" t="str">
+        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(F19),F19&gt;0,ISNUMBER(D19),D19&gt;0),IF((F19*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))&gt;0,(F19*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))/(2*PI()*C19*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B137" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C137" s="43" t="n">
+        <f aca="false">C20</f>
+        <v>0</v>
+      </c>
+      <c r="D137" s="43" t="n">
+        <f aca="false">D20</f>
+        <v>0</v>
+      </c>
+      <c r="E137" s="43" t="str">
+        <f aca="false">IF(ISNUMBER(E20),E20,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F137" s="43" t="str">
+        <f aca="false">IF(ISNUMBER(G20),G20,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G137" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(F20),F20&gt;0,ISNUMBER(D20),D20&gt;0),IF(($C$7*IF(ISNUMBER(E20),E20,0)/F20)&gt;0,($C$7*IF(ISNUMBER(E20),E20,0)/F20)/(2*PI()*C20*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H137" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(F20),F20&gt;0,ISNUMBER(D20),D20&gt;0),IF(($C$7*IF(ISNUMBER(E20),E20,0)/F20)&lt;0,1/((2*PI()*C20*1000000)*ABS(($C$7*IF(ISNUMBER(E20),E20,0)/F20)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I137" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(F20),F20&gt;0,ISNUMBER(D20),D20&gt;0),IF((F20*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))&lt;0,-1/((2*PI()*C20*1000000)*(F20*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J137" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(F20),F20&gt;0,ISNUMBER(D20),D20&gt;0),IF((F20*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))&gt;0,(F20*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))/(2*PI()*C20*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B138" s="39" t="n">
+        <v>7</v>
+      </c>
+      <c r="C138" s="40" t="n">
+        <f aca="false">C21</f>
+        <v>0</v>
+      </c>
+      <c r="D138" s="40" t="n">
+        <f aca="false">D21</f>
+        <v>0</v>
+      </c>
+      <c r="E138" s="40" t="str">
+        <f aca="false">IF(ISNUMBER(E21),E21,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F138" s="40" t="str">
+        <f aca="false">IF(ISNUMBER(G21),G21,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G138" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(F21),F21&gt;0,ISNUMBER(D21),D21&gt;0),IF(($C$7*IF(ISNUMBER(E21),E21,0)/F21)&gt;0,($C$7*IF(ISNUMBER(E21),E21,0)/F21)/(2*PI()*C21*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H138" s="40" t="str">
+        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(F21),F21&gt;0,ISNUMBER(D21),D21&gt;0),IF(($C$7*IF(ISNUMBER(E21),E21,0)/F21)&lt;0,1/((2*PI()*C21*1000000)*ABS(($C$7*IF(ISNUMBER(E21),E21,0)/F21)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I138" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(F21),F21&gt;0,ISNUMBER(D21),D21&gt;0),IF((F21*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))&lt;0,-1/((2*PI()*C21*1000000)*(F21*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J138" s="40" t="str">
+        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(F21),F21&gt;0,ISNUMBER(D21),D21&gt;0),IF((F21*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))&gt;0,(F21*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))/(2*PI()*C21*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B139" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="C139" s="43" t="n">
+        <f aca="false">C22</f>
+        <v>0</v>
+      </c>
+      <c r="D139" s="43" t="n">
+        <f aca="false">D22</f>
+        <v>0</v>
+      </c>
+      <c r="E139" s="43" t="str">
+        <f aca="false">IF(ISNUMBER(E22),E22,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F139" s="43" t="str">
+        <f aca="false">IF(ISNUMBER(G22),G22,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G139" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(F22),F22&gt;0,ISNUMBER(D22),D22&gt;0),IF(($C$7*IF(ISNUMBER(E22),E22,0)/F22)&gt;0,($C$7*IF(ISNUMBER(E22),E22,0)/F22)/(2*PI()*C22*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H139" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(F22),F22&gt;0,ISNUMBER(D22),D22&gt;0),IF(($C$7*IF(ISNUMBER(E22),E22,0)/F22)&lt;0,1/((2*PI()*C22*1000000)*ABS(($C$7*IF(ISNUMBER(E22),E22,0)/F22)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I139" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(F22),F22&gt;0,ISNUMBER(D22),D22&gt;0),IF((F22*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))&lt;0,-1/((2*PI()*C22*1000000)*(F22*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J139" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(F22),F22&gt;0,ISNUMBER(D22),D22&gt;0),IF((F22*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))&gt;0,(F22*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))/(2*PI()*C22*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="39" t="n">
+        <v>9</v>
+      </c>
+      <c r="C140" s="40" t="n">
+        <f aca="false">C23</f>
+        <v>0</v>
+      </c>
+      <c r="D140" s="40" t="n">
+        <f aca="false">D23</f>
+        <v>0</v>
+      </c>
+      <c r="E140" s="40" t="str">
+        <f aca="false">IF(ISNUMBER(E23),E23,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F140" s="40" t="str">
+        <f aca="false">IF(ISNUMBER(G23),G23,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G140" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(F23),F23&gt;0,ISNUMBER(D23),D23&gt;0),IF(($C$7*IF(ISNUMBER(E23),E23,0)/F23)&gt;0,($C$7*IF(ISNUMBER(E23),E23,0)/F23)/(2*PI()*C23*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H140" s="40" t="str">
+        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(F23),F23&gt;0,ISNUMBER(D23),D23&gt;0),IF(($C$7*IF(ISNUMBER(E23),E23,0)/F23)&lt;0,1/((2*PI()*C23*1000000)*ABS(($C$7*IF(ISNUMBER(E23),E23,0)/F23)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I140" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(F23),F23&gt;0,ISNUMBER(D23),D23&gt;0),IF((F23*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))&lt;0,-1/((2*PI()*C23*1000000)*(F23*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J140" s="40" t="str">
+        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(F23),F23&gt;0,ISNUMBER(D23),D23&gt;0),IF((F23*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))&gt;0,(F23*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))/(2*PI()*C23*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B141" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="C141" s="43" t="n">
+        <f aca="false">C24</f>
+        <v>0</v>
+      </c>
+      <c r="D141" s="43" t="n">
+        <f aca="false">D24</f>
+        <v>0</v>
+      </c>
+      <c r="E141" s="43" t="str">
+        <f aca="false">IF(ISNUMBER(E24),E24,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F141" s="43" t="str">
+        <f aca="false">IF(ISNUMBER(G24),G24,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G141" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(F24),F24&gt;0,ISNUMBER(D24),D24&gt;0),IF(($C$7*IF(ISNUMBER(E24),E24,0)/F24)&gt;0,($C$7*IF(ISNUMBER(E24),E24,0)/F24)/(2*PI()*C24*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H141" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(F24),F24&gt;0,ISNUMBER(D24),D24&gt;0),IF(($C$7*IF(ISNUMBER(E24),E24,0)/F24)&lt;0,1/((2*PI()*C24*1000000)*ABS(($C$7*IF(ISNUMBER(E24),E24,0)/F24)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I141" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(F24),F24&gt;0,ISNUMBER(D24),D24&gt;0),IF((F24*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))&lt;0,-1/((2*PI()*C24*1000000)*(F24*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J141" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(F24),F24&gt;0,ISNUMBER(D24),D24&gt;0),IF((F24*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))&gt;0,(F24*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))/(2*PI()*C24*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B142" s="39" t="n">
+        <v>11</v>
+      </c>
+      <c r="C142" s="40" t="n">
+        <f aca="false">C25</f>
+        <v>0</v>
+      </c>
+      <c r="D142" s="40" t="n">
+        <f aca="false">D25</f>
+        <v>0</v>
+      </c>
+      <c r="E142" s="40" t="str">
+        <f aca="false">IF(ISNUMBER(E25),E25,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F142" s="40" t="str">
+        <f aca="false">IF(ISNUMBER(G25),G25,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G142" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(F25),F25&gt;0,ISNUMBER(D25),D25&gt;0),IF(($C$7*IF(ISNUMBER(E25),E25,0)/F25)&gt;0,($C$7*IF(ISNUMBER(E25),E25,0)/F25)/(2*PI()*C25*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H142" s="40" t="str">
+        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(F25),F25&gt;0,ISNUMBER(D25),D25&gt;0),IF(($C$7*IF(ISNUMBER(E25),E25,0)/F25)&lt;0,1/((2*PI()*C25*1000000)*ABS(($C$7*IF(ISNUMBER(E25),E25,0)/F25)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I142" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(F25),F25&gt;0,ISNUMBER(D25),D25&gt;0),IF((F25*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))&lt;0,-1/((2*PI()*C25*1000000)*(F25*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J142" s="40" t="str">
+        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(F25),F25&gt;0,ISNUMBER(D25),D25&gt;0),IF((F25*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))&gt;0,(F25*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))/(2*PI()*C25*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B144" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="C144" s="36"/>
+      <c r="D144" s="36"/>
+      <c r="E144" s="36"/>
+      <c r="F144" s="36"/>
+      <c r="G144" s="36"/>
+      <c r="H144" s="36"/>
+      <c r="I144" s="36"/>
+      <c r="J144" s="36"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B145" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C145" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="D145" s="37"/>
+      <c r="E145" s="37"/>
+      <c r="F145" s="37"/>
+      <c r="G145" s="37"/>
+      <c r="H145" s="37"/>
+      <c r="I145" s="37"/>
+      <c r="J145" s="37"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="C146" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="D146" s="37"/>
+      <c r="E146" s="37"/>
+      <c r="F146" s="37"/>
+      <c r="G146" s="37"/>
+      <c r="H146" s="37"/>
+      <c r="I146" s="37"/>
+      <c r="J146" s="37"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C147" s="37" t="s">
+        <v>130</v>
+      </c>
+      <c r="D147" s="37"/>
+      <c r="E147" s="37"/>
+      <c r="F147" s="37"/>
+      <c r="G147" s="37"/>
+      <c r="H147" s="37"/>
+      <c r="I147" s="37"/>
+      <c r="J147" s="37"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="C148" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="D148" s="37"/>
+      <c r="E148" s="37"/>
+      <c r="F148" s="37"/>
+      <c r="G148" s="37"/>
+      <c r="H148" s="37"/>
+      <c r="I148" s="37"/>
+      <c r="J148" s="37"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B149" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="C149" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="D149" s="37"/>
+      <c r="E149" s="37"/>
+      <c r="F149" s="37"/>
+      <c r="G149" s="37"/>
+      <c r="H149" s="37"/>
+      <c r="I149" s="37"/>
+      <c r="J149" s="37"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B150" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="C150" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="D150" s="37"/>
+      <c r="E150" s="37"/>
+      <c r="F150" s="37"/>
+      <c r="G150" s="37"/>
+      <c r="H150" s="37"/>
+      <c r="I150" s="37"/>
+      <c r="J150" s="37"/>
     </row>
     <row r="1048554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -3360,7 +4177,7 @@
     <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <mergeCells count="47">
+  <mergeCells count="62">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B5:I5"/>
@@ -3408,6 +4225,21 @@
     <mergeCell ref="E116:G116"/>
     <mergeCell ref="E117:G117"/>
     <mergeCell ref="E118:G118"/>
+    <mergeCell ref="B121:J121"/>
+    <mergeCell ref="B122:J122"/>
+    <mergeCell ref="B124:J124"/>
+    <mergeCell ref="B125:J125"/>
+    <mergeCell ref="B126:J126"/>
+    <mergeCell ref="B127:J127"/>
+    <mergeCell ref="B128:J128"/>
+    <mergeCell ref="B129:J129"/>
+    <mergeCell ref="B144:J144"/>
+    <mergeCell ref="C145:J145"/>
+    <mergeCell ref="C146:J146"/>
+    <mergeCell ref="C147:J147"/>
+    <mergeCell ref="C148:J148"/>
+    <mergeCell ref="C149:J149"/>
+    <mergeCell ref="C150:J150"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Autotransformer_UnUn_AirCore_Calculator.xlsx
+++ b/Autotransformer_UnUn_AirCore_Calculator.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="134">
   <si>
     <t xml:space="preserve">✦  AIR-CORE AUTOTRANSFORMER UnUn CALCULATOR  ✦</t>
   </si>
@@ -99,131 +99,122 @@
 Reactance (+L / −C)</t>
   </si>
   <si>
+    <t xml:space="preserve">✦  AIR-CORE UnUn DESIGN  —  SUMMARY DASHBOARD  ✦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All key results in one place. Go to individual sheets to adjust inputs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEY PARAMETERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target Z_out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min. Tap Frequency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wire Dia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T_ref turns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active taps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inductance L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">µH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L sufficient?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAP SUMMARY — ALL ACTIVE TAPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequency (MHz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z_in (Ω)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase (°)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turns Ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cum. Turns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Loss (dB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refl. Power (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✦  AIR-CORE AUTOTRANSFORMER  —  WINDING DESIGN  ✦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tap turn counts, cumulative turns, wire lengths, and DC resistance per section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PER-TAP WINDING CALCULATIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turns Ratio
+n = √(|Z|/Z₀)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turns at Tap
+(cumulative from low-Z end)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δ Turns
+(this section)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section Wire
+Length (mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section DC
+Resistance (mΩ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative
+Wire (mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTALS (active taps only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✦  AIR-CORE UnUn  —  RF PERFORMANCE  ✦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWR, Return Loss, Mismatch Loss, and Reflected Power per tap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PER-TAP RF PERFORMANCE  (referenced to 50Ω system)</t>
+  </si>
+  <si>
     <t xml:space="preserve">|Z| (Ω)
 Magnitude</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phase (°)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turns Ratio
-n = √(|Z|/Z₀)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✦  AIR-CORE UnUn DESIGN  —  SUMMARY DASHBOARD  ✦</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All key results in one place. Go to individual sheets to adjust inputs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY PARAMETERS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target Z_out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min. Tap Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MHz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wire Dia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T_ref turns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active taps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total wire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inductance L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">µH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L sufficient?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAP SUMMARY — ALL ACTIVE TAPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frequency (MHz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_in (Ω)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turns Ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cum. Turns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Return Loss (dB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refl. Power (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✦  AIR-CORE AUTOTRANSFORMER  —  WINDING DESIGN  ✦</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tap turn counts, cumulative turns, wire lengths, and DC resistance per section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PER-TAP WINDING CALCULATIONS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turns Ratio n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turns at Tap
-(cumulative from low-Z end)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Δ Turns
-(this section)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Section Wire
-Length (mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Section DC
-Resistance (mΩ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cumulative
-Wire (mm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTALS (active taps only)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">✦  AIR-CORE UnUn  —  RF PERFORMANCE  ✦</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SWR, Return Loss, Mismatch Loss, and Reflected Power per tap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PER-TAP RF PERFORMANCE  (referenced to 50Ω system)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">|Z| (Ω)</t>
   </si>
   <si>
     <t xml:space="preserve">SWR
@@ -470,7 +461,7 @@
     <numFmt numFmtId="172" formatCode="0.00"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,15 +485,13 @@
       <family val="0"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Cantarell Light"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Cantarell Light"/>
@@ -524,7 +513,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
       <sz val="10"/>
       <color rgb="FF555555"/>
       <name val="Cantarell Light"/>
@@ -532,71 +520,36 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Cantarell Light"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFD700"/>
       <name val="Cantarell Light"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FFFFD700"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <color rgb="FF8EA9C1"/>
+      <name val="Cantarell Light"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
       <sz val="10"/>
-      <color rgb="FF8EA9C1"/>
-      <name val="Arial"/>
+      <color rgb="FF404040"/>
+      <name val="Cantarell Light"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF404040"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
       <color rgb="FF1F3864"/>
-      <name val="Arial"/>
+      <name val="Cantarell Light"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -724,16 +677,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -741,11 +694,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -777,7 +730,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -789,6 +750,38 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -797,30 +790,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="169" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="172" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -829,11 +802,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -845,11 +814,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -857,55 +826,51 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1161,7 +1126,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:J1048576"/>
+  <dimension ref="B2:J150"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.45"/>
@@ -1298,7 +1263,7 @@
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
     </row>
-    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="10" t="s">
         <v>18</v>
       </c>
@@ -1306,7 +1271,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="11" t="n">
-        <f aca="false">IFERROR(CEILING(5/MIN(I15:I25),1),5)</f>
+        <f aca="false">IFERROR(CEILING(5/MIN(D59:D69),1),5)</f>
         <v>3</v>
       </c>
       <c r="E11" s="12" t="s">
@@ -1324,12 +1289,12 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
         <v>21</v>
       </c>
@@ -1342,345 +1307,205 @@
       <c r="E14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="13" t="n">
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="15" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>7.2</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="E15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D15),D15&gt;0),SQRT(D15^2+IF(ISNUMBER(E15),E15,0)^2),"")</f>
-        <v>200</v>
-      </c>
-      <c r="G15" s="17" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D15),D15&gt;0),IFERROR(DEGREES(ATAN2(D15,IF(ISNUMBER(E15),E15,0))),""),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="18" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D15),D15&gt;0),IF(1&lt;=$C$10,"YES","—"),"—")</f>
-        <v>YES</v>
-      </c>
-      <c r="I15" s="19" t="n">
-        <f aca="false">IF(F15&lt;&gt;"",SQRT(F15/MAX($C$7,0.000000001)),"")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="20" t="n">
+      <c r="E15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="21"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="22" t="n">
         <v>2</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="F16" s="16" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D16),D16&gt;0),SQRT(D16^2+IF(ISNUMBER(E16),E16,0)^2),"")</f>
-        <v>316.227766016838</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D16),D16&gt;0),IFERROR(DEGREES(ATAN2(D16,IF(ISNUMBER(E16),E16,0))),""),"")</f>
-        <v>18.434948822922</v>
-      </c>
-      <c r="H16" s="18" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D16),D16&gt;0),IF(2&lt;=$C$10,"YES","—"),"—")</f>
-        <v>YES</v>
-      </c>
-      <c r="I16" s="19" t="n">
-        <f aca="false">IF(F16&lt;&gt;"",SQRT(F16/MAX($C$7,0.000000001)),"")</f>
-        <v>2.51486685936587</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="13" t="n">
+      <c r="F16" s="18"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="21"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="15" t="n">
         <v>3</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="16" t="n">
         <v>450</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="17" t="n">
         <v>-80</v>
       </c>
-      <c r="F17" s="16" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D17),D17&gt;0),SQRT(D17^2+IF(ISNUMBER(E17),E17,0)^2),"")</f>
-        <v>457.055795281058</v>
-      </c>
-      <c r="G17" s="17" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D17),D17&gt;0),IFERROR(DEGREES(ATAN2(D17,IF(ISNUMBER(E17),E17,0))),""),"")</f>
-        <v>-10.0805979875423</v>
-      </c>
-      <c r="H17" s="18" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D17),D17&gt;0),IF(3&lt;=$C$10,"YES","—"),"—")</f>
-        <v>YES</v>
-      </c>
-      <c r="I17" s="19" t="n">
-        <f aca="false">IF(F17&lt;&gt;"",SQRT(F17/MAX($C$7,0.000000001)),"")</f>
-        <v>3.02342784031985</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="20" t="n">
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="21"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="22" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="16" t="n">
         <v>800</v>
       </c>
-      <c r="E18" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D18),D18&gt;0),SQRT(D18^2+IF(ISNUMBER(E18),E18,0)^2),"")</f>
-        <v>800</v>
-      </c>
-      <c r="G18" s="17" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D18),D18&gt;0),IFERROR(DEGREES(ATAN2(D18,IF(ISNUMBER(E18),E18,0))),""),"")</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="18" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D18),D18&gt;0),IF(4&lt;=$C$10,"YES","—"),"—")</f>
-        <v>YES</v>
-      </c>
-      <c r="I18" s="19" t="n">
-        <f aca="false">IF(F18&lt;&gt;"",SQRT(F18/MAX($C$7,0.000000001)),"")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="n">
+      <c r="E18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="21"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="15" t="n">
         <v>5</v>
       </c>
       <c r="C19" s="7"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D19),D19&gt;0),SQRT(D19^2+IF(ISNUMBER(E19),E19,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="17" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D19),D19&gt;0),IFERROR(DEGREES(ATAN2(D19,IF(ISNUMBER(E19),E19,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="18" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D19),D19&gt;0),IF(5&lt;=$C$10,"YES","—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I19" s="19" t="str">
-        <f aca="false">IF(F19&lt;&gt;"",SQRT(F19/MAX($C$7,0.000000001)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="20" t="n">
+      <c r="D19" s="16"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="21"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="22" t="n">
         <v>6</v>
       </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="16" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D20),D20&gt;0),SQRT(D20^2+IF(ISNUMBER(E20),E20,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="17" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D20),D20&gt;0),IFERROR(DEGREES(ATAN2(D20,IF(ISNUMBER(E20),E20,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="18" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D20),D20&gt;0),IF(6&lt;=$C$10,"YES","—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I20" s="19" t="str">
-        <f aca="false">IF(F20&lt;&gt;"",SQRT(F20/MAX($C$7,0.000000001)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="n">
+      <c r="D20" s="16"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="21"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="15" t="n">
         <v>7</v>
       </c>
       <c r="C21" s="7"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D21),D21&gt;0),SQRT(D21^2+IF(ISNUMBER(E21),E21,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="17" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D21),D21&gt;0),IFERROR(DEGREES(ATAN2(D21,IF(ISNUMBER(E21),E21,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="18" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D21),D21&gt;0),IF(7&lt;=$C$10,"YES","—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I21" s="19" t="str">
-        <f aca="false">IF(F21&lt;&gt;"",SQRT(F21/MAX($C$7,0.000000001)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="20" t="n">
+      <c r="D21" s="16"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="21"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="22" t="n">
         <v>8</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="16" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D22),D22&gt;0),SQRT(D22^2+IF(ISNUMBER(E22),E22,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="17" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D22),D22&gt;0),IFERROR(DEGREES(ATAN2(D22,IF(ISNUMBER(E22),E22,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="18" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D22),D22&gt;0),IF(8&lt;=$C$10,"YES","—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I22" s="19" t="str">
-        <f aca="false">IF(F22&lt;&gt;"",SQRT(F22/MAX($C$7,0.000000001)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="13" t="n">
+      <c r="D22" s="16"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="21"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="15" t="n">
         <v>9</v>
       </c>
       <c r="C23" s="7"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="16" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D23),D23&gt;0),SQRT(D23^2+IF(ISNUMBER(E23),E23,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="17" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D23),D23&gt;0),IFERROR(DEGREES(ATAN2(D23,IF(ISNUMBER(E23),E23,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="18" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D23),D23&gt;0),IF(9&lt;=$C$10,"YES","—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I23" s="19" t="str">
-        <f aca="false">IF(F23&lt;&gt;"",SQRT(F23/MAX($C$7,0.000000001)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="20" t="n">
+      <c r="D23" s="16"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="21"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="22" t="n">
         <v>10</v>
       </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="16" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D24),D24&gt;0),SQRT(D24^2+IF(ISNUMBER(E24),E24,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="17" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D24),D24&gt;0),IFERROR(DEGREES(ATAN2(D24,IF(ISNUMBER(E24),E24,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="18" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D24),D24&gt;0),IF(10&lt;=$C$10,"YES","—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I24" s="19" t="str">
-        <f aca="false">IF(F24&lt;&gt;"",SQRT(F24/MAX($C$7,0.000000001)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="n">
+      <c r="D24" s="16"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="21"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="15" t="n">
         <v>11</v>
       </c>
       <c r="C25" s="7"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D25),D25&gt;0),SQRT(D25^2+IF(ISNUMBER(E25),E25,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="17" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D25),D25&gt;0),IFERROR(DEGREES(ATAN2(D25,IF(ISNUMBER(E25),E25,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="18" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D25),D25&gt;0),IF(11&lt;=$C$10,"YES","—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I25" s="19" t="str">
-        <f aca="false">IF(F25&lt;&gt;"",SQRT(F25/MAX($C$7,0.000000001)),"")</f>
-        <v/>
-      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="21" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" s="23" t="n">
         <f aca="false">C7</f>
         <v>50</v>
       </c>
@@ -1688,23 +1513,23 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="21" t="n">
+        <v>29</v>
+      </c>
+      <c r="C32" s="23" t="n">
         <f aca="false">IFERROR(aggregate(15,6,C15:C25*(1/(H15:H25="YES")),1),MIN(C15:C25))</f>
         <v>7.2</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="21" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" s="23" t="n">
         <f aca="false">C8</f>
         <v>0.45</v>
       </c>
@@ -1712,23 +1537,23 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" s="23" t="n">
         <f aca="false">C11</f>
         <v>20</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" s="21" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" s="23" t="n">
         <f aca="false">C10</f>
         <v>4</v>
       </c>
@@ -1736,11 +1561,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" s="24" t="n">
         <f aca="false">I71</f>
         <v>4134.33593212417</v>
       </c>
@@ -1748,23 +1573,23 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" s="25" t="n">
         <f aca="false">IFERROR(C115,"—")</f>
         <v>35.9977335339286</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="21" t="str">
+        <v>38</v>
+      </c>
+      <c r="C38" s="23" t="str">
         <f aca="false">IFERROR(C118,"—")</f>
         <v>✔ YES</v>
       </c>
@@ -1772,7 +1597,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -1783,52 +1608,52 @@
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G41" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="H41" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F41" s="5" t="s">
+      <c r="I41" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="J41" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="13" t="n">
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="18" t="n">
+      <c r="C42" s="23" t="n">
         <f aca="false">C15</f>
         <v>7.2</v>
       </c>
-      <c r="D42" s="16" t="n">
-        <f aca="false">F15</f>
+      <c r="D42" s="26" t="n">
+        <f aca="false">D78</f>
         <v>200</v>
       </c>
-      <c r="E42" s="17" t="n">
-        <f aca="false">G15</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="19" t="n">
+      <c r="E42" s="27" t="n">
+        <f aca="false">E78</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="28" t="n">
         <f aca="false">D59</f>
         <v>2</v>
       </c>
@@ -1836,36 +1661,36 @@
         <f aca="false">E59</f>
         <v>40</v>
       </c>
-      <c r="H42" s="24" t="n">
+      <c r="H42" s="29" t="n">
         <f aca="false">F78</f>
         <v>1</v>
       </c>
-      <c r="I42" s="25" t="n">
+      <c r="I42" s="30" t="n">
         <f aca="false">G78</f>
         <v>180</v>
       </c>
-      <c r="J42" s="24" t="n">
+      <c r="J42" s="29" t="n">
         <f aca="false">I78</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="20" t="n">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="18" t="n">
+      <c r="C43" s="23" t="n">
         <f aca="false">C16</f>
         <v>10</v>
       </c>
-      <c r="D43" s="16" t="n">
-        <f aca="false">F16</f>
+      <c r="D43" s="26" t="n">
+        <f aca="false">D79</f>
         <v>316.227766016838</v>
       </c>
-      <c r="E43" s="17" t="n">
-        <f aca="false">G16</f>
+      <c r="E43" s="27" t="n">
+        <f aca="false">E79</f>
         <v>18.434948822922</v>
       </c>
-      <c r="F43" s="19" t="n">
+      <c r="F43" s="28" t="n">
         <f aca="false">D60</f>
         <v>2.51486685936587</v>
       </c>
@@ -1873,36 +1698,36 @@
         <f aca="false">E60</f>
         <v>50</v>
       </c>
-      <c r="H43" s="24" t="n">
+      <c r="H43" s="29" t="n">
         <f aca="false">F79</f>
         <v>1.38742588672279</v>
       </c>
-      <c r="I43" s="25" t="n">
+      <c r="I43" s="30" t="n">
         <f aca="false">G79</f>
         <v>15.7948252576199</v>
       </c>
-      <c r="J43" s="24" t="n">
+      <c r="J43" s="29" t="n">
         <f aca="false">I79</f>
         <v>2.6334038989724</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="13" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C44" s="18" t="n">
+      <c r="C44" s="23" t="n">
         <f aca="false">C17</f>
         <v>18</v>
       </c>
-      <c r="D44" s="16" t="n">
-        <f aca="false">F17</f>
+      <c r="D44" s="26" t="n">
+        <f aca="false">D80</f>
         <v>457.055795281058</v>
       </c>
-      <c r="E44" s="17" t="n">
-        <f aca="false">G17</f>
+      <c r="E44" s="27" t="n">
+        <f aca="false">E80</f>
         <v>-10.0805979875423</v>
       </c>
-      <c r="F44" s="19" t="n">
+      <c r="F44" s="28" t="n">
         <f aca="false">D61</f>
         <v>3.02342784031985</v>
       </c>
@@ -1910,36 +1735,36 @@
         <f aca="false">E61</f>
         <v>60</v>
       </c>
-      <c r="H44" s="24" t="n">
+      <c r="H44" s="29" t="n">
         <f aca="false">F80</f>
         <v>1.19345732284679</v>
       </c>
-      <c r="I44" s="25" t="n">
+      <c r="I44" s="30" t="n">
         <f aca="false">G80</f>
         <v>21.0908803086925</v>
       </c>
-      <c r="J44" s="24" t="n">
+      <c r="J44" s="29" t="n">
         <f aca="false">I80</f>
         <v>0.777878860128034</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="20" t="n">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="C45" s="18" t="n">
+      <c r="C45" s="23" t="n">
         <f aca="false">C18</f>
         <v>28</v>
       </c>
-      <c r="D45" s="16" t="n">
-        <f aca="false">F18</f>
+      <c r="D45" s="26" t="n">
+        <f aca="false">D81</f>
         <v>800</v>
       </c>
-      <c r="E45" s="17" t="n">
-        <f aca="false">G18</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="19" t="n">
+      <c r="E45" s="27" t="n">
+        <f aca="false">E81</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="28" t="n">
         <f aca="false">D62</f>
         <v>4</v>
       </c>
@@ -1947,281 +1772,281 @@
         <f aca="false">E62</f>
         <v>80</v>
       </c>
-      <c r="H45" s="24" t="n">
+      <c r="H45" s="29" t="n">
         <f aca="false">F81</f>
         <v>1</v>
       </c>
-      <c r="I45" s="25" t="n">
+      <c r="I45" s="30" t="n">
         <f aca="false">G81</f>
         <v>180</v>
       </c>
-      <c r="J45" s="24" t="n">
+      <c r="J45" s="29" t="n">
         <f aca="false">I81</f>
         <v>0</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="13" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C46" s="18" t="n">
+      <c r="C46" s="23" t="n">
         <f aca="false">C19</f>
         <v>0</v>
       </c>
-      <c r="D46" s="18" t="str">
-        <f aca="false">F19</f>
-        <v/>
-      </c>
-      <c r="E46" s="18" t="str">
-        <f aca="false">G19</f>
-        <v/>
-      </c>
-      <c r="F46" s="18" t="str">
+      <c r="D46" s="23" t="str">
+        <f aca="false">D82</f>
+        <v/>
+      </c>
+      <c r="E46" s="23" t="str">
+        <f aca="false">E82</f>
+        <v/>
+      </c>
+      <c r="F46" s="23" t="str">
         <f aca="false">D63</f>
         <v/>
       </c>
-      <c r="G46" s="18" t="str">
+      <c r="G46" s="23" t="str">
         <f aca="false">E63</f>
         <v/>
       </c>
-      <c r="H46" s="18" t="str">
+      <c r="H46" s="23" t="str">
         <f aca="false">F82</f>
         <v/>
       </c>
-      <c r="I46" s="18" t="str">
+      <c r="I46" s="23" t="str">
         <f aca="false">G82</f>
         <v/>
       </c>
-      <c r="J46" s="18" t="str">
+      <c r="J46" s="23" t="str">
         <f aca="false">I82</f>
         <v/>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="20" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="C47" s="18" t="n">
+      <c r="C47" s="23" t="n">
         <f aca="false">C20</f>
         <v>0</v>
       </c>
-      <c r="D47" s="18" t="str">
-        <f aca="false">F20</f>
-        <v/>
-      </c>
-      <c r="E47" s="18" t="str">
-        <f aca="false">G20</f>
-        <v/>
-      </c>
-      <c r="F47" s="18" t="str">
+      <c r="D47" s="23" t="str">
+        <f aca="false">D83</f>
+        <v/>
+      </c>
+      <c r="E47" s="23" t="str">
+        <f aca="false">E83</f>
+        <v/>
+      </c>
+      <c r="F47" s="23" t="str">
         <f aca="false">D64</f>
         <v/>
       </c>
-      <c r="G47" s="18" t="str">
+      <c r="G47" s="23" t="str">
         <f aca="false">E64</f>
         <v/>
       </c>
-      <c r="H47" s="18" t="str">
+      <c r="H47" s="23" t="str">
         <f aca="false">F83</f>
         <v/>
       </c>
-      <c r="I47" s="18" t="str">
+      <c r="I47" s="23" t="str">
         <f aca="false">G83</f>
         <v/>
       </c>
-      <c r="J47" s="18" t="str">
+      <c r="J47" s="23" t="str">
         <f aca="false">I83</f>
         <v/>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="13" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C48" s="18" t="n">
+      <c r="C48" s="23" t="n">
         <f aca="false">C21</f>
         <v>0</v>
       </c>
-      <c r="D48" s="18" t="str">
-        <f aca="false">F21</f>
-        <v/>
-      </c>
-      <c r="E48" s="18" t="str">
-        <f aca="false">G21</f>
-        <v/>
-      </c>
-      <c r="F48" s="18" t="str">
+      <c r="D48" s="23" t="str">
+        <f aca="false">D84</f>
+        <v/>
+      </c>
+      <c r="E48" s="23" t="str">
+        <f aca="false">E84</f>
+        <v/>
+      </c>
+      <c r="F48" s="23" t="str">
         <f aca="false">D65</f>
         <v/>
       </c>
-      <c r="G48" s="18" t="str">
+      <c r="G48" s="23" t="str">
         <f aca="false">E65</f>
         <v/>
       </c>
-      <c r="H48" s="18" t="str">
+      <c r="H48" s="23" t="str">
         <f aca="false">F84</f>
         <v/>
       </c>
-      <c r="I48" s="18" t="str">
+      <c r="I48" s="23" t="str">
         <f aca="false">G84</f>
         <v/>
       </c>
-      <c r="J48" s="18" t="str">
+      <c r="J48" s="23" t="str">
         <f aca="false">I84</f>
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="20" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="C49" s="18" t="n">
+      <c r="C49" s="23" t="n">
         <f aca="false">C22</f>
         <v>0</v>
       </c>
-      <c r="D49" s="18" t="str">
-        <f aca="false">F22</f>
-        <v/>
-      </c>
-      <c r="E49" s="18" t="str">
-        <f aca="false">G22</f>
-        <v/>
-      </c>
-      <c r="F49" s="18" t="str">
+      <c r="D49" s="23" t="str">
+        <f aca="false">D85</f>
+        <v/>
+      </c>
+      <c r="E49" s="23" t="str">
+        <f aca="false">E85</f>
+        <v/>
+      </c>
+      <c r="F49" s="23" t="str">
         <f aca="false">D66</f>
         <v/>
       </c>
-      <c r="G49" s="18" t="str">
+      <c r="G49" s="23" t="str">
         <f aca="false">E66</f>
         <v/>
       </c>
-      <c r="H49" s="18" t="str">
+      <c r="H49" s="23" t="str">
         <f aca="false">F85</f>
         <v/>
       </c>
-      <c r="I49" s="18" t="str">
+      <c r="I49" s="23" t="str">
         <f aca="false">G85</f>
         <v/>
       </c>
-      <c r="J49" s="18" t="str">
+      <c r="J49" s="23" t="str">
         <f aca="false">I85</f>
         <v/>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="13" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C50" s="18" t="n">
+      <c r="C50" s="23" t="n">
         <f aca="false">C23</f>
         <v>0</v>
       </c>
-      <c r="D50" s="18" t="str">
-        <f aca="false">F23</f>
-        <v/>
-      </c>
-      <c r="E50" s="18" t="str">
-        <f aca="false">G23</f>
-        <v/>
-      </c>
-      <c r="F50" s="18" t="str">
+      <c r="D50" s="23" t="str">
+        <f aca="false">D86</f>
+        <v/>
+      </c>
+      <c r="E50" s="23" t="str">
+        <f aca="false">E86</f>
+        <v/>
+      </c>
+      <c r="F50" s="23" t="str">
         <f aca="false">D67</f>
         <v/>
       </c>
-      <c r="G50" s="18" t="str">
+      <c r="G50" s="23" t="str">
         <f aca="false">E67</f>
         <v/>
       </c>
-      <c r="H50" s="18" t="str">
+      <c r="H50" s="23" t="str">
         <f aca="false">F86</f>
         <v/>
       </c>
-      <c r="I50" s="18" t="str">
+      <c r="I50" s="23" t="str">
         <f aca="false">G86</f>
         <v/>
       </c>
-      <c r="J50" s="18" t="str">
+      <c r="J50" s="23" t="str">
         <f aca="false">I86</f>
         <v/>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="20" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="C51" s="18" t="n">
+      <c r="C51" s="23" t="n">
         <f aca="false">C24</f>
         <v>0</v>
       </c>
-      <c r="D51" s="18" t="str">
-        <f aca="false">F24</f>
-        <v/>
-      </c>
-      <c r="E51" s="18" t="str">
-        <f aca="false">G24</f>
-        <v/>
-      </c>
-      <c r="F51" s="18" t="str">
+      <c r="D51" s="23" t="str">
+        <f aca="false">D87</f>
+        <v/>
+      </c>
+      <c r="E51" s="23" t="str">
+        <f aca="false">E87</f>
+        <v/>
+      </c>
+      <c r="F51" s="23" t="str">
         <f aca="false">D68</f>
         <v/>
       </c>
-      <c r="G51" s="18" t="str">
+      <c r="G51" s="23" t="str">
         <f aca="false">E68</f>
         <v/>
       </c>
-      <c r="H51" s="18" t="str">
+      <c r="H51" s="23" t="str">
         <f aca="false">F87</f>
         <v/>
       </c>
-      <c r="I51" s="18" t="str">
+      <c r="I51" s="23" t="str">
         <f aca="false">G87</f>
         <v/>
       </c>
-      <c r="J51" s="18" t="str">
+      <c r="J51" s="23" t="str">
         <f aca="false">I87</f>
         <v/>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="13" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="C52" s="18" t="n">
+      <c r="C52" s="23" t="n">
         <f aca="false">C25</f>
         <v>0</v>
       </c>
-      <c r="D52" s="18" t="str">
-        <f aca="false">F25</f>
-        <v/>
-      </c>
-      <c r="E52" s="18" t="str">
-        <f aca="false">G25</f>
-        <v/>
-      </c>
-      <c r="F52" s="18" t="str">
+      <c r="D52" s="23" t="str">
+        <f aca="false">D88</f>
+        <v/>
+      </c>
+      <c r="E52" s="23" t="str">
+        <f aca="false">E88</f>
+        <v/>
+      </c>
+      <c r="F52" s="23" t="str">
         <f aca="false">D69</f>
         <v/>
       </c>
-      <c r="G52" s="18" t="str">
+      <c r="G52" s="23" t="str">
         <f aca="false">E69</f>
         <v/>
       </c>
-      <c r="H52" s="18" t="str">
+      <c r="H52" s="23" t="str">
         <f aca="false">F88</f>
         <v/>
       </c>
-      <c r="I52" s="18" t="str">
+      <c r="I52" s="23" t="str">
         <f aca="false">G88</f>
         <v/>
       </c>
-      <c r="J52" s="18" t="str">
+      <c r="J52" s="23" t="str">
         <f aca="false">I88</f>
         <v/>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -2230,11 +2055,11 @@
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
+      <c r="J54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
@@ -2243,11 +2068,11 @@
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
+      <c r="J55" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
@@ -2256,47 +2081,45 @@
       <c r="G57" s="4"/>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-    </row>
-    <row r="58" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J57" s="13"/>
+    </row>
+    <row r="58" customFormat="false" ht="38.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D58" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G58" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="H58" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="I58" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I58" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="J58" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="13" t="n">
+      <c r="J58" s="13"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="18" t="n">
+      <c r="C59" s="23" t="n">
         <f aca="false">C15</f>
         <v>7.2</v>
       </c>
-      <c r="D59" s="19" t="n">
-        <f aca="false">IF(I15&lt;&gt;"",I15,"")</f>
+      <c r="D59" s="28" t="n">
+        <f aca="false">IF(D78&lt;&gt;"",SQRT(D78/MAX($C$7,0.000000001)),"")</f>
         <v>2</v>
       </c>
       <c r="E59" s="11" t="n">
@@ -2307,33 +2130,30 @@
         <f aca="false">IF(E59&lt;&gt;"",E59,"")</f>
         <v>40</v>
       </c>
-      <c r="G59" s="26" t="n">
+      <c r="G59" s="24" t="n">
         <f aca="false">IF(F59&lt;&gt;"",F59*PI()*($C$9+$C$8),"")</f>
         <v>2067.16796606208</v>
       </c>
-      <c r="H59" s="16" t="n">
+      <c r="H59" s="26" t="n">
         <f aca="false">IF(G59&lt;&gt;"",G59*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>224.077432098765</v>
       </c>
-      <c r="I59" s="26" t="n">
+      <c r="I59" s="24" t="n">
         <f aca="false">IF(G59&lt;&gt;"",G59,"")</f>
         <v>2067.16796606208</v>
       </c>
-      <c r="J59" s="18" t="str">
-        <f aca="false">H15</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="20" t="n">
+      <c r="J59" s="20"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="C60" s="18" t="n">
+      <c r="C60" s="23" t="n">
         <f aca="false">C16</f>
         <v>10</v>
       </c>
-      <c r="D60" s="19" t="n">
-        <f aca="false">IF(I16&lt;&gt;"",I16,"")</f>
+      <c r="D60" s="28" t="n">
+        <f aca="false">IF(D79&lt;&gt;"",SQRT(D79/MAX($C$7,0.000000001)),"")</f>
         <v>2.51486685936587</v>
       </c>
       <c r="E60" s="11" t="n">
@@ -2344,33 +2164,30 @@
         <f aca="false">IF(AND(E60&lt;&gt;"",E59&lt;&gt;""),E60-E59,IF(E60&lt;&gt;"",E60,""))</f>
         <v>10</v>
       </c>
-      <c r="G60" s="26" t="n">
+      <c r="G60" s="24" t="n">
         <f aca="false">IF(F60&lt;&gt;"",F60*PI()*($C$9+$C$8),"")</f>
         <v>516.791991515521</v>
       </c>
-      <c r="H60" s="16" t="n">
+      <c r="H60" s="26" t="n">
         <f aca="false">IF(G60&lt;&gt;"",G60*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>56.0193580246914</v>
       </c>
-      <c r="I60" s="26" t="n">
+      <c r="I60" s="24" t="n">
         <f aca="false">IF(G60&lt;&gt;"",SUM(G59:G60),"")</f>
         <v>2583.9599575776</v>
       </c>
-      <c r="J60" s="18" t="str">
-        <f aca="false">H16</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="13" t="n">
+      <c r="J60" s="20"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C61" s="18" t="n">
+      <c r="C61" s="23" t="n">
         <f aca="false">C17</f>
         <v>18</v>
       </c>
-      <c r="D61" s="19" t="n">
-        <f aca="false">IF(I17&lt;&gt;"",I17,"")</f>
+      <c r="D61" s="28" t="n">
+        <f aca="false">IF(D80&lt;&gt;"",SQRT(D80/MAX($C$7,0.000000001)),"")</f>
         <v>3.02342784031985</v>
       </c>
       <c r="E61" s="11" t="n">
@@ -2381,33 +2198,30 @@
         <f aca="false">IF(AND(E61&lt;&gt;"",E60&lt;&gt;""),E61-E60,IF(E61&lt;&gt;"",E61,""))</f>
         <v>10</v>
       </c>
-      <c r="G61" s="26" t="n">
+      <c r="G61" s="24" t="n">
         <f aca="false">IF(F61&lt;&gt;"",F61*PI()*($C$9+$C$8),"")</f>
         <v>516.791991515521</v>
       </c>
-      <c r="H61" s="16" t="n">
+      <c r="H61" s="26" t="n">
         <f aca="false">IF(G61&lt;&gt;"",G61*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>56.0193580246914</v>
       </c>
-      <c r="I61" s="26" t="n">
+      <c r="I61" s="24" t="n">
         <f aca="false">IF(G61&lt;&gt;"",SUM(G59:G61),"")</f>
         <v>3100.75194909313</v>
       </c>
-      <c r="J61" s="18" t="str">
-        <f aca="false">H17</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="20" t="n">
+      <c r="J61" s="20"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="C62" s="18" t="n">
+      <c r="C62" s="23" t="n">
         <f aca="false">C18</f>
         <v>28</v>
       </c>
-      <c r="D62" s="19" t="n">
-        <f aca="false">IF(I18&lt;&gt;"",I18,"")</f>
+      <c r="D62" s="28" t="n">
+        <f aca="false">IF(D81&lt;&gt;"",SQRT(D81/MAX($C$7,0.000000001)),"")</f>
         <v>4</v>
       </c>
       <c r="E62" s="11" t="n">
@@ -2418,33 +2232,30 @@
         <f aca="false">IF(AND(E62&lt;&gt;"",E61&lt;&gt;""),E62-E61,IF(E62&lt;&gt;"",E62,""))</f>
         <v>20</v>
       </c>
-      <c r="G62" s="26" t="n">
+      <c r="G62" s="24" t="n">
         <f aca="false">IF(F62&lt;&gt;"",F62*PI()*($C$9+$C$8),"")</f>
         <v>1033.58398303104</v>
       </c>
-      <c r="H62" s="16" t="n">
+      <c r="H62" s="26" t="n">
         <f aca="false">IF(G62&lt;&gt;"",G62*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>112.038716049383</v>
       </c>
-      <c r="I62" s="26" t="n">
+      <c r="I62" s="24" t="n">
         <f aca="false">IF(G62&lt;&gt;"",SUM(G59:G62),"")</f>
         <v>4134.33593212417</v>
       </c>
-      <c r="J62" s="18" t="str">
-        <f aca="false">H18</f>
-        <v>YES</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="13" t="n">
+      <c r="J62" s="20"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C63" s="18" t="n">
+      <c r="C63" s="23" t="n">
         <f aca="false">C19</f>
         <v>0</v>
       </c>
-      <c r="D63" s="19" t="str">
-        <f aca="false">IF(I19&lt;&gt;"",I19,"")</f>
+      <c r="D63" s="28" t="str">
+        <f aca="false">IF(D82&lt;&gt;"",SQRT(D82/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
       <c r="E63" s="11" t="str">
@@ -2455,33 +2266,30 @@
         <f aca="false">IF(AND(E63&lt;&gt;"",E62&lt;&gt;""),E63-E62,IF(E63&lt;&gt;"",E63,""))</f>
         <v/>
       </c>
-      <c r="G63" s="26" t="str">
+      <c r="G63" s="24" t="str">
         <f aca="false">IF(F63&lt;&gt;"",F63*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H63" s="16" t="str">
+      <c r="H63" s="26" t="str">
         <f aca="false">IF(G63&lt;&gt;"",G63*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I63" s="26" t="str">
+      <c r="I63" s="24" t="str">
         <f aca="false">IF(G63&lt;&gt;"",SUM(G59:G63),"")</f>
         <v/>
       </c>
-      <c r="J63" s="18" t="str">
-        <f aca="false">H19</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="20" t="n">
+      <c r="J63" s="20"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="C64" s="18" t="n">
+      <c r="C64" s="23" t="n">
         <f aca="false">C20</f>
         <v>0</v>
       </c>
-      <c r="D64" s="19" t="str">
-        <f aca="false">IF(I20&lt;&gt;"",I20,"")</f>
+      <c r="D64" s="28" t="str">
+        <f aca="false">IF(D83&lt;&gt;"",SQRT(D83/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
       <c r="E64" s="11" t="str">
@@ -2492,33 +2300,30 @@
         <f aca="false">IF(AND(E64&lt;&gt;"",E63&lt;&gt;""),E64-E63,IF(E64&lt;&gt;"",E64,""))</f>
         <v/>
       </c>
-      <c r="G64" s="26" t="str">
+      <c r="G64" s="24" t="str">
         <f aca="false">IF(F64&lt;&gt;"",F64*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H64" s="16" t="str">
+      <c r="H64" s="26" t="str">
         <f aca="false">IF(G64&lt;&gt;"",G64*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I64" s="26" t="str">
+      <c r="I64" s="24" t="str">
         <f aca="false">IF(G64&lt;&gt;"",SUM(G59:G64),"")</f>
         <v/>
       </c>
-      <c r="J64" s="18" t="str">
-        <f aca="false">H20</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B65" s="13" t="n">
+      <c r="J64" s="20"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C65" s="18" t="n">
+      <c r="C65" s="23" t="n">
         <f aca="false">C21</f>
         <v>0</v>
       </c>
-      <c r="D65" s="19" t="str">
-        <f aca="false">IF(I21&lt;&gt;"",I21,"")</f>
+      <c r="D65" s="28" t="str">
+        <f aca="false">IF(D84&lt;&gt;"",SQRT(D84/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
       <c r="E65" s="11" t="str">
@@ -2529,33 +2334,30 @@
         <f aca="false">IF(AND(E65&lt;&gt;"",E64&lt;&gt;""),E65-E64,IF(E65&lt;&gt;"",E65,""))</f>
         <v/>
       </c>
-      <c r="G65" s="26" t="str">
+      <c r="G65" s="24" t="str">
         <f aca="false">IF(F65&lt;&gt;"",F65*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H65" s="16" t="str">
+      <c r="H65" s="26" t="str">
         <f aca="false">IF(G65&lt;&gt;"",G65*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I65" s="26" t="str">
+      <c r="I65" s="24" t="str">
         <f aca="false">IF(G65&lt;&gt;"",SUM(G59:G65),"")</f>
         <v/>
       </c>
-      <c r="J65" s="18" t="str">
-        <f aca="false">H21</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B66" s="20" t="n">
+      <c r="J65" s="20"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="C66" s="18" t="n">
+      <c r="C66" s="23" t="n">
         <f aca="false">C22</f>
         <v>0</v>
       </c>
-      <c r="D66" s="19" t="str">
-        <f aca="false">IF(I22&lt;&gt;"",I22,"")</f>
+      <c r="D66" s="28" t="str">
+        <f aca="false">IF(D85&lt;&gt;"",SQRT(D85/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
       <c r="E66" s="11" t="str">
@@ -2566,33 +2368,30 @@
         <f aca="false">IF(AND(E66&lt;&gt;"",E65&lt;&gt;""),E66-E65,IF(E66&lt;&gt;"",E66,""))</f>
         <v/>
       </c>
-      <c r="G66" s="26" t="str">
+      <c r="G66" s="24" t="str">
         <f aca="false">IF(F66&lt;&gt;"",F66*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H66" s="16" t="str">
+      <c r="H66" s="26" t="str">
         <f aca="false">IF(G66&lt;&gt;"",G66*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I66" s="26" t="str">
+      <c r="I66" s="24" t="str">
         <f aca="false">IF(G66&lt;&gt;"",SUM(G59:G66),"")</f>
         <v/>
       </c>
-      <c r="J66" s="18" t="str">
-        <f aca="false">H22</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B67" s="13" t="n">
+      <c r="J66" s="20"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C67" s="18" t="n">
+      <c r="C67" s="23" t="n">
         <f aca="false">C23</f>
         <v>0</v>
       </c>
-      <c r="D67" s="19" t="str">
-        <f aca="false">IF(I23&lt;&gt;"",I23,"")</f>
+      <c r="D67" s="28" t="str">
+        <f aca="false">IF(D86&lt;&gt;"",SQRT(D86/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
       <c r="E67" s="11" t="str">
@@ -2603,33 +2402,30 @@
         <f aca="false">IF(AND(E67&lt;&gt;"",E66&lt;&gt;""),E67-E66,IF(E67&lt;&gt;"",E67,""))</f>
         <v/>
       </c>
-      <c r="G67" s="26" t="str">
+      <c r="G67" s="24" t="str">
         <f aca="false">IF(F67&lt;&gt;"",F67*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H67" s="16" t="str">
+      <c r="H67" s="26" t="str">
         <f aca="false">IF(G67&lt;&gt;"",G67*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I67" s="26" t="str">
+      <c r="I67" s="24" t="str">
         <f aca="false">IF(G67&lt;&gt;"",SUM(G59:G67),"")</f>
         <v/>
       </c>
-      <c r="J67" s="18" t="str">
-        <f aca="false">H23</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B68" s="20" t="n">
+      <c r="J67" s="20"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="C68" s="18" t="n">
+      <c r="C68" s="23" t="n">
         <f aca="false">C24</f>
         <v>0</v>
       </c>
-      <c r="D68" s="19" t="str">
-        <f aca="false">IF(I24&lt;&gt;"",I24,"")</f>
+      <c r="D68" s="28" t="str">
+        <f aca="false">IF(D87&lt;&gt;"",SQRT(D87/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
       <c r="E68" s="11" t="str">
@@ -2640,33 +2436,30 @@
         <f aca="false">IF(AND(E68&lt;&gt;"",E67&lt;&gt;""),E68-E67,IF(E68&lt;&gt;"",E68,""))</f>
         <v/>
       </c>
-      <c r="G68" s="26" t="str">
+      <c r="G68" s="24" t="str">
         <f aca="false">IF(F68&lt;&gt;"",F68*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H68" s="16" t="str">
+      <c r="H68" s="26" t="str">
         <f aca="false">IF(G68&lt;&gt;"",G68*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I68" s="26" t="str">
+      <c r="I68" s="24" t="str">
         <f aca="false">IF(G68&lt;&gt;"",SUM(G59:G68),"")</f>
         <v/>
       </c>
-      <c r="J68" s="18" t="str">
-        <f aca="false">H24</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B69" s="13" t="n">
+      <c r="J68" s="20"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="C69" s="18" t="n">
+      <c r="C69" s="23" t="n">
         <f aca="false">C25</f>
         <v>0</v>
       </c>
-      <c r="D69" s="19" t="str">
-        <f aca="false">IF(I25&lt;&gt;"",I25,"")</f>
+      <c r="D69" s="28" t="str">
+        <f aca="false">IF(D88&lt;&gt;"",SQRT(D88/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
       <c r="E69" s="11" t="str">
@@ -2677,45 +2470,42 @@
         <f aca="false">IF(AND(E69&lt;&gt;"",E68&lt;&gt;""),E69-E68,IF(E69&lt;&gt;"",E69,""))</f>
         <v/>
       </c>
-      <c r="G69" s="26" t="str">
+      <c r="G69" s="24" t="str">
         <f aca="false">IF(F69&lt;&gt;"",F69*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H69" s="16" t="str">
+      <c r="H69" s="26" t="str">
         <f aca="false">IF(G69&lt;&gt;"",G69*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I69" s="26" t="str">
+      <c r="I69" s="24" t="str">
         <f aca="false">IF(G69&lt;&gt;"",SUM(G59:G69),"")</f>
         <v/>
       </c>
-      <c r="J69" s="18" t="str">
-        <f aca="false">H25</f>
-        <v>—</v>
-      </c>
+      <c r="J69" s="20"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B71" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C71" s="27"/>
-      <c r="D71" s="27"/>
+      <c r="B71" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="31"/>
+      <c r="D71" s="31"/>
       <c r="E71" s="11" t="n">
         <f aca="false">IFERROR(MAX(E59:E69),"")</f>
         <v>80</v>
       </c>
-      <c r="H71" s="28" t="n">
+      <c r="H71" s="32" t="n">
         <f aca="false">IFERROR(SUM(H59:H69),"")</f>
         <v>448.154864197531</v>
       </c>
-      <c r="I71" s="29" t="n">
+      <c r="I71" s="33" t="n">
         <f aca="false">IFERROR(MAX(I59:I69),"")</f>
         <v>4134.33593212417</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -2727,7 +2517,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
@@ -2739,7 +2529,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -2749,494 +2539,494 @@
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
     </row>
-    <row r="77" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="38.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D77" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H77" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E77" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F77" s="5" t="s">
+      <c r="I77" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G77" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I77" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B78" s="13" t="n">
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C78" s="18" t="n">
+      <c r="C78" s="23" t="n">
         <f aca="false">C15</f>
         <v>7.2</v>
       </c>
-      <c r="D78" s="16" t="n">
-        <f aca="false">F15</f>
+      <c r="D78" s="26" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D15),D15&gt;0),SQRT(D15^2+IF(ISNUMBER(E15),E15,0)^2),"")</f>
         <v>200</v>
       </c>
-      <c r="E78" s="25" t="n">
-        <f aca="false">G15</f>
-        <v>0</v>
-      </c>
-      <c r="F78" s="24" t="n">
-        <f aca="false">IF(F15&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2))),999),"")</f>
+      <c r="E78" s="27" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D15),D15&gt;0),IFERROR(DEGREES(ATAN2(D15,IF(ISNUMBER(E15),E15,0))),""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="29" t="n">
+        <f aca="false">IF(D78&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2))),999),"")</f>
         <v>1</v>
       </c>
-      <c r="G78" s="25" t="n">
-        <f aca="false">IF(F15&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+      <c r="G78" s="30" t="n">
+        <f aca="false">IF(D78&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>180</v>
       </c>
-      <c r="H78" s="24" t="n">
-        <f aca="false">IF(F15&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2))),0),"")</f>
+      <c r="H78" s="29" t="n">
+        <f aca="false">IF(D78&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2))),0),"")</f>
         <v>-0</v>
       </c>
-      <c r="I78" s="24" t="n">
-        <f aca="false">IF(F15&lt;&gt;"",IFERROR(((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((F15/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((F15/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B79" s="20" t="n">
+      <c r="I78" s="29" t="n">
+        <f aca="false">IF(D78&lt;&gt;"",IFERROR(((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="C79" s="18" t="n">
+      <c r="C79" s="23" t="n">
         <f aca="false">C16</f>
         <v>10</v>
       </c>
-      <c r="D79" s="16" t="n">
-        <f aca="false">F16</f>
+      <c r="D79" s="26" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D16),D16&gt;0),SQRT(D16^2+IF(ISNUMBER(E16),E16,0)^2),"")</f>
         <v>316.227766016838</v>
       </c>
-      <c r="E79" s="25" t="n">
-        <f aca="false">G16</f>
+      <c r="E79" s="27" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D16),D16&gt;0),IFERROR(DEGREES(ATAN2(D16,IF(ISNUMBER(E16),E16,0))),""),"")</f>
         <v>18.434948822922</v>
       </c>
-      <c r="F79" s="24" t="n">
-        <f aca="false">IF(F16&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2))),999),"")</f>
+      <c r="F79" s="29" t="n">
+        <f aca="false">IF(D79&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2))),999),"")</f>
         <v>1.38742588672279</v>
       </c>
-      <c r="G79" s="25" t="n">
-        <f aca="false">IF(F16&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+      <c r="G79" s="30" t="n">
+        <f aca="false">IF(D79&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>15.7948252576199</v>
       </c>
-      <c r="H79" s="24" t="n">
-        <f aca="false">IF(F16&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2))),0),"")</f>
+      <c r="H79" s="29" t="n">
+        <f aca="false">IF(D79&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2))),0),"")</f>
         <v>0.115900124973496</v>
       </c>
-      <c r="I79" s="24" t="n">
-        <f aca="false">IF(F16&lt;&gt;"",IFERROR(((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((F16/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((F16/C7),0.000000001),0))^2)*100,0),"")</f>
+      <c r="I79" s="29" t="n">
+        <f aca="false">IF(D79&lt;&gt;"",IFERROR(((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)*100,0),"")</f>
         <v>2.6334038989724</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B80" s="13" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C80" s="18" t="n">
+      <c r="C80" s="23" t="n">
         <f aca="false">C17</f>
         <v>18</v>
       </c>
-      <c r="D80" s="16" t="n">
-        <f aca="false">F17</f>
+      <c r="D80" s="26" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D17),D17&gt;0),SQRT(D17^2+IF(ISNUMBER(E17),E17,0)^2),"")</f>
         <v>457.055795281058</v>
       </c>
-      <c r="E80" s="25" t="n">
-        <f aca="false">G17</f>
+      <c r="E80" s="27" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D17),D17&gt;0),IFERROR(DEGREES(ATAN2(D17,IF(ISNUMBER(E17),E17,0))),""),"")</f>
         <v>-10.0805979875423</v>
       </c>
-      <c r="F80" s="24" t="n">
-        <f aca="false">IF(F17&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2))),999),"")</f>
+      <c r="F80" s="29" t="n">
+        <f aca="false">IF(D80&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2))),999),"")</f>
         <v>1.19345732284679</v>
       </c>
-      <c r="G80" s="25" t="n">
-        <f aca="false">IF(F17&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+      <c r="G80" s="30" t="n">
+        <f aca="false">IF(D80&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>21.0908803086925</v>
       </c>
-      <c r="H80" s="24" t="n">
-        <f aca="false">IF(F17&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2))),0),"")</f>
+      <c r="H80" s="29" t="n">
+        <f aca="false">IF(D80&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2))),0),"")</f>
         <v>0.0339149298724391</v>
       </c>
-      <c r="I80" s="24" t="n">
-        <f aca="false">IF(F17&lt;&gt;"",IFERROR(((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((F17/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((F17/C7),0.000000001),0))^2)*100,0),"")</f>
+      <c r="I80" s="29" t="n">
+        <f aca="false">IF(D80&lt;&gt;"",IFERROR(((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)*100,0),"")</f>
         <v>0.777878860128034</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B81" s="20" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="C81" s="18" t="n">
+      <c r="C81" s="23" t="n">
         <f aca="false">C18</f>
         <v>28</v>
       </c>
-      <c r="D81" s="16" t="n">
-        <f aca="false">F18</f>
+      <c r="D81" s="26" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D18),D18&gt;0),SQRT(D18^2+IF(ISNUMBER(E18),E18,0)^2),"")</f>
         <v>800</v>
       </c>
-      <c r="E81" s="25" t="n">
-        <f aca="false">G18</f>
-        <v>0</v>
-      </c>
-      <c r="F81" s="24" t="n">
-        <f aca="false">IF(F18&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2))),999),"")</f>
+      <c r="E81" s="27" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D18),D18&gt;0),IFERROR(DEGREES(ATAN2(D18,IF(ISNUMBER(E18),E18,0))),""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="F81" s="29" t="n">
+        <f aca="false">IF(D81&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2))),999),"")</f>
         <v>1</v>
       </c>
-      <c r="G81" s="25" t="n">
-        <f aca="false">IF(F18&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+      <c r="G81" s="30" t="n">
+        <f aca="false">IF(D81&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>180</v>
       </c>
-      <c r="H81" s="24" t="n">
-        <f aca="false">IF(F18&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2))),0),"")</f>
+      <c r="H81" s="29" t="n">
+        <f aca="false">IF(D81&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2))),0),"")</f>
         <v>-0</v>
       </c>
-      <c r="I81" s="24" t="n">
-        <f aca="false">IF(F18&lt;&gt;"",IFERROR(((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((F18/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((F18/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B82" s="13" t="n">
+      <c r="I81" s="29" t="n">
+        <f aca="false">IF(D81&lt;&gt;"",IFERROR(((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C82" s="18" t="n">
+      <c r="C82" s="23" t="n">
         <f aca="false">C19</f>
         <v>0</v>
       </c>
-      <c r="D82" s="16" t="str">
-        <f aca="false">F19</f>
-        <v/>
-      </c>
-      <c r="E82" s="25" t="str">
-        <f aca="false">G19</f>
-        <v/>
-      </c>
-      <c r="F82" s="24" t="str">
-        <f aca="false">IF(F19&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G82" s="25" t="str">
-        <f aca="false">IF(F19&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H82" s="24" t="str">
-        <f aca="false">IF(F19&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I82" s="24" t="str">
-        <f aca="false">IF(F19&lt;&gt;"",IFERROR(((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((F19/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((F19/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B83" s="20" t="n">
+      <c r="D82" s="26" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D19),D19&gt;0),SQRT(D19^2+IF(ISNUMBER(E19),E19,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="27" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D19),D19&gt;0),IFERROR(DEGREES(ATAN2(D19,IF(ISNUMBER(E19),E19,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="29" t="str">
+        <f aca="false">IF(D82&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G82" s="30" t="str">
+        <f aca="false">IF(D82&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H82" s="29" t="str">
+        <f aca="false">IF(D82&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I82" s="29" t="str">
+        <f aca="false">IF(D82&lt;&gt;"",IFERROR(((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="C83" s="18" t="n">
+      <c r="C83" s="23" t="n">
         <f aca="false">C20</f>
         <v>0</v>
       </c>
-      <c r="D83" s="16" t="str">
-        <f aca="false">F20</f>
-        <v/>
-      </c>
-      <c r="E83" s="25" t="str">
-        <f aca="false">G20</f>
-        <v/>
-      </c>
-      <c r="F83" s="24" t="str">
-        <f aca="false">IF(F20&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G83" s="25" t="str">
-        <f aca="false">IF(F20&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H83" s="24" t="str">
-        <f aca="false">IF(F20&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I83" s="24" t="str">
-        <f aca="false">IF(F20&lt;&gt;"",IFERROR(((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((F20/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((F20/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B84" s="13" t="n">
+      <c r="D83" s="26" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D20),D20&gt;0),SQRT(D20^2+IF(ISNUMBER(E20),E20,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="27" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D20),D20&gt;0),IFERROR(DEGREES(ATAN2(D20,IF(ISNUMBER(E20),E20,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="29" t="str">
+        <f aca="false">IF(D83&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G83" s="30" t="str">
+        <f aca="false">IF(D83&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H83" s="29" t="str">
+        <f aca="false">IF(D83&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I83" s="29" t="str">
+        <f aca="false">IF(D83&lt;&gt;"",IFERROR(((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="C84" s="18" t="n">
+      <c r="C84" s="23" t="n">
         <f aca="false">C21</f>
         <v>0</v>
       </c>
-      <c r="D84" s="16" t="str">
-        <f aca="false">F21</f>
-        <v/>
-      </c>
-      <c r="E84" s="25" t="str">
-        <f aca="false">G21</f>
-        <v/>
-      </c>
-      <c r="F84" s="24" t="str">
-        <f aca="false">IF(F21&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G84" s="25" t="str">
-        <f aca="false">IF(F21&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H84" s="24" t="str">
-        <f aca="false">IF(F21&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I84" s="24" t="str">
-        <f aca="false">IF(F21&lt;&gt;"",IFERROR(((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((F21/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((F21/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B85" s="20" t="n">
+      <c r="D84" s="26" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D21),D21&gt;0),SQRT(D21^2+IF(ISNUMBER(E21),E21,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="27" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D21),D21&gt;0),IFERROR(DEGREES(ATAN2(D21,IF(ISNUMBER(E21),E21,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="29" t="str">
+        <f aca="false">IF(D84&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G84" s="30" t="str">
+        <f aca="false">IF(D84&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H84" s="29" t="str">
+        <f aca="false">IF(D84&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I84" s="29" t="str">
+        <f aca="false">IF(D84&lt;&gt;"",IFERROR(((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="C85" s="18" t="n">
+      <c r="C85" s="23" t="n">
         <f aca="false">C22</f>
         <v>0</v>
       </c>
-      <c r="D85" s="16" t="str">
-        <f aca="false">F22</f>
-        <v/>
-      </c>
-      <c r="E85" s="25" t="str">
-        <f aca="false">G22</f>
-        <v/>
-      </c>
-      <c r="F85" s="24" t="str">
-        <f aca="false">IF(F22&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G85" s="25" t="str">
-        <f aca="false">IF(F22&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H85" s="24" t="str">
-        <f aca="false">IF(F22&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I85" s="24" t="str">
-        <f aca="false">IF(F22&lt;&gt;"",IFERROR(((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((F22/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((F22/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B86" s="13" t="n">
+      <c r="D85" s="26" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D22),D22&gt;0),SQRT(D22^2+IF(ISNUMBER(E22),E22,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="27" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D22),D22&gt;0),IFERROR(DEGREES(ATAN2(D22,IF(ISNUMBER(E22),E22,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="29" t="str">
+        <f aca="false">IF(D85&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G85" s="30" t="str">
+        <f aca="false">IF(D85&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H85" s="29" t="str">
+        <f aca="false">IF(D85&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I85" s="29" t="str">
+        <f aca="false">IF(D85&lt;&gt;"",IFERROR(((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="C86" s="18" t="n">
+      <c r="C86" s="23" t="n">
         <f aca="false">C23</f>
         <v>0</v>
       </c>
-      <c r="D86" s="16" t="str">
-        <f aca="false">F23</f>
-        <v/>
-      </c>
-      <c r="E86" s="25" t="str">
-        <f aca="false">G23</f>
-        <v/>
-      </c>
-      <c r="F86" s="24" t="str">
-        <f aca="false">IF(F23&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G86" s="25" t="str">
-        <f aca="false">IF(F23&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H86" s="24" t="str">
-        <f aca="false">IF(F23&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I86" s="24" t="str">
-        <f aca="false">IF(F23&lt;&gt;"",IFERROR(((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((F23/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((F23/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B87" s="20" t="n">
+      <c r="D86" s="26" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D23),D23&gt;0),SQRT(D23^2+IF(ISNUMBER(E23),E23,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="27" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D23),D23&gt;0),IFERROR(DEGREES(ATAN2(D23,IF(ISNUMBER(E23),E23,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="29" t="str">
+        <f aca="false">IF(D86&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G86" s="30" t="str">
+        <f aca="false">IF(D86&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H86" s="29" t="str">
+        <f aca="false">IF(D86&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I86" s="29" t="str">
+        <f aca="false">IF(D86&lt;&gt;"",IFERROR(((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="C87" s="18" t="n">
+      <c r="C87" s="23" t="n">
         <f aca="false">C24</f>
         <v>0</v>
       </c>
-      <c r="D87" s="16" t="str">
-        <f aca="false">F24</f>
-        <v/>
-      </c>
-      <c r="E87" s="25" t="str">
-        <f aca="false">G24</f>
-        <v/>
-      </c>
-      <c r="F87" s="24" t="str">
-        <f aca="false">IF(F24&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G87" s="25" t="str">
-        <f aca="false">IF(F24&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H87" s="24" t="str">
-        <f aca="false">IF(F24&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I87" s="24" t="str">
-        <f aca="false">IF(F24&lt;&gt;"",IFERROR(((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((F24/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((F24/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B88" s="13" t="n">
+      <c r="D87" s="26" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D24),D24&gt;0),SQRT(D24^2+IF(ISNUMBER(E24),E24,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="27" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D24),D24&gt;0),IFERROR(DEGREES(ATAN2(D24,IF(ISNUMBER(E24),E24,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="29" t="str">
+        <f aca="false">IF(D87&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G87" s="30" t="str">
+        <f aca="false">IF(D87&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H87" s="29" t="str">
+        <f aca="false">IF(D87&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I87" s="29" t="str">
+        <f aca="false">IF(D87&lt;&gt;"",IFERROR(((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="C88" s="18" t="n">
+      <c r="C88" s="23" t="n">
         <f aca="false">C25</f>
         <v>0</v>
       </c>
-      <c r="D88" s="16" t="str">
-        <f aca="false">F25</f>
-        <v/>
-      </c>
-      <c r="E88" s="25" t="str">
-        <f aca="false">G25</f>
-        <v/>
-      </c>
-      <c r="F88" s="24" t="str">
-        <f aca="false">IF(F25&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G88" s="25" t="str">
-        <f aca="false">IF(F25&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H88" s="24" t="str">
-        <f aca="false">IF(F25&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I88" s="24" t="str">
-        <f aca="false">IF(F25&lt;&gt;"",IFERROR(((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((F25/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((F25/C7),0.000000001),0))^2)*100,0),"")</f>
+      <c r="D88" s="26" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D25),D25&gt;0),SQRT(D25^2+IF(ISNUMBER(E25),E25,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E88" s="27" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D25),D25&gt;0),IFERROR(DEGREES(ATAN2(D25,IF(ISNUMBER(E25),E25,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="29" t="str">
+        <f aca="false">IF(D88&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G88" s="30" t="str">
+        <f aca="false">IF(D88&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H88" s="29" t="str">
+        <f aca="false">IF(D88&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I88" s="29" t="str">
+        <f aca="false">IF(D88&lt;&gt;"",IFERROR(((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)*100,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B90" s="30" t="s">
+      <c r="B90" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C90" s="34"/>
+      <c r="D90" s="34"/>
+      <c r="E90" s="34"/>
+      <c r="F90" s="34"/>
+      <c r="G90" s="34"/>
+      <c r="H90" s="34"/>
+      <c r="I90" s="34"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B91" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C91" s="35"/>
+      <c r="D91" s="35"/>
+      <c r="E91" s="35"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="35"/>
+      <c r="H91" s="35"/>
+      <c r="I91" s="35"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B92" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C92" s="35"/>
+      <c r="D92" s="35"/>
+      <c r="E92" s="35"/>
+      <c r="F92" s="35"/>
+      <c r="G92" s="35"/>
+      <c r="H92" s="35"/>
+      <c r="I92" s="35"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B93" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="C90" s="30"/>
-      <c r="D90" s="30"/>
-      <c r="E90" s="30"/>
-      <c r="F90" s="30"/>
-      <c r="G90" s="30"/>
-      <c r="H90" s="30"/>
-      <c r="I90" s="30"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B91" s="31" t="s">
+      <c r="C93" s="35"/>
+      <c r="D93" s="35"/>
+      <c r="E93" s="35"/>
+      <c r="F93" s="35"/>
+      <c r="G93" s="35"/>
+      <c r="H93" s="35"/>
+      <c r="I93" s="35"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B94" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="C91" s="31"/>
-      <c r="D91" s="31"/>
-      <c r="E91" s="31"/>
-      <c r="F91" s="31"/>
-      <c r="G91" s="31"/>
-      <c r="H91" s="31"/>
-      <c r="I91" s="31"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B92" s="31" t="s">
+      <c r="C94" s="35"/>
+      <c r="D94" s="35"/>
+      <c r="E94" s="35"/>
+      <c r="F94" s="35"/>
+      <c r="G94" s="35"/>
+      <c r="H94" s="35"/>
+      <c r="I94" s="35"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B95" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="C92" s="31"/>
-      <c r="D92" s="31"/>
-      <c r="E92" s="31"/>
-      <c r="F92" s="31"/>
-      <c r="G92" s="31"/>
-      <c r="H92" s="31"/>
-      <c r="I92" s="31"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B93" s="31" t="s">
+      <c r="C95" s="35"/>
+      <c r="D95" s="35"/>
+      <c r="E95" s="35"/>
+      <c r="F95" s="35"/>
+      <c r="G95" s="35"/>
+      <c r="H95" s="35"/>
+      <c r="I95" s="35"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B96" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C93" s="31"/>
-      <c r="D93" s="31"/>
-      <c r="E93" s="31"/>
-      <c r="F93" s="31"/>
-      <c r="G93" s="31"/>
-      <c r="H93" s="31"/>
-      <c r="I93" s="31"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B94" s="31" t="s">
+      <c r="C96" s="35"/>
+      <c r="D96" s="35"/>
+      <c r="E96" s="35"/>
+      <c r="F96" s="35"/>
+      <c r="G96" s="35"/>
+      <c r="H96" s="35"/>
+      <c r="I96" s="35"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B97" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="C94" s="31"/>
-      <c r="D94" s="31"/>
-      <c r="E94" s="31"/>
-      <c r="F94" s="31"/>
-      <c r="G94" s="31"/>
-      <c r="H94" s="31"/>
-      <c r="I94" s="31"/>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B95" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="C95" s="31"/>
-      <c r="D95" s="31"/>
-      <c r="E95" s="31"/>
-      <c r="F95" s="31"/>
-      <c r="G95" s="31"/>
-      <c r="H95" s="31"/>
-      <c r="I95" s="31"/>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B96" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="C96" s="31"/>
-      <c r="D96" s="31"/>
-      <c r="E96" s="31"/>
-      <c r="F96" s="31"/>
-      <c r="G96" s="31"/>
-      <c r="H96" s="31"/>
-      <c r="I96" s="31"/>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B97" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="C97" s="31"/>
-      <c r="D97" s="31"/>
-      <c r="E97" s="31"/>
-      <c r="F97" s="31"/>
-      <c r="G97" s="31"/>
-      <c r="H97" s="31"/>
-      <c r="I97" s="31"/>
+      <c r="C97" s="35"/>
+      <c r="D97" s="35"/>
+      <c r="E97" s="35"/>
+      <c r="F97" s="35"/>
+      <c r="G97" s="35"/>
+      <c r="H97" s="35"/>
+      <c r="I97" s="35"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -3246,7 +3036,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B100" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
@@ -3256,7 +3046,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -3275,16 +3065,16 @@
         <v>5</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C104" s="32" t="n">
+        <v>78</v>
+      </c>
+      <c r="C104" s="36" t="n">
         <f aca="false">C9</f>
         <v>16</v>
       </c>
@@ -3292,16 +3082,16 @@
         <v>11</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F104" s="9"/>
       <c r="G104" s="9"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B105" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C105" s="32" t="n">
+        <v>80</v>
+      </c>
+      <c r="C105" s="36" t="n">
         <f aca="false">C8</f>
         <v>0.45</v>
       </c>
@@ -3309,16 +3099,16 @@
         <v>11</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F105" s="9"/>
       <c r="G105" s="9"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C106" s="32" t="n">
+        <v>82</v>
+      </c>
+      <c r="C106" s="36" t="n">
         <f aca="false">MAX(C8*1.1,C8+0.05)</f>
         <v>0.5</v>
       </c>
@@ -3326,31 +3116,31 @@
         <v>11</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F106" s="9"/>
       <c r="G106" s="9"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C107" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="C107" s="23" t="n">
         <f aca="false">IFERROR(IF(E71&lt;&gt;"",VALUE(E71),10),10)</f>
         <v>80</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F107" s="9"/>
       <c r="G107" s="9"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B109" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -3369,16 +3159,16 @@
         <v>5</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F110" s="5"/>
       <c r="G110" s="5"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C111" s="33" t="n">
+        <v>88</v>
+      </c>
+      <c r="C111" s="25" t="n">
         <f aca="false">IFERROR(IF(C107&gt;0,(C107-1)*C106+C105,""),"")</f>
         <v>39.95</v>
       </c>
@@ -3386,16 +3176,16 @@
         <v>11</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F111" s="9"/>
       <c r="G111" s="9"/>
     </row>
-    <row r="112" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C112" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="C112" s="25" t="n">
         <f aca="false">(C104+C105)/2</f>
         <v>8.225</v>
       </c>
@@ -3403,67 +3193,67 @@
         <v>11</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F112" s="9"/>
       <c r="G112" s="9"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B113" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C113" s="33" t="n">
+        <v>92</v>
+      </c>
+      <c r="C113" s="25" t="n">
         <f aca="false">((C104+C105)/2)/25.4</f>
         <v>0.323818897637795</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F113" s="9"/>
       <c r="G113" s="9"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B114" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C114" s="33" t="n">
+        <v>95</v>
+      </c>
+      <c r="C114" s="25" t="n">
         <f aca="false">IFERROR(C111/25.4,"")</f>
         <v>1.57283464566929</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F114" s="9"/>
       <c r="G114" s="9"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B115" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C115" s="33" t="n">
+        <v>96</v>
+      </c>
+      <c r="C115" s="25" t="n">
         <f aca="false">IFERROR((C113^2*C107^2)/(9*C113+10*C114),"")</f>
         <v>35.9977335339286</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F115" s="9"/>
       <c r="G115" s="9"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B116" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C116" s="33" t="n">
+        <v>98</v>
+      </c>
+      <c r="C116" s="25" t="n">
         <f aca="false">IFERROR(2*PI()*C32*1000000*C115/1000000,"")</f>
         <v>1628.49909911145</v>
       </c>
@@ -3471,711 +3261,688 @@
         <v>8</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F116" s="9"/>
       <c r="G116" s="9"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B117" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C117" s="33" t="n">
-        <f aca="false">IFERROR(4*MIN(F15:F25)/(2*PI()*C32*1000000)*1000000,"")</f>
+        <v>100</v>
+      </c>
+      <c r="C117" s="25" t="n">
+        <f aca="false">IFERROR(4*MIN(D78:D88)/(2*PI()*C32*1000000)*1000000,"")</f>
         <v>17.6838825657662</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F117" s="9"/>
       <c r="G117" s="9"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B118" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C118" s="33" t="str">
+        <v>102</v>
+      </c>
+      <c r="C118" s="25" t="str">
         <f aca="false">IFERROR(IF(AND(ISNUMBER(C115),ISNUMBER(C117)),IF(C115&gt;=C117,"✔ YES","✘ INCREASE TURNS"),"—"),"")</f>
         <v>✔ YES</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F118" s="9"/>
       <c r="G118" s="9"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="34" t="s">
+      <c r="B121" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="C121" s="37"/>
+      <c r="D121" s="37"/>
+      <c r="E121" s="37"/>
+      <c r="F121" s="37"/>
+      <c r="G121" s="37"/>
+      <c r="H121" s="37"/>
+      <c r="I121" s="37"/>
+      <c r="J121" s="37"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C122" s="38"/>
+      <c r="D122" s="38"/>
+      <c r="E122" s="38"/>
+      <c r="F122" s="38"/>
+      <c r="G122" s="38"/>
+      <c r="H122" s="38"/>
+      <c r="I122" s="38"/>
+      <c r="J122" s="38"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C124" s="39"/>
+      <c r="D124" s="39"/>
+      <c r="E124" s="39"/>
+      <c r="F124" s="39"/>
+      <c r="G124" s="39"/>
+      <c r="H124" s="39"/>
+      <c r="I124" s="39"/>
+      <c r="J124" s="39"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="C121" s="34"/>
-      <c r="D121" s="34"/>
-      <c r="E121" s="34"/>
-      <c r="F121" s="34"/>
-      <c r="G121" s="34"/>
-      <c r="H121" s="34"/>
-      <c r="I121" s="34"/>
-      <c r="J121" s="34"/>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="35" t="s">
+      <c r="C125" s="40"/>
+      <c r="D125" s="40"/>
+      <c r="E125" s="40"/>
+      <c r="F125" s="40"/>
+      <c r="G125" s="40"/>
+      <c r="H125" s="40"/>
+      <c r="I125" s="40"/>
+      <c r="J125" s="40"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="C122" s="35"/>
-      <c r="D122" s="35"/>
-      <c r="E122" s="35"/>
-      <c r="F122" s="35"/>
-      <c r="G122" s="35"/>
-      <c r="H122" s="35"/>
-      <c r="I122" s="35"/>
-      <c r="J122" s="35"/>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="36" t="s">
+      <c r="C126" s="40"/>
+      <c r="D126" s="40"/>
+      <c r="E126" s="40"/>
+      <c r="F126" s="40"/>
+      <c r="G126" s="40"/>
+      <c r="H126" s="40"/>
+      <c r="I126" s="40"/>
+      <c r="J126" s="40"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="C124" s="36"/>
-      <c r="D124" s="36"/>
-      <c r="E124" s="36"/>
-      <c r="F124" s="36"/>
-      <c r="G124" s="36"/>
-      <c r="H124" s="36"/>
-      <c r="I124" s="36"/>
-      <c r="J124" s="36"/>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="37" t="s">
+      <c r="C127" s="40"/>
+      <c r="D127" s="40"/>
+      <c r="E127" s="40"/>
+      <c r="F127" s="40"/>
+      <c r="G127" s="40"/>
+      <c r="H127" s="40"/>
+      <c r="I127" s="40"/>
+      <c r="J127" s="40"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B128" s="40" t="s">
         <v>111</v>
       </c>
-      <c r="C125" s="37"/>
-      <c r="D125" s="37"/>
-      <c r="E125" s="37"/>
-      <c r="F125" s="37"/>
-      <c r="G125" s="37"/>
-      <c r="H125" s="37"/>
-      <c r="I125" s="37"/>
-      <c r="J125" s="37"/>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="37" t="s">
+      <c r="C128" s="40"/>
+      <c r="D128" s="40"/>
+      <c r="E128" s="40"/>
+      <c r="F128" s="40"/>
+      <c r="G128" s="40"/>
+      <c r="H128" s="40"/>
+      <c r="I128" s="40"/>
+      <c r="J128" s="40"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="C126" s="37"/>
-      <c r="D126" s="37"/>
-      <c r="E126" s="37"/>
-      <c r="F126" s="37"/>
-      <c r="G126" s="37"/>
-      <c r="H126" s="37"/>
-      <c r="I126" s="37"/>
-      <c r="J126" s="37"/>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B127" s="37" t="s">
+      <c r="C129" s="40"/>
+      <c r="D129" s="40"/>
+      <c r="E129" s="40"/>
+      <c r="F129" s="40"/>
+      <c r="G129" s="40"/>
+      <c r="H129" s="40"/>
+      <c r="I129" s="40"/>
+      <c r="J129" s="40"/>
+    </row>
+    <row r="131" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C131" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="C127" s="37"/>
-      <c r="D127" s="37"/>
-      <c r="E127" s="37"/>
-      <c r="F127" s="37"/>
-      <c r="G127" s="37"/>
-      <c r="H127" s="37"/>
-      <c r="I127" s="37"/>
-      <c r="J127" s="37"/>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="37" t="s">
+      <c r="D131" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="C128" s="37"/>
-      <c r="D128" s="37"/>
-      <c r="E128" s="37"/>
-      <c r="F128" s="37"/>
-      <c r="G128" s="37"/>
-      <c r="H128" s="37"/>
-      <c r="I128" s="37"/>
-      <c r="J128" s="37"/>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B129" s="37" t="s">
+      <c r="E131" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="C129" s="37"/>
-      <c r="D129" s="37"/>
-      <c r="E129" s="37"/>
-      <c r="F129" s="37"/>
-      <c r="G129" s="37"/>
-      <c r="H129" s="37"/>
-      <c r="I129" s="37"/>
-      <c r="J129" s="37"/>
-    </row>
-    <row r="131" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="C131" s="38" t="s">
+      <c r="F131" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="D131" s="38" t="s">
+      <c r="G131" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="E131" s="38" t="s">
+      <c r="H131" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="F131" s="38" t="s">
+      <c r="I131" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="G131" s="38" t="s">
+      <c r="J131" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="H131" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="I131" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="J131" s="38" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B132" s="39" t="n">
+      <c r="B132" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="C132" s="40" t="n">
+      <c r="C132" s="43" t="n">
         <f aca="false">C15</f>
         <v>7.2</v>
       </c>
-      <c r="D132" s="40" t="n">
+      <c r="D132" s="43" t="n">
         <f aca="false">D15</f>
         <v>200</v>
       </c>
-      <c r="E132" s="40" t="n">
+      <c r="E132" s="43" t="n">
         <f aca="false">IF(ISNUMBER(E15),E15,"—")</f>
         <v>0</v>
       </c>
-      <c r="F132" s="40" t="n">
-        <f aca="false">IF(ISNUMBER(G15),G15,"—")</f>
-        <v>0</v>
-      </c>
-      <c r="G132" s="41" t="str">
-        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(F15),F15&gt;0,ISNUMBER(D15),D15&gt;0),IF(($C$7*IF(ISNUMBER(E15),E15,0)/F15)&gt;0,($C$7*IF(ISNUMBER(E15),E15,0)/F15)/(2*PI()*C15*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H132" s="40" t="str">
-        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(F15),F15&gt;0,ISNUMBER(D15),D15&gt;0),IF(($C$7*IF(ISNUMBER(E15),E15,0)/F15)&lt;0,1/((2*PI()*C15*1000000)*ABS(($C$7*IF(ISNUMBER(E15),E15,0)/F15)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I132" s="41" t="str">
-        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(F15),F15&gt;0,ISNUMBER(D15),D15&gt;0),IF((F15*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))&lt;0,-1/((2*PI()*C15*1000000)*(F15*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J132" s="40" t="str">
-        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(F15),F15&gt;0,ISNUMBER(D15),D15&gt;0),IF((F15*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))&gt;0,(F15*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))/(2*PI()*C15*1000000)*1000000000000,"—"),"—"),"—")</f>
+      <c r="F132" s="43" t="n">
+        <f aca="false">IF(ISNUMBER(E78),E78,"—")</f>
+        <v>0</v>
+      </c>
+      <c r="G132" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D15),D15&gt;0),IF(($C$7*IF(ISNUMBER(E15),E15,0)/D78)&gt;0,($C$7*IF(ISNUMBER(E15),E15,0)/D78)/(2*PI()*C15*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H132" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D15),D15&gt;0),IF(($C$7*IF(ISNUMBER(E15),E15,0)/D78)&lt;0,1/((2*PI()*C15*1000000)*ABS(($C$7*IF(ISNUMBER(E15),E15,0)/D78)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I132" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D15),D15&gt;0),IF((D78*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))&lt;0,-1/((2*PI()*C15*1000000)*(D78*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J132" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D15),D15&gt;0),IF((D78*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))&gt;0,(D78*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))/(2*PI()*C15*1000000)*1000000000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B133" s="42" t="n">
+      <c r="B133" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="C133" s="43" t="n">
+      <c r="C133" s="46" t="n">
         <f aca="false">C16</f>
         <v>10</v>
       </c>
-      <c r="D133" s="43" t="n">
+      <c r="D133" s="46" t="n">
         <f aca="false">D16</f>
         <v>300</v>
       </c>
-      <c r="E133" s="43" t="n">
+      <c r="E133" s="46" t="n">
         <f aca="false">IF(ISNUMBER(E16),E16,"—")</f>
         <v>100</v>
       </c>
-      <c r="F133" s="43" t="n">
-        <f aca="false">IF(ISNUMBER(G16),G16,"—")</f>
+      <c r="F133" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(E79),E79,"—")</f>
         <v>18.434948822922</v>
       </c>
-      <c r="G133" s="44" t="n">
-        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(F16),F16&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$7*IF(ISNUMBER(E16),E16,0)/F16)&gt;0,($C$7*IF(ISNUMBER(E16),E16,0)/F16)/(2*PI()*C16*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>0.251646060522435</v>
-      </c>
-      <c r="H133" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(F16),F16&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$7*IF(ISNUMBER(E16),E16,0)/F16)&lt;0,1/((2*PI()*C16*1000000)*ABS(($C$7*IF(ISNUMBER(E16),E16,0)/F16)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I133" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(F16),F16&gt;0,ISNUMBER(D16),D16&gt;0),IF((F16*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&lt;0,-1/((2*PI()*C16*1000000)*(F16*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J133" s="43" t="n">
-        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(F16),F16&gt;0,ISNUMBER(D16),D16&gt;0),IF((F16*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&gt;0,(F16*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))/(2*PI()*C16*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>100.658424208974</v>
+      <c r="G133" s="47" t="str">
+        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$7*IF(ISNUMBER(E16),E16,0)/D79)&gt;0,($C$7*IF(ISNUMBER(E16),E16,0)/D79)/(2*PI()*C16*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H133" s="46" t="str">
+        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$7*IF(ISNUMBER(E16),E16,0)/D79)&lt;0,1/((2*PI()*C16*1000000)*ABS(($C$7*IF(ISNUMBER(E16),E16,0)/D79)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I133" s="47" t="str">
+        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D16),D16&gt;0),IF((D79*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&lt;0,-1/((2*PI()*C16*1000000)*(D79*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J133" s="46" t="str">
+        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D16),D16&gt;0),IF((D79*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&gt;0,(D79*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))/(2*PI()*C16*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="39" t="n">
+      <c r="B134" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C134" s="40" t="n">
+      <c r="C134" s="43" t="n">
         <f aca="false">C17</f>
         <v>18</v>
       </c>
-      <c r="D134" s="40" t="n">
+      <c r="D134" s="43" t="n">
         <f aca="false">D17</f>
         <v>450</v>
       </c>
-      <c r="E134" s="40" t="n">
+      <c r="E134" s="43" t="n">
         <f aca="false">IF(ISNUMBER(E17),E17,"—")</f>
         <v>-80</v>
       </c>
-      <c r="F134" s="40" t="n">
-        <f aca="false">IF(ISNUMBER(G17),G17,"—")</f>
+      <c r="F134" s="43" t="n">
+        <f aca="false">IF(ISNUMBER(E80),E80,"—")</f>
         <v>-10.0805979875423</v>
       </c>
-      <c r="G134" s="41" t="str">
-        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(F17),F17&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$7*IF(ISNUMBER(E17),E17,0)/F17)&gt;0,($C$7*IF(ISNUMBER(E17),E17,0)/F17)/(2*PI()*C17*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H134" s="40" t="n">
-        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(F17),F17&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$7*IF(ISNUMBER(E17),E17,0)/F17)&lt;0,1/((2*PI()*C17*1000000)*ABS(($C$7*IF(ISNUMBER(E17),E17,0)/F17)))*1000000000000,"—"),"—"),"—")</f>
-        <v>1010.31512621913</v>
-      </c>
-      <c r="I134" s="41" t="n">
-        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(F17),F17&gt;0,ISNUMBER(D17),D17&gt;0),IF((F17*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&lt;0,-1/((2*PI()*C17*1000000)*(F17*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>2.52578781554784</v>
-      </c>
-      <c r="J134" s="40" t="str">
-        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(F17),F17&gt;0,ISNUMBER(D17),D17&gt;0),IF((F17*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&gt;0,(F17*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))/(2*PI()*C17*1000000)*1000000000000,"—"),"—"),"—")</f>
+      <c r="G134" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$7*IF(ISNUMBER(E17),E17,0)/D80)&gt;0,($C$7*IF(ISNUMBER(E17),E17,0)/D80)/(2*PI()*C17*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H134" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$7*IF(ISNUMBER(E17),E17,0)/D80)&lt;0,1/((2*PI()*C17*1000000)*ABS(($C$7*IF(ISNUMBER(E17),E17,0)/D80)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I134" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D17),D17&gt;0),IF((D80*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&lt;0,-1/((2*PI()*C17*1000000)*(D80*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J134" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D17),D17&gt;0),IF((D80*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&gt;0,(D80*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))/(2*PI()*C17*1000000)*1000000000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="42" t="n">
+      <c r="B135" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="C135" s="43" t="n">
+      <c r="C135" s="46" t="n">
         <f aca="false">C18</f>
         <v>28</v>
       </c>
-      <c r="D135" s="43" t="n">
+      <c r="D135" s="46" t="n">
         <f aca="false">D18</f>
         <v>800</v>
       </c>
-      <c r="E135" s="43" t="n">
+      <c r="E135" s="46" t="n">
         <f aca="false">IF(ISNUMBER(E18),E18,"—")</f>
         <v>0</v>
       </c>
-      <c r="F135" s="43" t="n">
-        <f aca="false">IF(ISNUMBER(G18),G18,"—")</f>
-        <v>0</v>
-      </c>
-      <c r="G135" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(F18),F18&gt;0,ISNUMBER(D18),D18&gt;0),IF(($C$7*IF(ISNUMBER(E18),E18,0)/F18)&gt;0,($C$7*IF(ISNUMBER(E18),E18,0)/F18)/(2*PI()*C18*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H135" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(F18),F18&gt;0,ISNUMBER(D18),D18&gt;0),IF(($C$7*IF(ISNUMBER(E18),E18,0)/F18)&lt;0,1/((2*PI()*C18*1000000)*ABS(($C$7*IF(ISNUMBER(E18),E18,0)/F18)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I135" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(F18),F18&gt;0,ISNUMBER(D18),D18&gt;0),IF((F18*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))&lt;0,-1/((2*PI()*C18*1000000)*(F18*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J135" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(F18),F18&gt;0,ISNUMBER(D18),D18&gt;0),IF((F18*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))&gt;0,(F18*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))/(2*PI()*C18*1000000)*1000000000000,"—"),"—"),"—")</f>
+      <c r="F135" s="46" t="n">
+        <f aca="false">IF(ISNUMBER(E81),E81,"—")</f>
+        <v>0</v>
+      </c>
+      <c r="G135" s="47" t="str">
+        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D18),D18&gt;0),IF(($C$7*IF(ISNUMBER(E18),E18,0)/D81)&gt;0,($C$7*IF(ISNUMBER(E18),E18,0)/D81)/(2*PI()*C18*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H135" s="46" t="str">
+        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D18),D18&gt;0),IF(($C$7*IF(ISNUMBER(E18),E18,0)/D81)&lt;0,1/((2*PI()*C18*1000000)*ABS(($C$7*IF(ISNUMBER(E18),E18,0)/D81)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I135" s="47" t="str">
+        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D18),D18&gt;0),IF((D81*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))&lt;0,-1/((2*PI()*C18*1000000)*(D81*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J135" s="46" t="str">
+        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D18),D18&gt;0),IF((D81*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))&gt;0,(D81*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))/(2*PI()*C18*1000000)*1000000000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="39" t="n">
+      <c r="B136" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="C136" s="40" t="n">
+      <c r="C136" s="43" t="n">
         <f aca="false">C19</f>
         <v>0</v>
       </c>
-      <c r="D136" s="40" t="n">
+      <c r="D136" s="43" t="n">
         <f aca="false">D19</f>
         <v>0</v>
       </c>
-      <c r="E136" s="40" t="str">
+      <c r="E136" s="43" t="str">
         <f aca="false">IF(ISNUMBER(E19),E19,"—")</f>
         <v>—</v>
       </c>
-      <c r="F136" s="40" t="str">
-        <f aca="false">IF(ISNUMBER(G19),G19,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="G136" s="41" t="str">
-        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(F19),F19&gt;0,ISNUMBER(D19),D19&gt;0),IF(($C$7*IF(ISNUMBER(E19),E19,0)/F19)&gt;0,($C$7*IF(ISNUMBER(E19),E19,0)/F19)/(2*PI()*C19*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H136" s="40" t="str">
-        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(F19),F19&gt;0,ISNUMBER(D19),D19&gt;0),IF(($C$7*IF(ISNUMBER(E19),E19,0)/F19)&lt;0,1/((2*PI()*C19*1000000)*ABS(($C$7*IF(ISNUMBER(E19),E19,0)/F19)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I136" s="41" t="str">
-        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(F19),F19&gt;0,ISNUMBER(D19),D19&gt;0),IF((F19*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))&lt;0,-1/((2*PI()*C19*1000000)*(F19*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J136" s="40" t="str">
-        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(F19),F19&gt;0,ISNUMBER(D19),D19&gt;0),IF((F19*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))&gt;0,(F19*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))/(2*PI()*C19*1000000)*1000000000000,"—"),"—"),"—")</f>
+      <c r="F136" s="43" t="str">
+        <f aca="false">IF(ISNUMBER(E82),E82,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G136" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D19),D19&gt;0),IF(($C$7*IF(ISNUMBER(E19),E19,0)/D82)&gt;0,($C$7*IF(ISNUMBER(E19),E19,0)/D82)/(2*PI()*C19*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H136" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D19),D19&gt;0),IF(($C$7*IF(ISNUMBER(E19),E19,0)/D82)&lt;0,1/((2*PI()*C19*1000000)*ABS(($C$7*IF(ISNUMBER(E19),E19,0)/D82)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I136" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D19),D19&gt;0),IF((D82*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))&lt;0,-1/((2*PI()*C19*1000000)*(D82*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J136" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D19),D19&gt;0),IF((D82*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))&gt;0,(D82*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))/(2*PI()*C19*1000000)*1000000000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="42" t="n">
+      <c r="B137" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="C137" s="43" t="n">
+      <c r="C137" s="46" t="n">
         <f aca="false">C20</f>
         <v>0</v>
       </c>
-      <c r="D137" s="43" t="n">
+      <c r="D137" s="46" t="n">
         <f aca="false">D20</f>
         <v>0</v>
       </c>
-      <c r="E137" s="43" t="str">
+      <c r="E137" s="46" t="str">
         <f aca="false">IF(ISNUMBER(E20),E20,"—")</f>
         <v>—</v>
       </c>
-      <c r="F137" s="43" t="str">
-        <f aca="false">IF(ISNUMBER(G20),G20,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="G137" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(F20),F20&gt;0,ISNUMBER(D20),D20&gt;0),IF(($C$7*IF(ISNUMBER(E20),E20,0)/F20)&gt;0,($C$7*IF(ISNUMBER(E20),E20,0)/F20)/(2*PI()*C20*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H137" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(F20),F20&gt;0,ISNUMBER(D20),D20&gt;0),IF(($C$7*IF(ISNUMBER(E20),E20,0)/F20)&lt;0,1/((2*PI()*C20*1000000)*ABS(($C$7*IF(ISNUMBER(E20),E20,0)/F20)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I137" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(F20),F20&gt;0,ISNUMBER(D20),D20&gt;0),IF((F20*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))&lt;0,-1/((2*PI()*C20*1000000)*(F20*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J137" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(F20),F20&gt;0,ISNUMBER(D20),D20&gt;0),IF((F20*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))&gt;0,(F20*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))/(2*PI()*C20*1000000)*1000000000000,"—"),"—"),"—")</f>
+      <c r="F137" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(E83),E83,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G137" s="47" t="str">
+        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D20),D20&gt;0),IF(($C$7*IF(ISNUMBER(E20),E20,0)/D83)&gt;0,($C$7*IF(ISNUMBER(E20),E20,0)/D83)/(2*PI()*C20*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H137" s="46" t="str">
+        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D20),D20&gt;0),IF(($C$7*IF(ISNUMBER(E20),E20,0)/D83)&lt;0,1/((2*PI()*C20*1000000)*ABS(($C$7*IF(ISNUMBER(E20),E20,0)/D83)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I137" s="47" t="str">
+        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D20),D20&gt;0),IF((D83*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))&lt;0,-1/((2*PI()*C20*1000000)*(D83*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J137" s="46" t="str">
+        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D20),D20&gt;0),IF((D83*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))&gt;0,(D83*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))/(2*PI()*C20*1000000)*1000000000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="39" t="n">
+      <c r="B138" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="C138" s="40" t="n">
+      <c r="C138" s="43" t="n">
         <f aca="false">C21</f>
         <v>0</v>
       </c>
-      <c r="D138" s="40" t="n">
+      <c r="D138" s="43" t="n">
         <f aca="false">D21</f>
         <v>0</v>
       </c>
-      <c r="E138" s="40" t="str">
+      <c r="E138" s="43" t="str">
         <f aca="false">IF(ISNUMBER(E21),E21,"—")</f>
         <v>—</v>
       </c>
-      <c r="F138" s="40" t="str">
-        <f aca="false">IF(ISNUMBER(G21),G21,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="G138" s="41" t="str">
-        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(F21),F21&gt;0,ISNUMBER(D21),D21&gt;0),IF(($C$7*IF(ISNUMBER(E21),E21,0)/F21)&gt;0,($C$7*IF(ISNUMBER(E21),E21,0)/F21)/(2*PI()*C21*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H138" s="40" t="str">
-        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(F21),F21&gt;0,ISNUMBER(D21),D21&gt;0),IF(($C$7*IF(ISNUMBER(E21),E21,0)/F21)&lt;0,1/((2*PI()*C21*1000000)*ABS(($C$7*IF(ISNUMBER(E21),E21,0)/F21)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I138" s="41" t="str">
-        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(F21),F21&gt;0,ISNUMBER(D21),D21&gt;0),IF((F21*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))&lt;0,-1/((2*PI()*C21*1000000)*(F21*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J138" s="40" t="str">
-        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(F21),F21&gt;0,ISNUMBER(D21),D21&gt;0),IF((F21*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))&gt;0,(F21*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))/(2*PI()*C21*1000000)*1000000000000,"—"),"—"),"—")</f>
+      <c r="F138" s="43" t="str">
+        <f aca="false">IF(ISNUMBER(E84),E84,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G138" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D21),D21&gt;0),IF(($C$7*IF(ISNUMBER(E21),E21,0)/D84)&gt;0,($C$7*IF(ISNUMBER(E21),E21,0)/D84)/(2*PI()*C21*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H138" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D21),D21&gt;0),IF(($C$7*IF(ISNUMBER(E21),E21,0)/D84)&lt;0,1/((2*PI()*C21*1000000)*ABS(($C$7*IF(ISNUMBER(E21),E21,0)/D84)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I138" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D21),D21&gt;0),IF((D84*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))&lt;0,-1/((2*PI()*C21*1000000)*(D84*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J138" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D21),D21&gt;0),IF((D84*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))&gt;0,(D84*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))/(2*PI()*C21*1000000)*1000000000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="42" t="n">
+      <c r="B139" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="C139" s="43" t="n">
+      <c r="C139" s="46" t="n">
         <f aca="false">C22</f>
         <v>0</v>
       </c>
-      <c r="D139" s="43" t="n">
+      <c r="D139" s="46" t="n">
         <f aca="false">D22</f>
         <v>0</v>
       </c>
-      <c r="E139" s="43" t="str">
+      <c r="E139" s="46" t="str">
         <f aca="false">IF(ISNUMBER(E22),E22,"—")</f>
         <v>—</v>
       </c>
-      <c r="F139" s="43" t="str">
-        <f aca="false">IF(ISNUMBER(G22),G22,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="G139" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(F22),F22&gt;0,ISNUMBER(D22),D22&gt;0),IF(($C$7*IF(ISNUMBER(E22),E22,0)/F22)&gt;0,($C$7*IF(ISNUMBER(E22),E22,0)/F22)/(2*PI()*C22*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H139" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(F22),F22&gt;0,ISNUMBER(D22),D22&gt;0),IF(($C$7*IF(ISNUMBER(E22),E22,0)/F22)&lt;0,1/((2*PI()*C22*1000000)*ABS(($C$7*IF(ISNUMBER(E22),E22,0)/F22)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I139" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(F22),F22&gt;0,ISNUMBER(D22),D22&gt;0),IF((F22*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))&lt;0,-1/((2*PI()*C22*1000000)*(F22*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J139" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(F22),F22&gt;0,ISNUMBER(D22),D22&gt;0),IF((F22*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))&gt;0,(F22*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))/(2*PI()*C22*1000000)*1000000000000,"—"),"—"),"—")</f>
+      <c r="F139" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(E85),E85,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G139" s="47" t="str">
+        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D22),D22&gt;0),IF(($C$7*IF(ISNUMBER(E22),E22,0)/D85)&gt;0,($C$7*IF(ISNUMBER(E22),E22,0)/D85)/(2*PI()*C22*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H139" s="46" t="str">
+        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D22),D22&gt;0),IF(($C$7*IF(ISNUMBER(E22),E22,0)/D85)&lt;0,1/((2*PI()*C22*1000000)*ABS(($C$7*IF(ISNUMBER(E22),E22,0)/D85)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I139" s="47" t="str">
+        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D22),D22&gt;0),IF((D85*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))&lt;0,-1/((2*PI()*C22*1000000)*(D85*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J139" s="46" t="str">
+        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D22),D22&gt;0),IF((D85*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))&gt;0,(D85*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))/(2*PI()*C22*1000000)*1000000000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="39" t="n">
+      <c r="B140" s="42" t="n">
         <v>9</v>
       </c>
-      <c r="C140" s="40" t="n">
+      <c r="C140" s="43" t="n">
         <f aca="false">C23</f>
         <v>0</v>
       </c>
-      <c r="D140" s="40" t="n">
+      <c r="D140" s="43" t="n">
         <f aca="false">D23</f>
         <v>0</v>
       </c>
-      <c r="E140" s="40" t="str">
+      <c r="E140" s="43" t="str">
         <f aca="false">IF(ISNUMBER(E23),E23,"—")</f>
         <v>—</v>
       </c>
-      <c r="F140" s="40" t="str">
-        <f aca="false">IF(ISNUMBER(G23),G23,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="G140" s="41" t="str">
-        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(F23),F23&gt;0,ISNUMBER(D23),D23&gt;0),IF(($C$7*IF(ISNUMBER(E23),E23,0)/F23)&gt;0,($C$7*IF(ISNUMBER(E23),E23,0)/F23)/(2*PI()*C23*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H140" s="40" t="str">
-        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(F23),F23&gt;0,ISNUMBER(D23),D23&gt;0),IF(($C$7*IF(ISNUMBER(E23),E23,0)/F23)&lt;0,1/((2*PI()*C23*1000000)*ABS(($C$7*IF(ISNUMBER(E23),E23,0)/F23)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I140" s="41" t="str">
-        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(F23),F23&gt;0,ISNUMBER(D23),D23&gt;0),IF((F23*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))&lt;0,-1/((2*PI()*C23*1000000)*(F23*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J140" s="40" t="str">
-        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(F23),F23&gt;0,ISNUMBER(D23),D23&gt;0),IF((F23*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))&gt;0,(F23*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))/(2*PI()*C23*1000000)*1000000000000,"—"),"—"),"—")</f>
+      <c r="F140" s="43" t="str">
+        <f aca="false">IF(ISNUMBER(E86),E86,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G140" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D23),D23&gt;0),IF(($C$7*IF(ISNUMBER(E23),E23,0)/D86)&gt;0,($C$7*IF(ISNUMBER(E23),E23,0)/D86)/(2*PI()*C23*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H140" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D23),D23&gt;0),IF(($C$7*IF(ISNUMBER(E23),E23,0)/D86)&lt;0,1/((2*PI()*C23*1000000)*ABS(($C$7*IF(ISNUMBER(E23),E23,0)/D86)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I140" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D23),D23&gt;0),IF((D86*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))&lt;0,-1/((2*PI()*C23*1000000)*(D86*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J140" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D23),D23&gt;0),IF((D86*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))&gt;0,(D86*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))/(2*PI()*C23*1000000)*1000000000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="42" t="n">
+      <c r="B141" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="C141" s="43" t="n">
+      <c r="C141" s="46" t="n">
         <f aca="false">C24</f>
         <v>0</v>
       </c>
-      <c r="D141" s="43" t="n">
+      <c r="D141" s="46" t="n">
         <f aca="false">D24</f>
         <v>0</v>
       </c>
-      <c r="E141" s="43" t="str">
+      <c r="E141" s="46" t="str">
         <f aca="false">IF(ISNUMBER(E24),E24,"—")</f>
         <v>—</v>
       </c>
-      <c r="F141" s="43" t="str">
-        <f aca="false">IF(ISNUMBER(G24),G24,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="G141" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(F24),F24&gt;0,ISNUMBER(D24),D24&gt;0),IF(($C$7*IF(ISNUMBER(E24),E24,0)/F24)&gt;0,($C$7*IF(ISNUMBER(E24),E24,0)/F24)/(2*PI()*C24*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H141" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(F24),F24&gt;0,ISNUMBER(D24),D24&gt;0),IF(($C$7*IF(ISNUMBER(E24),E24,0)/F24)&lt;0,1/((2*PI()*C24*1000000)*ABS(($C$7*IF(ISNUMBER(E24),E24,0)/F24)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I141" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(F24),F24&gt;0,ISNUMBER(D24),D24&gt;0),IF((F24*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))&lt;0,-1/((2*PI()*C24*1000000)*(F24*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J141" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(F24),F24&gt;0,ISNUMBER(D24),D24&gt;0),IF((F24*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))&gt;0,(F24*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))/(2*PI()*C24*1000000)*1000000000000,"—"),"—"),"—")</f>
+      <c r="F141" s="46" t="str">
+        <f aca="false">IF(ISNUMBER(E87),E87,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G141" s="47" t="str">
+        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D24),D24&gt;0),IF(($C$7*IF(ISNUMBER(E24),E24,0)/D87)&gt;0,($C$7*IF(ISNUMBER(E24),E24,0)/D87)/(2*PI()*C24*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H141" s="46" t="str">
+        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D24),D24&gt;0),IF(($C$7*IF(ISNUMBER(E24),E24,0)/D87)&lt;0,1/((2*PI()*C24*1000000)*ABS(($C$7*IF(ISNUMBER(E24),E24,0)/D87)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I141" s="47" t="str">
+        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D24),D24&gt;0),IF((D87*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))&lt;0,-1/((2*PI()*C24*1000000)*(D87*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J141" s="46" t="str">
+        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D24),D24&gt;0),IF((D87*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))&gt;0,(D87*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))/(2*PI()*C24*1000000)*1000000000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="39" t="n">
+      <c r="B142" s="42" t="n">
         <v>11</v>
       </c>
-      <c r="C142" s="40" t="n">
+      <c r="C142" s="43" t="n">
         <f aca="false">C25</f>
         <v>0</v>
       </c>
-      <c r="D142" s="40" t="n">
+      <c r="D142" s="43" t="n">
         <f aca="false">D25</f>
         <v>0</v>
       </c>
-      <c r="E142" s="40" t="str">
+      <c r="E142" s="43" t="str">
         <f aca="false">IF(ISNUMBER(E25),E25,"—")</f>
         <v>—</v>
       </c>
-      <c r="F142" s="40" t="str">
-        <f aca="false">IF(ISNUMBER(G25),G25,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="G142" s="41" t="str">
-        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(F25),F25&gt;0,ISNUMBER(D25),D25&gt;0),IF(($C$7*IF(ISNUMBER(E25),E25,0)/F25)&gt;0,($C$7*IF(ISNUMBER(E25),E25,0)/F25)/(2*PI()*C25*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H142" s="40" t="str">
-        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(F25),F25&gt;0,ISNUMBER(D25),D25&gt;0),IF(($C$7*IF(ISNUMBER(E25),E25,0)/F25)&lt;0,1/((2*PI()*C25*1000000)*ABS(($C$7*IF(ISNUMBER(E25),E25,0)/F25)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I142" s="41" t="str">
-        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(F25),F25&gt;0,ISNUMBER(D25),D25&gt;0),IF((F25*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))&lt;0,-1/((2*PI()*C25*1000000)*(F25*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J142" s="40" t="str">
-        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(F25),F25&gt;0,ISNUMBER(D25),D25&gt;0),IF((F25*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))&gt;0,(F25*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))/(2*PI()*C25*1000000)*1000000000000,"—"),"—"),"—")</f>
+      <c r="F142" s="43" t="str">
+        <f aca="false">IF(ISNUMBER(E88),E88,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="G142" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D25),D25&gt;0),IF(($C$7*IF(ISNUMBER(E25),E25,0)/D88)&gt;0,($C$7*IF(ISNUMBER(E25),E25,0)/D88)/(2*PI()*C25*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H142" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D25),D25&gt;0),IF(($C$7*IF(ISNUMBER(E25),E25,0)/D88)&lt;0,1/((2*PI()*C25*1000000)*ABS(($C$7*IF(ISNUMBER(E25),E25,0)/D88)))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I142" s="44" t="str">
+        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D25),D25&gt;0),IF((D88*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))&lt;0,-1/((2*PI()*C25*1000000)*(D88*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J142" s="43" t="str">
+        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D25),D25&gt;0),IF((D88*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))&gt;0,(D88*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))/(2*PI()*C25*1000000)*1000000000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="36" t="s">
+      <c r="B144" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C144" s="39"/>
+      <c r="D144" s="39"/>
+      <c r="E144" s="39"/>
+      <c r="F144" s="39"/>
+      <c r="G144" s="39"/>
+      <c r="H144" s="39"/>
+      <c r="I144" s="39"/>
+      <c r="J144" s="39"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B145" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C145" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="D145" s="40"/>
+      <c r="E145" s="40"/>
+      <c r="F145" s="40"/>
+      <c r="G145" s="40"/>
+      <c r="H145" s="40"/>
+      <c r="I145" s="40"/>
+      <c r="J145" s="40"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="48" t="s">
         <v>124</v>
       </c>
-      <c r="C144" s="36"/>
-      <c r="D144" s="36"/>
-      <c r="E144" s="36"/>
-      <c r="F144" s="36"/>
-      <c r="G144" s="36"/>
-      <c r="H144" s="36"/>
-      <c r="I144" s="36"/>
-      <c r="J144" s="36"/>
-    </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="45" t="s">
+      <c r="C146" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="C145" s="37" t="s">
+      <c r="D146" s="40"/>
+      <c r="E146" s="40"/>
+      <c r="F146" s="40"/>
+      <c r="G146" s="40"/>
+      <c r="H146" s="40"/>
+      <c r="I146" s="40"/>
+      <c r="J146" s="40"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="D145" s="37"/>
-      <c r="E145" s="37"/>
-      <c r="F145" s="37"/>
-      <c r="G145" s="37"/>
-      <c r="H145" s="37"/>
-      <c r="I145" s="37"/>
-      <c r="J145" s="37"/>
-    </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="45" t="s">
+      <c r="C147" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="C146" s="37" t="s">
+      <c r="D147" s="40"/>
+      <c r="E147" s="40"/>
+      <c r="F147" s="40"/>
+      <c r="G147" s="40"/>
+      <c r="H147" s="40"/>
+      <c r="I147" s="40"/>
+      <c r="J147" s="40"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="D146" s="37"/>
-      <c r="E146" s="37"/>
-      <c r="F146" s="37"/>
-      <c r="G146" s="37"/>
-      <c r="H146" s="37"/>
-      <c r="I146" s="37"/>
-      <c r="J146" s="37"/>
-    </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="45" t="s">
+      <c r="C148" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="C147" s="37" t="s">
+      <c r="D148" s="40"/>
+      <c r="E148" s="40"/>
+      <c r="F148" s="40"/>
+      <c r="G148" s="40"/>
+      <c r="H148" s="40"/>
+      <c r="I148" s="40"/>
+      <c r="J148" s="40"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B149" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="D147" s="37"/>
-      <c r="E147" s="37"/>
-      <c r="F147" s="37"/>
-      <c r="G147" s="37"/>
-      <c r="H147" s="37"/>
-      <c r="I147" s="37"/>
-      <c r="J147" s="37"/>
-    </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="45" t="s">
+      <c r="C149" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="C148" s="37" t="s">
+      <c r="D149" s="40"/>
+      <c r="E149" s="40"/>
+      <c r="F149" s="40"/>
+      <c r="G149" s="40"/>
+      <c r="H149" s="40"/>
+      <c r="I149" s="40"/>
+      <c r="J149" s="40"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B150" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="D148" s="37"/>
-      <c r="E148" s="37"/>
-      <c r="F148" s="37"/>
-      <c r="G148" s="37"/>
-      <c r="H148" s="37"/>
-      <c r="I148" s="37"/>
-      <c r="J148" s="37"/>
-    </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="45" t="s">
+      <c r="C150" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="C149" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="D149" s="37"/>
-      <c r="E149" s="37"/>
-      <c r="F149" s="37"/>
-      <c r="G149" s="37"/>
-      <c r="H149" s="37"/>
-      <c r="I149" s="37"/>
-      <c r="J149" s="37"/>
-    </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="C150" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="D150" s="37"/>
-      <c r="E150" s="37"/>
-      <c r="F150" s="37"/>
-      <c r="G150" s="37"/>
-      <c r="H150" s="37"/>
-      <c r="I150" s="37"/>
-      <c r="J150" s="37"/>
-    </row>
-    <row r="1048554" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048555" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048556" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048557" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048558" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048559" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048560" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048561" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048562" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048563" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048564" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048565" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D150" s="40"/>
+      <c r="E150" s="40"/>
+      <c r="F150" s="40"/>
+      <c r="G150" s="40"/>
+      <c r="H150" s="40"/>
+      <c r="I150" s="40"/>
+      <c r="J150" s="40"/>
+    </row>
   </sheetData>
   <mergeCells count="62">
     <mergeCell ref="B2:I2"/>
@@ -4187,14 +3954,14 @@
     <mergeCell ref="E9:H9"/>
     <mergeCell ref="E10:H10"/>
     <mergeCell ref="E11:I11"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B28:J28"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B40:J40"/>
-    <mergeCell ref="B54:J54"/>
-    <mergeCell ref="B55:J55"/>
-    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B57:I57"/>
     <mergeCell ref="B71:D71"/>
     <mergeCell ref="B73:I73"/>
     <mergeCell ref="B74:I74"/>

--- a/Autotransformer_UnUn_AirCore_Calculator.xlsx
+++ b/Autotransformer_UnUn_AirCore_Calculator.xlsx
@@ -76,10 +76,13 @@
     <t xml:space="preserve">Enter 1–11  (rows below auto-activate)</t>
   </si>
   <si>
-    <t xml:space="preserve">T_ref  (turns at 50Ω tap — user sets or use suggestion below)</t>
+    <t xml:space="preserve">T_ref  (turns at 50Ω tap)</t>
   </si>
   <si>
     <t xml:space="preserve">Suggested T_ref (min 5 turns at lowest-Z tap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Space between coil turns</t>
   </si>
   <si>
     <t xml:space="preserve">TAP INPUT IMPEDANCES  (enter R + jX per tap, or leave blank for inactive taps)</t>
@@ -99,6 +102,9 @@
 Reactance (+L / −C)</t>
   </si>
   <si>
+    <t xml:space="preserve">Active</t>
+  </si>
+  <si>
     <t xml:space="preserve">✦  AIR-CORE UnUn DESIGN  —  SUMMARY DASHBOARD  ✦</t>
   </si>
   <si>
@@ -109,12 +115,6 @@
   </si>
   <si>
     <t xml:space="preserve">Target Z_out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Min. Tap Frequency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MHz</t>
   </si>
   <si>
     <t xml:space="preserve">Wire Dia.</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">Winding pitch (mm/turn)</t>
   </si>
   <si>
-    <t xml:space="preserve">Wire dia (from Inputs) + gap; must be ≥ wire dia</t>
+    <t xml:space="preserve">Wire dia + space between turns (C12); pitch = $C$8 + $C$12</t>
   </si>
   <si>
     <t xml:space="preserve">Total turns N (from Winding Design)</t>
@@ -554,7 +554,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -576,7 +576,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFEAF0FB"/>
+        <bgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
     <fill>
@@ -593,14 +593,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFF9E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6E8F5"/>
-        <bgColor rgb="FFEAF0FB"/>
+        <fgColor rgb="FFEEEEEE"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -619,12 +613,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4A6B"/>
         <bgColor rgb="FF1F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF0FB"/>
-        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -677,7 +665,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -703,7 +691,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -718,10 +706,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -730,11 +714,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -750,26 +738,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -782,6 +758,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -802,7 +782,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -814,7 +794,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -826,7 +806,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -834,7 +814,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -842,31 +822,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="173" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -904,7 +872,7 @@
       <rgbColor rgb="FF8EA9C1"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF9E6"/>
-      <rgbColor rgb="FFD6E8F5"/>
+      <rgbColor rgb="FFF0F8FF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF1F5C8B"/>
@@ -918,9 +886,9 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFEAF0FB"/>
+      <rgbColor rgb="FFEEEEEE"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFF0F8FF"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -1263,230 +1231,266 @@
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
     </row>
-    <row r="11" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="10" t="n">
         <f aca="false">IFERROR(CEILING(5/MIN(D59:D69),1),5)</f>
         <v>3</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-    </row>
-    <row r="14" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
+      <c r="C12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+    </row>
+    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="15" t="n">
+      <c r="E15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="14"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C16" s="7" t="n">
         <v>7.2</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D16" s="16" t="n">
         <v>200</v>
       </c>
-      <c r="E15" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="21"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="22" t="n">
+      <c r="E16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="15" t="str">
+        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G16" s="18"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="19"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C17" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D17" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E17" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="21"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="15" t="n">
+      <c r="F17" s="15" t="str">
+        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C18" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D18" s="16" t="n">
         <v>450</v>
       </c>
-      <c r="E17" s="17" t="n">
+      <c r="E18" s="17" t="n">
         <v>-80</v>
       </c>
-      <c r="F17" s="18"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="21"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="22" t="n">
+      <c r="F18" s="15" t="str">
+        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D19" s="16" t="n">
         <v>800</v>
       </c>
-      <c r="E18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="18"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="21"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="15" t="n">
+      <c r="E19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="15" t="str">
+        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="G19" s="18"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="19"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="15" t="n">
         <v>5</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="21"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="22" t="n">
-        <v>6</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="16"/>
       <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="21"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F20" s="15" t="str">
+        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="G20" s="18"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="16"/>
       <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="21"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="22" t="n">
-        <v>8</v>
+      <c r="F21" s="15" t="str">
+        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="G21" s="18"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="19"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="15" t="n">
+        <v>7</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="21"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F22" s="15" t="str">
+        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="G22" s="18"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="16"/>
       <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="21"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="22" t="n">
-        <v>10</v>
+      <c r="F23" s="15" t="str">
+        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="G23" s="18"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="15" t="n">
+        <v>9</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="16"/>
       <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="21"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F24" s="15" t="str">
+        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="G24" s="18"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="16"/>
       <c r="E25" s="17"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="21"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
+      <c r="F25" s="15" t="str">
+        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="G25" s="18"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="15" t="str">
+        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="G26" s="18"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="13"/>
       <c r="F28" s="13"/>
       <c r="G28" s="13"/>
@@ -1494,42 +1498,43 @@
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="6" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="23" t="n">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="20" t="n">
         <f aca="false">C7</f>
         <v>50</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D32" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="23" t="n">
-        <f aca="false">IFERROR(aggregate(15,6,C15:C25*(1/(H15:H25="YES")),1),MIN(C15:C25))</f>
-        <v>7.2</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="20" t="n">
         <f aca="false">C8</f>
         <v>0.45</v>
       </c>
@@ -1537,11 +1542,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C34" s="20" t="n">
         <f aca="false">C11</f>
         <v>20</v>
       </c>
@@ -1549,11 +1554,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="23" t="n">
+      <c r="C35" s="20" t="n">
         <f aca="false">C10</f>
         <v>4</v>
       </c>
@@ -1561,11 +1566,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="24" t="n">
+      <c r="C36" s="21" t="n">
         <f aca="false">I71</f>
         <v>4134.33593212417</v>
       </c>
@@ -1573,25 +1578,25 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="25" t="n">
+      <c r="C37" s="22" t="n">
         <f aca="false">IFERROR(C115,"—")</f>
-        <v>35.9977335339286</v>
+        <v>3.88816824074988</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="23" t="str">
+      <c r="C38" s="20" t="str">
         <f aca="false">IFERROR(C118,"—")</f>
-        <v>✔ YES</v>
+        <v>—</v>
       </c>
       <c r="D38" s="8"/>
     </row>
@@ -1608,9 +1613,9 @@
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>40</v>
@@ -1637,409 +1642,409 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="15" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="23" t="n">
-        <f aca="false">C15</f>
+      <c r="C42" s="20" t="n">
+        <f aca="false">C16</f>
         <v>7.2</v>
       </c>
-      <c r="D42" s="26" t="n">
+      <c r="D42" s="24" t="n">
         <f aca="false">D78</f>
         <v>200</v>
       </c>
-      <c r="E42" s="27" t="n">
+      <c r="E42" s="25" t="n">
         <f aca="false">E78</f>
         <v>0</v>
       </c>
-      <c r="F42" s="28" t="n">
+      <c r="F42" s="26" t="n">
         <f aca="false">D59</f>
         <v>2</v>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="G42" s="10" t="n">
         <f aca="false">E59</f>
         <v>40</v>
       </c>
-      <c r="H42" s="29" t="n">
+      <c r="H42" s="27" t="n">
         <f aca="false">F78</f>
         <v>1</v>
       </c>
-      <c r="I42" s="30" t="n">
+      <c r="I42" s="28" t="n">
         <f aca="false">G78</f>
         <v>180</v>
       </c>
-      <c r="J42" s="29" t="n">
+      <c r="J42" s="27" t="n">
         <f aca="false">I78</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="22" t="n">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="23" t="n">
-        <f aca="false">C16</f>
+      <c r="C43" s="20" t="n">
+        <f aca="false">C17</f>
         <v>10</v>
       </c>
-      <c r="D43" s="26" t="n">
+      <c r="D43" s="24" t="n">
         <f aca="false">D79</f>
         <v>316.227766016838</v>
       </c>
-      <c r="E43" s="27" t="n">
+      <c r="E43" s="25" t="n">
         <f aca="false">E79</f>
         <v>18.434948822922</v>
       </c>
-      <c r="F43" s="28" t="n">
+      <c r="F43" s="26" t="n">
         <f aca="false">D60</f>
         <v>2.51486685936587</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="10" t="n">
         <f aca="false">E60</f>
         <v>50</v>
       </c>
-      <c r="H43" s="29" t="n">
+      <c r="H43" s="27" t="n">
         <f aca="false">F79</f>
         <v>1.38742588672279</v>
       </c>
-      <c r="I43" s="30" t="n">
+      <c r="I43" s="28" t="n">
         <f aca="false">G79</f>
         <v>15.7948252576199</v>
       </c>
-      <c r="J43" s="29" t="n">
+      <c r="J43" s="27" t="n">
         <f aca="false">I79</f>
         <v>2.6334038989724</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="15" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="C44" s="23" t="n">
-        <f aca="false">C17</f>
+      <c r="C44" s="20" t="n">
+        <f aca="false">C18</f>
         <v>18</v>
       </c>
-      <c r="D44" s="26" t="n">
+      <c r="D44" s="24" t="n">
         <f aca="false">D80</f>
         <v>457.055795281058</v>
       </c>
-      <c r="E44" s="27" t="n">
+      <c r="E44" s="25" t="n">
         <f aca="false">E80</f>
         <v>-10.0805979875423</v>
       </c>
-      <c r="F44" s="28" t="n">
+      <c r="F44" s="26" t="n">
         <f aca="false">D61</f>
         <v>3.02342784031985</v>
       </c>
-      <c r="G44" s="11" t="n">
+      <c r="G44" s="10" t="n">
         <f aca="false">E61</f>
         <v>60</v>
       </c>
-      <c r="H44" s="29" t="n">
+      <c r="H44" s="27" t="n">
         <f aca="false">F80</f>
         <v>1.19345732284679</v>
       </c>
-      <c r="I44" s="30" t="n">
+      <c r="I44" s="28" t="n">
         <f aca="false">G80</f>
         <v>21.0908803086925</v>
       </c>
-      <c r="J44" s="29" t="n">
+      <c r="J44" s="27" t="n">
         <f aca="false">I80</f>
         <v>0.777878860128034</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="22" t="n">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="C45" s="23" t="n">
-        <f aca="false">C18</f>
+      <c r="C45" s="20" t="n">
+        <f aca="false">C19</f>
         <v>28</v>
       </c>
-      <c r="D45" s="26" t="n">
+      <c r="D45" s="24" t="n">
         <f aca="false">D81</f>
         <v>800</v>
       </c>
-      <c r="E45" s="27" t="n">
+      <c r="E45" s="25" t="n">
         <f aca="false">E81</f>
         <v>0</v>
       </c>
-      <c r="F45" s="28" t="n">
+      <c r="F45" s="26" t="n">
         <f aca="false">D62</f>
         <v>4</v>
       </c>
-      <c r="G45" s="11" t="n">
+      <c r="G45" s="10" t="n">
         <f aca="false">E62</f>
         <v>80</v>
       </c>
-      <c r="H45" s="29" t="n">
+      <c r="H45" s="27" t="n">
         <f aca="false">F81</f>
         <v>1</v>
       </c>
-      <c r="I45" s="30" t="n">
+      <c r="I45" s="28" t="n">
         <f aca="false">G81</f>
         <v>180</v>
       </c>
-      <c r="J45" s="29" t="n">
+      <c r="J45" s="27" t="n">
         <f aca="false">I81</f>
         <v>0</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="15" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="C46" s="23" t="n">
-        <f aca="false">C19</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="23" t="str">
+      <c r="C46" s="20" t="n">
+        <f aca="false">C20</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="20" t="str">
         <f aca="false">D82</f>
         <v/>
       </c>
-      <c r="E46" s="23" t="str">
+      <c r="E46" s="20" t="str">
         <f aca="false">E82</f>
         <v/>
       </c>
-      <c r="F46" s="23" t="str">
+      <c r="F46" s="20" t="str">
         <f aca="false">D63</f>
         <v/>
       </c>
-      <c r="G46" s="23" t="str">
+      <c r="G46" s="20" t="str">
         <f aca="false">E63</f>
         <v/>
       </c>
-      <c r="H46" s="23" t="str">
+      <c r="H46" s="20" t="str">
         <f aca="false">F82</f>
         <v/>
       </c>
-      <c r="I46" s="23" t="str">
+      <c r="I46" s="20" t="str">
         <f aca="false">G82</f>
         <v/>
       </c>
-      <c r="J46" s="23" t="str">
+      <c r="J46" s="20" t="str">
         <f aca="false">I82</f>
         <v/>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="22" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C47" s="23" t="n">
-        <f aca="false">C20</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="23" t="str">
+      <c r="C47" s="20" t="n">
+        <f aca="false">C21</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="20" t="str">
         <f aca="false">D83</f>
         <v/>
       </c>
-      <c r="E47" s="23" t="str">
+      <c r="E47" s="20" t="str">
         <f aca="false">E83</f>
         <v/>
       </c>
-      <c r="F47" s="23" t="str">
+      <c r="F47" s="20" t="str">
         <f aca="false">D64</f>
         <v/>
       </c>
-      <c r="G47" s="23" t="str">
+      <c r="G47" s="20" t="str">
         <f aca="false">E64</f>
         <v/>
       </c>
-      <c r="H47" s="23" t="str">
+      <c r="H47" s="20" t="str">
         <f aca="false">F83</f>
         <v/>
       </c>
-      <c r="I47" s="23" t="str">
+      <c r="I47" s="20" t="str">
         <f aca="false">G83</f>
         <v/>
       </c>
-      <c r="J47" s="23" t="str">
+      <c r="J47" s="20" t="str">
         <f aca="false">I83</f>
         <v/>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="15" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="C48" s="23" t="n">
-        <f aca="false">C21</f>
-        <v>0</v>
-      </c>
-      <c r="D48" s="23" t="str">
+      <c r="C48" s="20" t="n">
+        <f aca="false">C22</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="20" t="str">
         <f aca="false">D84</f>
         <v/>
       </c>
-      <c r="E48" s="23" t="str">
+      <c r="E48" s="20" t="str">
         <f aca="false">E84</f>
         <v/>
       </c>
-      <c r="F48" s="23" t="str">
+      <c r="F48" s="20" t="str">
         <f aca="false">D65</f>
         <v/>
       </c>
-      <c r="G48" s="23" t="str">
+      <c r="G48" s="20" t="str">
         <f aca="false">E65</f>
         <v/>
       </c>
-      <c r="H48" s="23" t="str">
+      <c r="H48" s="20" t="str">
         <f aca="false">F84</f>
         <v/>
       </c>
-      <c r="I48" s="23" t="str">
+      <c r="I48" s="20" t="str">
         <f aca="false">G84</f>
         <v/>
       </c>
-      <c r="J48" s="23" t="str">
+      <c r="J48" s="20" t="str">
         <f aca="false">I84</f>
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="22" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="C49" s="23" t="n">
-        <f aca="false">C22</f>
-        <v>0</v>
-      </c>
-      <c r="D49" s="23" t="str">
+      <c r="C49" s="20" t="n">
+        <f aca="false">C23</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="20" t="str">
         <f aca="false">D85</f>
         <v/>
       </c>
-      <c r="E49" s="23" t="str">
+      <c r="E49" s="20" t="str">
         <f aca="false">E85</f>
         <v/>
       </c>
-      <c r="F49" s="23" t="str">
+      <c r="F49" s="20" t="str">
         <f aca="false">D66</f>
         <v/>
       </c>
-      <c r="G49" s="23" t="str">
+      <c r="G49" s="20" t="str">
         <f aca="false">E66</f>
         <v/>
       </c>
-      <c r="H49" s="23" t="str">
+      <c r="H49" s="20" t="str">
         <f aca="false">F85</f>
         <v/>
       </c>
-      <c r="I49" s="23" t="str">
+      <c r="I49" s="20" t="str">
         <f aca="false">G85</f>
         <v/>
       </c>
-      <c r="J49" s="23" t="str">
+      <c r="J49" s="20" t="str">
         <f aca="false">I85</f>
         <v/>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="15" t="n">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="C50" s="23" t="n">
-        <f aca="false">C23</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="23" t="str">
+      <c r="C50" s="20" t="n">
+        <f aca="false">C24</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="20" t="str">
         <f aca="false">D86</f>
         <v/>
       </c>
-      <c r="E50" s="23" t="str">
+      <c r="E50" s="20" t="str">
         <f aca="false">E86</f>
         <v/>
       </c>
-      <c r="F50" s="23" t="str">
+      <c r="F50" s="20" t="str">
         <f aca="false">D67</f>
         <v/>
       </c>
-      <c r="G50" s="23" t="str">
+      <c r="G50" s="20" t="str">
         <f aca="false">E67</f>
         <v/>
       </c>
-      <c r="H50" s="23" t="str">
+      <c r="H50" s="20" t="str">
         <f aca="false">F86</f>
         <v/>
       </c>
-      <c r="I50" s="23" t="str">
+      <c r="I50" s="20" t="str">
         <f aca="false">G86</f>
         <v/>
       </c>
-      <c r="J50" s="23" t="str">
+      <c r="J50" s="20" t="str">
         <f aca="false">I86</f>
         <v/>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="22" t="n">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="C51" s="23" t="n">
-        <f aca="false">C24</f>
-        <v>0</v>
-      </c>
-      <c r="D51" s="23" t="str">
+      <c r="C51" s="20" t="n">
+        <f aca="false">C25</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="20" t="str">
         <f aca="false">D87</f>
         <v/>
       </c>
-      <c r="E51" s="23" t="str">
+      <c r="E51" s="20" t="str">
         <f aca="false">E87</f>
         <v/>
       </c>
-      <c r="F51" s="23" t="str">
+      <c r="F51" s="20" t="str">
         <f aca="false">D68</f>
         <v/>
       </c>
-      <c r="G51" s="23" t="str">
+      <c r="G51" s="20" t="str">
         <f aca="false">E68</f>
         <v/>
       </c>
-      <c r="H51" s="23" t="str">
+      <c r="H51" s="20" t="str">
         <f aca="false">F87</f>
         <v/>
       </c>
-      <c r="I51" s="23" t="str">
+      <c r="I51" s="20" t="str">
         <f aca="false">G87</f>
         <v/>
       </c>
-      <c r="J51" s="23" t="str">
+      <c r="J51" s="20" t="str">
         <f aca="false">I87</f>
         <v/>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="15" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="C52" s="23" t="n">
-        <f aca="false">C25</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="23" t="str">
+      <c r="C52" s="20" t="n">
+        <f aca="false">C26</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="20" t="str">
         <f aca="false">D88</f>
         <v/>
       </c>
-      <c r="E52" s="23" t="str">
+      <c r="E52" s="20" t="str">
         <f aca="false">E88</f>
         <v/>
       </c>
-      <c r="F52" s="23" t="str">
+      <c r="F52" s="20" t="str">
         <f aca="false">D69</f>
         <v/>
       </c>
-      <c r="G52" s="23" t="str">
+      <c r="G52" s="20" t="str">
         <f aca="false">E69</f>
         <v/>
       </c>
-      <c r="H52" s="23" t="str">
+      <c r="H52" s="20" t="str">
         <f aca="false">F88</f>
         <v/>
       </c>
-      <c r="I52" s="23" t="str">
+      <c r="I52" s="20" t="str">
         <f aca="false">G88</f>
         <v/>
       </c>
-      <c r="J52" s="23" t="str">
+      <c r="J52" s="20" t="str">
         <f aca="false">I88</f>
         <v/>
       </c>
@@ -2083,9 +2088,9 @@
       <c r="I57" s="4"/>
       <c r="J57" s="13"/>
     </row>
-    <row r="58" customFormat="false" ht="38.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>40</v>
@@ -2110,395 +2115,395 @@
       </c>
       <c r="J58" s="13"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="15" t="n">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B59" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C59" s="23" t="n">
-        <f aca="false">C15</f>
+      <c r="C59" s="20" t="n">
+        <f aca="false">C16</f>
         <v>7.2</v>
       </c>
-      <c r="D59" s="28" t="n">
+      <c r="D59" s="26" t="n">
         <f aca="false">IF(D78&lt;&gt;"",SQRT(D78/MAX($C$7,0.000000001)),"")</f>
         <v>2</v>
       </c>
-      <c r="E59" s="11" t="n">
+      <c r="E59" s="10" t="n">
         <f aca="false">IF(D59&lt;&gt;"",MAX(1,ROUND(C11*D59,0)),"")</f>
         <v>40</v>
       </c>
-      <c r="F59" s="11" t="n">
+      <c r="F59" s="10" t="n">
         <f aca="false">IF(E59&lt;&gt;"",E59,"")</f>
         <v>40</v>
       </c>
-      <c r="G59" s="24" t="n">
+      <c r="G59" s="21" t="n">
         <f aca="false">IF(F59&lt;&gt;"",F59*PI()*($C$9+$C$8),"")</f>
         <v>2067.16796606208</v>
       </c>
-      <c r="H59" s="26" t="n">
+      <c r="H59" s="24" t="n">
         <f aca="false">IF(G59&lt;&gt;"",G59*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>224.077432098765</v>
       </c>
-      <c r="I59" s="24" t="n">
+      <c r="I59" s="21" t="n">
         <f aca="false">IF(G59&lt;&gt;"",G59,"")</f>
         <v>2067.16796606208</v>
       </c>
-      <c r="J59" s="20"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="22" t="n">
+      <c r="J59" s="8"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B60" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C60" s="23" t="n">
-        <f aca="false">C16</f>
+      <c r="C60" s="20" t="n">
+        <f aca="false">C17</f>
         <v>10</v>
       </c>
-      <c r="D60" s="28" t="n">
+      <c r="D60" s="26" t="n">
         <f aca="false">IF(D79&lt;&gt;"",SQRT(D79/MAX($C$7,0.000000001)),"")</f>
         <v>2.51486685936587</v>
       </c>
-      <c r="E60" s="11" t="n">
+      <c r="E60" s="10" t="n">
         <f aca="false">IF(D60&lt;&gt;"",MAX(1,ROUND(C11*D60,0)),"")</f>
         <v>50</v>
       </c>
-      <c r="F60" s="11" t="n">
+      <c r="F60" s="10" t="n">
         <f aca="false">IF(AND(E60&lt;&gt;"",E59&lt;&gt;""),E60-E59,IF(E60&lt;&gt;"",E60,""))</f>
         <v>10</v>
       </c>
-      <c r="G60" s="24" t="n">
+      <c r="G60" s="21" t="n">
         <f aca="false">IF(F60&lt;&gt;"",F60*PI()*($C$9+$C$8),"")</f>
         <v>516.791991515521</v>
       </c>
-      <c r="H60" s="26" t="n">
+      <c r="H60" s="24" t="n">
         <f aca="false">IF(G60&lt;&gt;"",G60*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>56.0193580246914</v>
       </c>
-      <c r="I60" s="24" t="n">
+      <c r="I60" s="21" t="n">
         <f aca="false">IF(G60&lt;&gt;"",SUM(G59:G60),"")</f>
         <v>2583.9599575776</v>
       </c>
-      <c r="J60" s="20"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="15" t="n">
+      <c r="J60" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B61" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="C61" s="23" t="n">
-        <f aca="false">C17</f>
+      <c r="C61" s="20" t="n">
+        <f aca="false">C18</f>
         <v>18</v>
       </c>
-      <c r="D61" s="28" t="n">
+      <c r="D61" s="26" t="n">
         <f aca="false">IF(D80&lt;&gt;"",SQRT(D80/MAX($C$7,0.000000001)),"")</f>
         <v>3.02342784031985</v>
       </c>
-      <c r="E61" s="11" t="n">
+      <c r="E61" s="10" t="n">
         <f aca="false">IF(D61&lt;&gt;"",MAX(1,ROUND(C11*D61,0)),"")</f>
         <v>60</v>
       </c>
-      <c r="F61" s="11" t="n">
+      <c r="F61" s="10" t="n">
         <f aca="false">IF(AND(E61&lt;&gt;"",E60&lt;&gt;""),E61-E60,IF(E61&lt;&gt;"",E61,""))</f>
         <v>10</v>
       </c>
-      <c r="G61" s="24" t="n">
+      <c r="G61" s="21" t="n">
         <f aca="false">IF(F61&lt;&gt;"",F61*PI()*($C$9+$C$8),"")</f>
         <v>516.791991515521</v>
       </c>
-      <c r="H61" s="26" t="n">
+      <c r="H61" s="24" t="n">
         <f aca="false">IF(G61&lt;&gt;"",G61*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>56.0193580246914</v>
       </c>
-      <c r="I61" s="24" t="n">
+      <c r="I61" s="21" t="n">
         <f aca="false">IF(G61&lt;&gt;"",SUM(G59:G61),"")</f>
         <v>3100.75194909313</v>
       </c>
-      <c r="J61" s="20"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="22" t="n">
+      <c r="J61" s="8"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B62" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="C62" s="23" t="n">
-        <f aca="false">C18</f>
+      <c r="C62" s="20" t="n">
+        <f aca="false">C19</f>
         <v>28</v>
       </c>
-      <c r="D62" s="28" t="n">
+      <c r="D62" s="26" t="n">
         <f aca="false">IF(D81&lt;&gt;"",SQRT(D81/MAX($C$7,0.000000001)),"")</f>
         <v>4</v>
       </c>
-      <c r="E62" s="11" t="n">
+      <c r="E62" s="10" t="n">
         <f aca="false">IF(D62&lt;&gt;"",MAX(1,ROUND(C11*D62,0)),"")</f>
         <v>80</v>
       </c>
-      <c r="F62" s="11" t="n">
+      <c r="F62" s="10" t="n">
         <f aca="false">IF(AND(E62&lt;&gt;"",E61&lt;&gt;""),E62-E61,IF(E62&lt;&gt;"",E62,""))</f>
         <v>20</v>
       </c>
-      <c r="G62" s="24" t="n">
+      <c r="G62" s="21" t="n">
         <f aca="false">IF(F62&lt;&gt;"",F62*PI()*($C$9+$C$8),"")</f>
         <v>1033.58398303104</v>
       </c>
-      <c r="H62" s="26" t="n">
+      <c r="H62" s="24" t="n">
         <f aca="false">IF(G62&lt;&gt;"",G62*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v>112.038716049383</v>
       </c>
-      <c r="I62" s="24" t="n">
+      <c r="I62" s="21" t="n">
         <f aca="false">IF(G62&lt;&gt;"",SUM(G59:G62),"")</f>
         <v>4134.33593212417</v>
       </c>
-      <c r="J62" s="20"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="15" t="n">
+      <c r="J62" s="8"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B63" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="C63" s="23" t="n">
-        <f aca="false">C19</f>
-        <v>0</v>
-      </c>
-      <c r="D63" s="28" t="str">
+      <c r="C63" s="20" t="n">
+        <f aca="false">C20</f>
+        <v>0</v>
+      </c>
+      <c r="D63" s="26" t="str">
         <f aca="false">IF(D82&lt;&gt;"",SQRT(D82/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
-      <c r="E63" s="11" t="str">
+      <c r="E63" s="10" t="str">
         <f aca="false">IF(D63&lt;&gt;"",MAX(1,ROUND(C11*D63,0)),"")</f>
         <v/>
       </c>
-      <c r="F63" s="11" t="str">
+      <c r="F63" s="10" t="str">
         <f aca="false">IF(AND(E63&lt;&gt;"",E62&lt;&gt;""),E63-E62,IF(E63&lt;&gt;"",E63,""))</f>
         <v/>
       </c>
-      <c r="G63" s="24" t="str">
+      <c r="G63" s="21" t="str">
         <f aca="false">IF(F63&lt;&gt;"",F63*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H63" s="26" t="str">
+      <c r="H63" s="24" t="str">
         <f aca="false">IF(G63&lt;&gt;"",G63*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I63" s="24" t="str">
+      <c r="I63" s="21" t="str">
         <f aca="false">IF(G63&lt;&gt;"",SUM(G59:G63),"")</f>
         <v/>
       </c>
-      <c r="J63" s="20"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="22" t="n">
+      <c r="J63" s="8"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B64" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="C64" s="23" t="n">
-        <f aca="false">C20</f>
-        <v>0</v>
-      </c>
-      <c r="D64" s="28" t="str">
+      <c r="C64" s="20" t="n">
+        <f aca="false">C21</f>
+        <v>0</v>
+      </c>
+      <c r="D64" s="26" t="str">
         <f aca="false">IF(D83&lt;&gt;"",SQRT(D83/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
-      <c r="E64" s="11" t="str">
+      <c r="E64" s="10" t="str">
         <f aca="false">IF(D64&lt;&gt;"",MAX(1,ROUND(C11*D64,0)),"")</f>
         <v/>
       </c>
-      <c r="F64" s="11" t="str">
+      <c r="F64" s="10" t="str">
         <f aca="false">IF(AND(E64&lt;&gt;"",E63&lt;&gt;""),E64-E63,IF(E64&lt;&gt;"",E64,""))</f>
         <v/>
       </c>
-      <c r="G64" s="24" t="str">
+      <c r="G64" s="21" t="str">
         <f aca="false">IF(F64&lt;&gt;"",F64*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H64" s="26" t="str">
+      <c r="H64" s="24" t="str">
         <f aca="false">IF(G64&lt;&gt;"",G64*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I64" s="24" t="str">
+      <c r="I64" s="21" t="str">
         <f aca="false">IF(G64&lt;&gt;"",SUM(G59:G64),"")</f>
         <v/>
       </c>
-      <c r="J64" s="20"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="15" t="n">
+      <c r="J64" s="8"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B65" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="C65" s="23" t="n">
-        <f aca="false">C21</f>
-        <v>0</v>
-      </c>
-      <c r="D65" s="28" t="str">
+      <c r="C65" s="20" t="n">
+        <f aca="false">C22</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="26" t="str">
         <f aca="false">IF(D84&lt;&gt;"",SQRT(D84/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
-      <c r="E65" s="11" t="str">
+      <c r="E65" s="10" t="str">
         <f aca="false">IF(D65&lt;&gt;"",MAX(1,ROUND(C11*D65,0)),"")</f>
         <v/>
       </c>
-      <c r="F65" s="11" t="str">
+      <c r="F65" s="10" t="str">
         <f aca="false">IF(AND(E65&lt;&gt;"",E64&lt;&gt;""),E65-E64,IF(E65&lt;&gt;"",E65,""))</f>
         <v/>
       </c>
-      <c r="G65" s="24" t="str">
+      <c r="G65" s="21" t="str">
         <f aca="false">IF(F65&lt;&gt;"",F65*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H65" s="26" t="str">
+      <c r="H65" s="24" t="str">
         <f aca="false">IF(G65&lt;&gt;"",G65*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I65" s="24" t="str">
+      <c r="I65" s="21" t="str">
         <f aca="false">IF(G65&lt;&gt;"",SUM(G59:G65),"")</f>
         <v/>
       </c>
-      <c r="J65" s="20"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="22" t="n">
+      <c r="J65" s="8"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B66" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="C66" s="23" t="n">
-        <f aca="false">C22</f>
-        <v>0</v>
-      </c>
-      <c r="D66" s="28" t="str">
+      <c r="C66" s="20" t="n">
+        <f aca="false">C23</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="26" t="str">
         <f aca="false">IF(D85&lt;&gt;"",SQRT(D85/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
-      <c r="E66" s="11" t="str">
+      <c r="E66" s="10" t="str">
         <f aca="false">IF(D66&lt;&gt;"",MAX(1,ROUND(C11*D66,0)),"")</f>
         <v/>
       </c>
-      <c r="F66" s="11" t="str">
+      <c r="F66" s="10" t="str">
         <f aca="false">IF(AND(E66&lt;&gt;"",E65&lt;&gt;""),E66-E65,IF(E66&lt;&gt;"",E66,""))</f>
         <v/>
       </c>
-      <c r="G66" s="24" t="str">
+      <c r="G66" s="21" t="str">
         <f aca="false">IF(F66&lt;&gt;"",F66*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H66" s="26" t="str">
+      <c r="H66" s="24" t="str">
         <f aca="false">IF(G66&lt;&gt;"",G66*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I66" s="24" t="str">
+      <c r="I66" s="21" t="str">
         <f aca="false">IF(G66&lt;&gt;"",SUM(G59:G66),"")</f>
         <v/>
       </c>
-      <c r="J66" s="20"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="15" t="n">
+      <c r="J66" s="8"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B67" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="C67" s="23" t="n">
-        <f aca="false">C23</f>
-        <v>0</v>
-      </c>
-      <c r="D67" s="28" t="str">
+      <c r="C67" s="20" t="n">
+        <f aca="false">C24</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="26" t="str">
         <f aca="false">IF(D86&lt;&gt;"",SQRT(D86/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
-      <c r="E67" s="11" t="str">
+      <c r="E67" s="10" t="str">
         <f aca="false">IF(D67&lt;&gt;"",MAX(1,ROUND(C11*D67,0)),"")</f>
         <v/>
       </c>
-      <c r="F67" s="11" t="str">
+      <c r="F67" s="10" t="str">
         <f aca="false">IF(AND(E67&lt;&gt;"",E66&lt;&gt;""),E67-E66,IF(E67&lt;&gt;"",E67,""))</f>
         <v/>
       </c>
-      <c r="G67" s="24" t="str">
+      <c r="G67" s="21" t="str">
         <f aca="false">IF(F67&lt;&gt;"",F67*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H67" s="26" t="str">
+      <c r="H67" s="24" t="str">
         <f aca="false">IF(G67&lt;&gt;"",G67*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I67" s="24" t="str">
+      <c r="I67" s="21" t="str">
         <f aca="false">IF(G67&lt;&gt;"",SUM(G59:G67),"")</f>
         <v/>
       </c>
-      <c r="J67" s="20"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="22" t="n">
+      <c r="J67" s="8"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B68" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="C68" s="23" t="n">
-        <f aca="false">C24</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="28" t="str">
+      <c r="C68" s="20" t="n">
+        <f aca="false">C25</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="26" t="str">
         <f aca="false">IF(D87&lt;&gt;"",SQRT(D87/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
-      <c r="E68" s="11" t="str">
+      <c r="E68" s="10" t="str">
         <f aca="false">IF(D68&lt;&gt;"",MAX(1,ROUND(C11*D68,0)),"")</f>
         <v/>
       </c>
-      <c r="F68" s="11" t="str">
+      <c r="F68" s="10" t="str">
         <f aca="false">IF(AND(E68&lt;&gt;"",E67&lt;&gt;""),E68-E67,IF(E68&lt;&gt;"",E68,""))</f>
         <v/>
       </c>
-      <c r="G68" s="24" t="str">
+      <c r="G68" s="21" t="str">
         <f aca="false">IF(F68&lt;&gt;"",F68*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H68" s="26" t="str">
+      <c r="H68" s="24" t="str">
         <f aca="false">IF(G68&lt;&gt;"",G68*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I68" s="24" t="str">
+      <c r="I68" s="21" t="str">
         <f aca="false">IF(G68&lt;&gt;"",SUM(G59:G68),"")</f>
         <v/>
       </c>
-      <c r="J68" s="20"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="15" t="n">
+      <c r="J68" s="8"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B69" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="C69" s="23" t="n">
-        <f aca="false">C25</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="28" t="str">
+      <c r="C69" s="20" t="n">
+        <f aca="false">C26</f>
+        <v>0</v>
+      </c>
+      <c r="D69" s="26" t="str">
         <f aca="false">IF(D88&lt;&gt;"",SQRT(D88/MAX($C$7,0.000000001)),"")</f>
         <v/>
       </c>
-      <c r="E69" s="11" t="str">
+      <c r="E69" s="10" t="str">
         <f aca="false">IF(D69&lt;&gt;"",MAX(1,ROUND(C11*D69,0)),"")</f>
         <v/>
       </c>
-      <c r="F69" s="11" t="str">
+      <c r="F69" s="10" t="str">
         <f aca="false">IF(AND(E69&lt;&gt;"",E68&lt;&gt;""),E69-E68,IF(E69&lt;&gt;"",E69,""))</f>
         <v/>
       </c>
-      <c r="G69" s="24" t="str">
+      <c r="G69" s="21" t="str">
         <f aca="false">IF(F69&lt;&gt;"",F69*PI()*($C$9+$C$8),"")</f>
         <v/>
       </c>
-      <c r="H69" s="26" t="str">
+      <c r="H69" s="24" t="str">
         <f aca="false">IF(G69&lt;&gt;"",G69*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
         <v/>
       </c>
-      <c r="I69" s="24" t="str">
+      <c r="I69" s="21" t="str">
         <f aca="false">IF(G69&lt;&gt;"",SUM(G59:G69),"")</f>
         <v/>
       </c>
-      <c r="J69" s="20"/>
+      <c r="J69" s="8"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B71" s="31" t="s">
+      <c r="B71" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="C71" s="31"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="11" t="n">
+      <c r="C71" s="29"/>
+      <c r="D71" s="29"/>
+      <c r="E71" s="10" t="n">
         <f aca="false">IFERROR(MAX(E59:E69),"")</f>
         <v>80</v>
       </c>
-      <c r="H71" s="32" t="n">
+      <c r="H71" s="30" t="n">
         <f aca="false">IFERROR(SUM(H59:H69),"")</f>
         <v>448.154864197531</v>
       </c>
-      <c r="I71" s="33" t="n">
+      <c r="I71" s="31" t="n">
         <f aca="false">IFERROR(MAX(I59:I69),"")</f>
         <v>4134.33593212417</v>
       </c>
@@ -2539,9 +2544,9 @@
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
     </row>
-    <row r="77" customFormat="false" ht="38.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>40</v>
@@ -2565,464 +2570,464 @@
         <v>65</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="15" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B78" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="C78" s="23" t="n">
-        <f aca="false">C15</f>
+      <c r="C78" s="20" t="n">
+        <f aca="false">C16</f>
         <v>7.2</v>
       </c>
-      <c r="D78" s="26" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D15),D15&gt;0),SQRT(D15^2+IF(ISNUMBER(E15),E15,0)^2),"")</f>
+      <c r="D78" s="24" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D16),D16&gt;0),SQRT(D16^2+IF(ISNUMBER(E16),E16,0)^2),"")</f>
         <v>200</v>
       </c>
-      <c r="E78" s="27" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D15),D15&gt;0),IFERROR(DEGREES(ATAN2(D15,IF(ISNUMBER(E15),E15,0))),""),"")</f>
-        <v>0</v>
-      </c>
-      <c r="F78" s="29" t="n">
-        <f aca="false">IF(D78&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2))),999),"")</f>
+      <c r="E78" s="25" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D16),D16&gt;0),IFERROR(DEGREES(ATAN2(D16,IF(ISNUMBER(E16),E16,0))),""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="27" t="n">
+        <f aca="false">IF(D78&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D16),D16/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D78/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D16),D16/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D78/C7),0.000000001),0))^2))),999),"")</f>
         <v>1</v>
       </c>
-      <c r="G78" s="30" t="n">
-        <f aca="false">IF(D78&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+      <c r="G78" s="28" t="n">
+        <f aca="false">IF(D78&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D16),D16/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D78/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>180</v>
       </c>
-      <c r="H78" s="29" t="n">
-        <f aca="false">IF(D78&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2))),0),"")</f>
+      <c r="H78" s="27" t="n">
+        <f aca="false">IF(D78&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D16),D16/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D78/C7),0.000000001),0))^2))),0),"")</f>
         <v>-0</v>
       </c>
-      <c r="I78" s="29" t="n">
-        <f aca="false">IF(D78&lt;&gt;"",IFERROR(((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E15),E15/MAX((D78/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="22" t="n">
+      <c r="I78" s="27" t="n">
+        <f aca="false">IF(D78&lt;&gt;"",IFERROR(((IF(ISNUMBER(D16),D16/MAX((D78/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D78/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D78/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D78/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B79" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="C79" s="23" t="n">
-        <f aca="false">C16</f>
+      <c r="C79" s="20" t="n">
+        <f aca="false">C17</f>
         <v>10</v>
       </c>
-      <c r="D79" s="26" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D16),D16&gt;0),SQRT(D16^2+IF(ISNUMBER(E16),E16,0)^2),"")</f>
+      <c r="D79" s="24" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D17),D17&gt;0),SQRT(D17^2+IF(ISNUMBER(E17),E17,0)^2),"")</f>
         <v>316.227766016838</v>
       </c>
-      <c r="E79" s="27" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D16),D16&gt;0),IFERROR(DEGREES(ATAN2(D16,IF(ISNUMBER(E16),E16,0))),""),"")</f>
+      <c r="E79" s="25" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D17),D17&gt;0),IFERROR(DEGREES(ATAN2(D17,IF(ISNUMBER(E17),E17,0))),""),"")</f>
         <v>18.434948822922</v>
       </c>
-      <c r="F79" s="29" t="n">
-        <f aca="false">IF(D79&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2))),999),"")</f>
+      <c r="F79" s="27" t="n">
+        <f aca="false">IF(D79&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D17),D17/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D79/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D17),D17/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D79/C7),0.000000001),0))^2))),999),"")</f>
         <v>1.38742588672279</v>
       </c>
-      <c r="G79" s="30" t="n">
-        <f aca="false">IF(D79&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+      <c r="G79" s="28" t="n">
+        <f aca="false">IF(D79&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D17),D17/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D79/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>15.7948252576199</v>
       </c>
-      <c r="H79" s="29" t="n">
-        <f aca="false">IF(D79&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2))),0),"")</f>
+      <c r="H79" s="27" t="n">
+        <f aca="false">IF(D79&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D17),D17/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D79/C7),0.000000001),0))^2))),0),"")</f>
         <v>0.115900124973496</v>
       </c>
-      <c r="I79" s="29" t="n">
-        <f aca="false">IF(D79&lt;&gt;"",IFERROR(((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E16),E16/MAX((D79/C7),0.000000001),0))^2)*100,0),"")</f>
+      <c r="I79" s="27" t="n">
+        <f aca="false">IF(D79&lt;&gt;"",IFERROR(((IF(ISNUMBER(D17),D17/MAX((D79/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D79/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D79/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D79/C7),0.000000001),0))^2)*100,0),"")</f>
         <v>2.6334038989724</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="15" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B80" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="C80" s="23" t="n">
-        <f aca="false">C17</f>
+      <c r="C80" s="20" t="n">
+        <f aca="false">C18</f>
         <v>18</v>
       </c>
-      <c r="D80" s="26" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D17),D17&gt;0),SQRT(D17^2+IF(ISNUMBER(E17),E17,0)^2),"")</f>
+      <c r="D80" s="24" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D18),D18&gt;0),SQRT(D18^2+IF(ISNUMBER(E18),E18,0)^2),"")</f>
         <v>457.055795281058</v>
       </c>
-      <c r="E80" s="27" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D17),D17&gt;0),IFERROR(DEGREES(ATAN2(D17,IF(ISNUMBER(E17),E17,0))),""),"")</f>
+      <c r="E80" s="25" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D18),D18&gt;0),IFERROR(DEGREES(ATAN2(D18,IF(ISNUMBER(E18),E18,0))),""),"")</f>
         <v>-10.0805979875423</v>
       </c>
-      <c r="F80" s="29" t="n">
-        <f aca="false">IF(D80&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2))),999),"")</f>
+      <c r="F80" s="27" t="n">
+        <f aca="false">IF(D80&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D18),D18/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D80/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D18),D18/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D80/C7),0.000000001),0))^2))),999),"")</f>
         <v>1.19345732284679</v>
       </c>
-      <c r="G80" s="30" t="n">
-        <f aca="false">IF(D80&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+      <c r="G80" s="28" t="n">
+        <f aca="false">IF(D80&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D18),D18/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D80/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>21.0908803086925</v>
       </c>
-      <c r="H80" s="29" t="n">
-        <f aca="false">IF(D80&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2))),0),"")</f>
+      <c r="H80" s="27" t="n">
+        <f aca="false">IF(D80&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D18),D18/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D80/C7),0.000000001),0))^2))),0),"")</f>
         <v>0.0339149298724391</v>
       </c>
-      <c r="I80" s="29" t="n">
-        <f aca="false">IF(D80&lt;&gt;"",IFERROR(((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E17),E17/MAX((D80/C7),0.000000001),0))^2)*100,0),"")</f>
+      <c r="I80" s="27" t="n">
+        <f aca="false">IF(D80&lt;&gt;"",IFERROR(((IF(ISNUMBER(D18),D18/MAX((D80/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D80/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D80/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D80/C7),0.000000001),0))^2)*100,0),"")</f>
         <v>0.777878860128034</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="22" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B81" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="C81" s="23" t="n">
-        <f aca="false">C18</f>
+      <c r="C81" s="20" t="n">
+        <f aca="false">C19</f>
         <v>28</v>
       </c>
-      <c r="D81" s="26" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D18),D18&gt;0),SQRT(D18^2+IF(ISNUMBER(E18),E18,0)^2),"")</f>
+      <c r="D81" s="24" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D19),D19&gt;0),SQRT(D19^2+IF(ISNUMBER(E19),E19,0)^2),"")</f>
         <v>800</v>
       </c>
-      <c r="E81" s="27" t="n">
-        <f aca="false">IF(AND(ISNUMBER(D18),D18&gt;0),IFERROR(DEGREES(ATAN2(D18,IF(ISNUMBER(E18),E18,0))),""),"")</f>
-        <v>0</v>
-      </c>
-      <c r="F81" s="29" t="n">
-        <f aca="false">IF(D81&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2))),999),"")</f>
+      <c r="E81" s="25" t="n">
+        <f aca="false">IF(AND(ISNUMBER(D19),D19&gt;0),IFERROR(DEGREES(ATAN2(D19,IF(ISNUMBER(E19),E19,0))),""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="F81" s="27" t="n">
+        <f aca="false">IF(D81&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D19),D19/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D81/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D19),D19/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D81/C7),0.000000001),0))^2))),999),"")</f>
         <v>1</v>
       </c>
-      <c r="G81" s="30" t="n">
-        <f aca="false">IF(D81&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+      <c r="G81" s="28" t="n">
+        <f aca="false">IF(D81&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D19),D19/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D81/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
         <v>180</v>
       </c>
-      <c r="H81" s="29" t="n">
-        <f aca="false">IF(D81&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2))),0),"")</f>
+      <c r="H81" s="27" t="n">
+        <f aca="false">IF(D81&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D19),D19/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D81/C7),0.000000001),0))^2))),0),"")</f>
         <v>-0</v>
       </c>
-      <c r="I81" s="29" t="n">
-        <f aca="false">IF(D81&lt;&gt;"",IFERROR(((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D18),D18/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E18),E18/MAX((D81/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="15" t="n">
+      <c r="I81" s="27" t="n">
+        <f aca="false">IF(D81&lt;&gt;"",IFERROR(((IF(ISNUMBER(D19),D19/MAX((D81/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D81/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D81/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D81/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B82" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="C82" s="23" t="n">
-        <f aca="false">C19</f>
-        <v>0</v>
-      </c>
-      <c r="D82" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D19),D19&gt;0),SQRT(D19^2+IF(ISNUMBER(E19),E19,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="27" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D19),D19&gt;0),IFERROR(DEGREES(ATAN2(D19,IF(ISNUMBER(E19),E19,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="F82" s="29" t="str">
-        <f aca="false">IF(D82&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G82" s="30" t="str">
-        <f aca="false">IF(D82&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H82" s="29" t="str">
-        <f aca="false">IF(D82&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I82" s="29" t="str">
-        <f aca="false">IF(D82&lt;&gt;"",IFERROR(((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D19),D19/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E19),E19/MAX((D82/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="22" t="n">
+      <c r="C82" s="20" t="n">
+        <f aca="false">C20</f>
+        <v>0</v>
+      </c>
+      <c r="D82" s="24" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D20),D20&gt;0),SQRT(D20^2+IF(ISNUMBER(E20),E20,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="25" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D20),D20&gt;0),IFERROR(DEGREES(ATAN2(D20,IF(ISNUMBER(E20),E20,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="27" t="str">
+        <f aca="false">IF(D82&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D20),D20/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D82/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D20),D20/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D82/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G82" s="28" t="str">
+        <f aca="false">IF(D82&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D20),D20/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D82/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H82" s="27" t="str">
+        <f aca="false">IF(D82&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D20),D20/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D82/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I82" s="27" t="str">
+        <f aca="false">IF(D82&lt;&gt;"",IFERROR(((IF(ISNUMBER(D20),D20/MAX((D82/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D82/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D82/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D82/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B83" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C83" s="23" t="n">
-        <f aca="false">C20</f>
-        <v>0</v>
-      </c>
-      <c r="D83" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D20),D20&gt;0),SQRT(D20^2+IF(ISNUMBER(E20),E20,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="27" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D20),D20&gt;0),IFERROR(DEGREES(ATAN2(D20,IF(ISNUMBER(E20),E20,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="F83" s="29" t="str">
-        <f aca="false">IF(D83&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G83" s="30" t="str">
-        <f aca="false">IF(D83&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H83" s="29" t="str">
-        <f aca="false">IF(D83&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I83" s="29" t="str">
-        <f aca="false">IF(D83&lt;&gt;"",IFERROR(((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D20),D20/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E20),E20/MAX((D83/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="15" t="n">
+      <c r="C83" s="20" t="n">
+        <f aca="false">C21</f>
+        <v>0</v>
+      </c>
+      <c r="D83" s="24" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D21),D21&gt;0),SQRT(D21^2+IF(ISNUMBER(E21),E21,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="25" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D21),D21&gt;0),IFERROR(DEGREES(ATAN2(D21,IF(ISNUMBER(E21),E21,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="27" t="str">
+        <f aca="false">IF(D83&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D21),D21/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D83/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D21),D21/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D83/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G83" s="28" t="str">
+        <f aca="false">IF(D83&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D21),D21/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D83/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H83" s="27" t="str">
+        <f aca="false">IF(D83&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D21),D21/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D83/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I83" s="27" t="str">
+        <f aca="false">IF(D83&lt;&gt;"",IFERROR(((IF(ISNUMBER(D21),D21/MAX((D83/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D83/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D83/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D83/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B84" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="C84" s="23" t="n">
-        <f aca="false">C21</f>
-        <v>0</v>
-      </c>
-      <c r="D84" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D21),D21&gt;0),SQRT(D21^2+IF(ISNUMBER(E21),E21,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="E84" s="27" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D21),D21&gt;0),IFERROR(DEGREES(ATAN2(D21,IF(ISNUMBER(E21),E21,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="F84" s="29" t="str">
-        <f aca="false">IF(D84&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G84" s="30" t="str">
-        <f aca="false">IF(D84&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H84" s="29" t="str">
-        <f aca="false">IF(D84&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I84" s="29" t="str">
-        <f aca="false">IF(D84&lt;&gt;"",IFERROR(((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D21),D21/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E21),E21/MAX((D84/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="22" t="n">
+      <c r="C84" s="20" t="n">
+        <f aca="false">C22</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="24" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D22),D22&gt;0),SQRT(D22^2+IF(ISNUMBER(E22),E22,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="25" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D22),D22&gt;0),IFERROR(DEGREES(ATAN2(D22,IF(ISNUMBER(E22),E22,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="27" t="str">
+        <f aca="false">IF(D84&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D22),D22/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D84/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D22),D22/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D84/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G84" s="28" t="str">
+        <f aca="false">IF(D84&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D22),D22/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D84/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H84" s="27" t="str">
+        <f aca="false">IF(D84&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D22),D22/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D84/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I84" s="27" t="str">
+        <f aca="false">IF(D84&lt;&gt;"",IFERROR(((IF(ISNUMBER(D22),D22/MAX((D84/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D84/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D84/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D84/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B85" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="C85" s="23" t="n">
-        <f aca="false">C22</f>
-        <v>0</v>
-      </c>
-      <c r="D85" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D22),D22&gt;0),SQRT(D22^2+IF(ISNUMBER(E22),E22,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="E85" s="27" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D22),D22&gt;0),IFERROR(DEGREES(ATAN2(D22,IF(ISNUMBER(E22),E22,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="F85" s="29" t="str">
-        <f aca="false">IF(D85&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G85" s="30" t="str">
-        <f aca="false">IF(D85&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H85" s="29" t="str">
-        <f aca="false">IF(D85&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I85" s="29" t="str">
-        <f aca="false">IF(D85&lt;&gt;"",IFERROR(((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D22),D22/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E22),E22/MAX((D85/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="15" t="n">
+      <c r="C85" s="20" t="n">
+        <f aca="false">C23</f>
+        <v>0</v>
+      </c>
+      <c r="D85" s="24" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D23),D23&gt;0),SQRT(D23^2+IF(ISNUMBER(E23),E23,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="25" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D23),D23&gt;0),IFERROR(DEGREES(ATAN2(D23,IF(ISNUMBER(E23),E23,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="27" t="str">
+        <f aca="false">IF(D85&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D23),D23/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D85/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D23),D23/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D85/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G85" s="28" t="str">
+        <f aca="false">IF(D85&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D23),D23/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D85/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H85" s="27" t="str">
+        <f aca="false">IF(D85&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D23),D23/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D85/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I85" s="27" t="str">
+        <f aca="false">IF(D85&lt;&gt;"",IFERROR(((IF(ISNUMBER(D23),D23/MAX((D85/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D85/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D85/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D85/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B86" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="C86" s="23" t="n">
-        <f aca="false">C23</f>
-        <v>0</v>
-      </c>
-      <c r="D86" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D23),D23&gt;0),SQRT(D23^2+IF(ISNUMBER(E23),E23,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="E86" s="27" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D23),D23&gt;0),IFERROR(DEGREES(ATAN2(D23,IF(ISNUMBER(E23),E23,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="F86" s="29" t="str">
-        <f aca="false">IF(D86&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G86" s="30" t="str">
-        <f aca="false">IF(D86&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H86" s="29" t="str">
-        <f aca="false">IF(D86&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I86" s="29" t="str">
-        <f aca="false">IF(D86&lt;&gt;"",IFERROR(((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D23),D23/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E23),E23/MAX((D86/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="22" t="n">
+      <c r="C86" s="20" t="n">
+        <f aca="false">C24</f>
+        <v>0</v>
+      </c>
+      <c r="D86" s="24" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D24),D24&gt;0),SQRT(D24^2+IF(ISNUMBER(E24),E24,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E86" s="25" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D24),D24&gt;0),IFERROR(DEGREES(ATAN2(D24,IF(ISNUMBER(E24),E24,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="27" t="str">
+        <f aca="false">IF(D86&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D24),D24/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D86/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D24),D24/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D86/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G86" s="28" t="str">
+        <f aca="false">IF(D86&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D24),D24/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D86/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H86" s="27" t="str">
+        <f aca="false">IF(D86&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D24),D24/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D86/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I86" s="27" t="str">
+        <f aca="false">IF(D86&lt;&gt;"",IFERROR(((IF(ISNUMBER(D24),D24/MAX((D86/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D86/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D86/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D86/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B87" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="C87" s="23" t="n">
-        <f aca="false">C24</f>
-        <v>0</v>
-      </c>
-      <c r="D87" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D24),D24&gt;0),SQRT(D24^2+IF(ISNUMBER(E24),E24,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="E87" s="27" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D24),D24&gt;0),IFERROR(DEGREES(ATAN2(D24,IF(ISNUMBER(E24),E24,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="F87" s="29" t="str">
-        <f aca="false">IF(D87&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G87" s="30" t="str">
-        <f aca="false">IF(D87&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H87" s="29" t="str">
-        <f aca="false">IF(D87&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I87" s="29" t="str">
-        <f aca="false">IF(D87&lt;&gt;"",IFERROR(((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D24),D24/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E24),E24/MAX((D87/C7),0.000000001),0))^2)*100,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="15" t="n">
+      <c r="C87" s="20" t="n">
+        <f aca="false">C25</f>
+        <v>0</v>
+      </c>
+      <c r="D87" s="24" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D25),D25&gt;0),SQRT(D25^2+IF(ISNUMBER(E25),E25,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E87" s="25" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D25),D25&gt;0),IFERROR(DEGREES(ATAN2(D25,IF(ISNUMBER(E25),E25,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="27" t="str">
+        <f aca="false">IF(D87&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D25),D25/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D87/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D25),D25/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D87/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G87" s="28" t="str">
+        <f aca="false">IF(D87&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D25),D25/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D87/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H87" s="27" t="str">
+        <f aca="false">IF(D87&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D25),D25/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D87/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I87" s="27" t="str">
+        <f aca="false">IF(D87&lt;&gt;"",IFERROR(((IF(ISNUMBER(D25),D25/MAX((D87/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D87/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D87/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D87/C7),0.000000001),0))^2)*100,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B88" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="C88" s="23" t="n">
-        <f aca="false">C25</f>
-        <v>0</v>
-      </c>
-      <c r="D88" s="26" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D25),D25&gt;0),SQRT(D25^2+IF(ISNUMBER(E25),E25,0)^2),"")</f>
-        <v/>
-      </c>
-      <c r="E88" s="27" t="str">
-        <f aca="false">IF(AND(ISNUMBER(D25),D25&gt;0),IFERROR(DEGREES(ATAN2(D25,IF(ISNUMBER(E25),E25,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="F88" s="29" t="str">
-        <f aca="false">IF(D88&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2))),999),"")</f>
-        <v/>
-      </c>
-      <c r="G88" s="30" t="str">
-        <f aca="false">IF(D88&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v/>
-      </c>
-      <c r="H88" s="29" t="str">
-        <f aca="false">IF(D88&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2))),0),"")</f>
-        <v/>
-      </c>
-      <c r="I88" s="29" t="str">
-        <f aca="false">IF(D88&lt;&gt;"",IFERROR(((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D25),D25/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E25),E25/MAX((D88/C7),0.000000001),0))^2)*100,0),"")</f>
+      <c r="C88" s="20" t="n">
+        <f aca="false">C26</f>
+        <v>0</v>
+      </c>
+      <c r="D88" s="24" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D26),D26&gt;0),SQRT(D26^2+IF(ISNUMBER(E26),E26,0)^2),"")</f>
+        <v/>
+      </c>
+      <c r="E88" s="25" t="str">
+        <f aca="false">IF(AND(ISNUMBER(D26),D26&gt;0),IFERROR(DEGREES(ATAN2(D26,IF(ISNUMBER(E26),E26,0))),""),"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="27" t="str">
+        <f aca="false">IF(D88&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D26),D26/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E26),E26/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D26),D26/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E26),E26/MAX((D88/C7),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D26),D26/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E26),E26/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D26),D26/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E26),E26/MAX((D88/C7),0.000000001),0))^2))),999),"")</f>
+        <v/>
+      </c>
+      <c r="G88" s="28" t="str">
+        <f aca="false">IF(D88&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D26),D26/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E26),E26/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D26),D26/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E26),E26/MAX((D88/C7),0.000000001),0))^2)),0.000000001)),0),"")</f>
+        <v/>
+      </c>
+      <c r="H88" s="27" t="str">
+        <f aca="false">IF(D88&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D26),D26/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E26),E26/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D26),D26/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E26),E26/MAX((D88/C7),0.000000001),0))^2))),0),"")</f>
+        <v/>
+      </c>
+      <c r="I88" s="27" t="str">
+        <f aca="false">IF(D88&lt;&gt;"",IFERROR(((IF(ISNUMBER(D26),D26/MAX((D88/C7),0.000000001),C7)-C7)^2+(IF(ISNUMBER(E26),E26/MAX((D88/C7),0.000000001),0))^2)/((IF(ISNUMBER(D26),D26/MAX((D88/C7),0.000000001),C7)+C7)^2+(IF(ISNUMBER(E26),E26/MAX((D88/C7),0.000000001),0))^2)*100,0),"")</f>
         <v/>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B90" s="34" t="s">
+      <c r="B90" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C90" s="34"/>
-      <c r="D90" s="34"/>
-      <c r="E90" s="34"/>
-      <c r="F90" s="34"/>
-      <c r="G90" s="34"/>
-      <c r="H90" s="34"/>
-      <c r="I90" s="34"/>
+      <c r="C90" s="32"/>
+      <c r="D90" s="32"/>
+      <c r="E90" s="32"/>
+      <c r="F90" s="32"/>
+      <c r="G90" s="32"/>
+      <c r="H90" s="32"/>
+      <c r="I90" s="32"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B91" s="35" t="s">
+      <c r="B91" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="C91" s="35"/>
-      <c r="D91" s="35"/>
-      <c r="E91" s="35"/>
-      <c r="F91" s="35"/>
-      <c r="G91" s="35"/>
-      <c r="H91" s="35"/>
-      <c r="I91" s="35"/>
+      <c r="C91" s="33"/>
+      <c r="D91" s="33"/>
+      <c r="E91" s="33"/>
+      <c r="F91" s="33"/>
+      <c r="G91" s="33"/>
+      <c r="H91" s="33"/>
+      <c r="I91" s="33"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B92" s="35" t="s">
+      <c r="B92" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C92" s="35"/>
-      <c r="D92" s="35"/>
-      <c r="E92" s="35"/>
-      <c r="F92" s="35"/>
-      <c r="G92" s="35"/>
-      <c r="H92" s="35"/>
-      <c r="I92" s="35"/>
+      <c r="C92" s="33"/>
+      <c r="D92" s="33"/>
+      <c r="E92" s="33"/>
+      <c r="F92" s="33"/>
+      <c r="G92" s="33"/>
+      <c r="H92" s="33"/>
+      <c r="I92" s="33"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B93" s="35" t="s">
+      <c r="B93" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C93" s="35"/>
-      <c r="D93" s="35"/>
-      <c r="E93" s="35"/>
-      <c r="F93" s="35"/>
-      <c r="G93" s="35"/>
-      <c r="H93" s="35"/>
-      <c r="I93" s="35"/>
+      <c r="C93" s="33"/>
+      <c r="D93" s="33"/>
+      <c r="E93" s="33"/>
+      <c r="F93" s="33"/>
+      <c r="G93" s="33"/>
+      <c r="H93" s="33"/>
+      <c r="I93" s="33"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B94" s="35" t="s">
+      <c r="B94" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="C94" s="35"/>
-      <c r="D94" s="35"/>
-      <c r="E94" s="35"/>
-      <c r="F94" s="35"/>
-      <c r="G94" s="35"/>
-      <c r="H94" s="35"/>
-      <c r="I94" s="35"/>
+      <c r="C94" s="33"/>
+      <c r="D94" s="33"/>
+      <c r="E94" s="33"/>
+      <c r="F94" s="33"/>
+      <c r="G94" s="33"/>
+      <c r="H94" s="33"/>
+      <c r="I94" s="33"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B95" s="35" t="s">
+      <c r="B95" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="C95" s="35"/>
-      <c r="D95" s="35"/>
-      <c r="E95" s="35"/>
-      <c r="F95" s="35"/>
-      <c r="G95" s="35"/>
-      <c r="H95" s="35"/>
-      <c r="I95" s="35"/>
+      <c r="C95" s="33"/>
+      <c r="D95" s="33"/>
+      <c r="E95" s="33"/>
+      <c r="F95" s="33"/>
+      <c r="G95" s="33"/>
+      <c r="H95" s="33"/>
+      <c r="I95" s="33"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B96" s="35" t="s">
+      <c r="B96" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="C96" s="35"/>
-      <c r="D96" s="35"/>
-      <c r="E96" s="35"/>
-      <c r="F96" s="35"/>
-      <c r="G96" s="35"/>
-      <c r="H96" s="35"/>
-      <c r="I96" s="35"/>
+      <c r="C96" s="33"/>
+      <c r="D96" s="33"/>
+      <c r="E96" s="33"/>
+      <c r="F96" s="33"/>
+      <c r="G96" s="33"/>
+      <c r="H96" s="33"/>
+      <c r="I96" s="33"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B97" s="35" t="s">
+      <c r="B97" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C97" s="35"/>
-      <c r="D97" s="35"/>
-      <c r="E97" s="35"/>
-      <c r="F97" s="35"/>
-      <c r="G97" s="35"/>
-      <c r="H97" s="35"/>
-      <c r="I97" s="35"/>
+      <c r="C97" s="33"/>
+      <c r="D97" s="33"/>
+      <c r="E97" s="33"/>
+      <c r="F97" s="33"/>
+      <c r="G97" s="33"/>
+      <c r="H97" s="33"/>
+      <c r="I97" s="33"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B99" s="2" t="s">
@@ -3074,7 +3079,7 @@
       <c r="B104" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C104" s="36" t="n">
+      <c r="C104" s="34" t="n">
         <f aca="false">C9</f>
         <v>16</v>
       </c>
@@ -3091,7 +3096,7 @@
       <c r="B105" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C105" s="36" t="n">
+      <c r="C105" s="34" t="n">
         <f aca="false">C8</f>
         <v>0.45</v>
       </c>
@@ -3108,9 +3113,9 @@
       <c r="B106" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C106" s="36" t="n">
-        <f aca="false">MAX(C8*1.1,C8+0.05)</f>
-        <v>0.5</v>
+      <c r="C106" s="34" t="n">
+        <f aca="false">$C$8+$C$12</f>
+        <v>5.45</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>11</v>
@@ -3125,7 +3130,7 @@
       <c r="B107" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C107" s="23" t="n">
+      <c r="C107" s="20" t="n">
         <f aca="false">IFERROR(IF(E71&lt;&gt;"",VALUE(E71),10),10)</f>
         <v>80</v>
       </c>
@@ -3168,9 +3173,9 @@
       <c r="B111" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C111" s="25" t="n">
+      <c r="C111" s="22" t="n">
         <f aca="false">IFERROR(IF(C107&gt;0,(C107-1)*C106+C105,""),"")</f>
-        <v>39.95</v>
+        <v>431</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>11</v>
@@ -3181,11 +3186,11 @@
       <c r="F111" s="9"/>
       <c r="G111" s="9"/>
     </row>
-    <row r="112" customFormat="false" ht="26.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B112" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="C112" s="25" t="n">
+      <c r="C112" s="22" t="n">
         <f aca="false">(C104+C105)/2</f>
         <v>8.225</v>
       </c>
@@ -3202,7 +3207,7 @@
       <c r="B113" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C113" s="25" t="n">
+      <c r="C113" s="22" t="n">
         <f aca="false">((C104+C105)/2)/25.4</f>
         <v>0.323818897637795</v>
       </c>
@@ -3219,9 +3224,9 @@
       <c r="B114" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C114" s="25" t="n">
+      <c r="C114" s="22" t="n">
         <f aca="false">IFERROR(C111/25.4,"")</f>
-        <v>1.57283464566929</v>
+        <v>16.9685039370079</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>93</v>
@@ -3236,9 +3241,9 @@
       <c r="B115" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C115" s="25" t="n">
+      <c r="C115" s="22" t="n">
         <f aca="false">IFERROR((C113^2*C107^2)/(9*C113+10*C114),"")</f>
-        <v>35.9977335339286</v>
+        <v>3.88816824074988</v>
       </c>
       <c r="D115" s="8" t="s">
         <v>37</v>
@@ -3253,9 +3258,9 @@
       <c r="B116" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C116" s="25" t="n">
-        <f aca="false">IFERROR(2*PI()*C32*1000000*C115/1000000,"")</f>
-        <v>1628.49909911145</v>
+      <c r="C116" s="22" t="str">
+        <f aca="false">IFERROR(2*PI()*minifs($C$16:$C$26,$F$16:$F$26,"YES")*1000000*C115/1000000,"")</f>
+        <v/>
       </c>
       <c r="D116" s="8" t="s">
         <v>8</v>
@@ -3270,9 +3275,9 @@
       <c r="B117" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C117" s="25" t="n">
-        <f aca="false">IFERROR(4*MIN(D78:D88)/(2*PI()*C32*1000000)*1000000,"")</f>
-        <v>17.6838825657662</v>
+      <c r="C117" s="22" t="str">
+        <f aca="false">IFERROR(4*MIN(D78:D88)/(2*PI()*minifs($C$16:$C$26,$F$16:$F$26,"YES")*1000000)*1000000,"")</f>
+        <v/>
       </c>
       <c r="D117" s="8" t="s">
         <v>37</v>
@@ -3287,9 +3292,9 @@
       <c r="B118" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="C118" s="25" t="str">
+      <c r="C118" s="22" t="str">
         <f aca="false">IFERROR(IF(AND(ISNUMBER(C115),ISNUMBER(C117)),IF(C115&gt;=C117,"✔ YES","✘ INCREASE TURNS"),"—"),"")</f>
-        <v>✔ YES</v>
+        <v>—</v>
       </c>
       <c r="D118" s="8" t="s">
         <v>103</v>
@@ -3300,648 +3305,648 @@
       <c r="F118" s="9"/>
       <c r="G118" s="9"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="37" t="s">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B121" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="C121" s="37"/>
-      <c r="D121" s="37"/>
-      <c r="E121" s="37"/>
-      <c r="F121" s="37"/>
-      <c r="G121" s="37"/>
-      <c r="H121" s="37"/>
-      <c r="I121" s="37"/>
-      <c r="J121" s="37"/>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="38" t="s">
+      <c r="C121" s="35"/>
+      <c r="D121" s="35"/>
+      <c r="E121" s="35"/>
+      <c r="F121" s="35"/>
+      <c r="G121" s="35"/>
+      <c r="H121" s="35"/>
+      <c r="I121" s="35"/>
+      <c r="J121" s="35"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B122" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="C122" s="38"/>
-      <c r="D122" s="38"/>
-      <c r="E122" s="38"/>
-      <c r="F122" s="38"/>
-      <c r="G122" s="38"/>
-      <c r="H122" s="38"/>
-      <c r="I122" s="38"/>
-      <c r="J122" s="38"/>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="39" t="s">
+      <c r="C122" s="36"/>
+      <c r="D122" s="36"/>
+      <c r="E122" s="36"/>
+      <c r="F122" s="36"/>
+      <c r="G122" s="36"/>
+      <c r="H122" s="36"/>
+      <c r="I122" s="36"/>
+      <c r="J122" s="36"/>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B124" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="C124" s="39"/>
-      <c r="D124" s="39"/>
-      <c r="E124" s="39"/>
-      <c r="F124" s="39"/>
-      <c r="G124" s="39"/>
-      <c r="H124" s="39"/>
-      <c r="I124" s="39"/>
-      <c r="J124" s="39"/>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="40" t="s">
+      <c r="C124" s="37"/>
+      <c r="D124" s="37"/>
+      <c r="E124" s="37"/>
+      <c r="F124" s="37"/>
+      <c r="G124" s="37"/>
+      <c r="H124" s="37"/>
+      <c r="I124" s="37"/>
+      <c r="J124" s="37"/>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B125" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="C125" s="40"/>
-      <c r="D125" s="40"/>
-      <c r="E125" s="40"/>
-      <c r="F125" s="40"/>
-      <c r="G125" s="40"/>
-      <c r="H125" s="40"/>
-      <c r="I125" s="40"/>
-      <c r="J125" s="40"/>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="40" t="s">
+      <c r="C125" s="38"/>
+      <c r="D125" s="38"/>
+      <c r="E125" s="38"/>
+      <c r="F125" s="38"/>
+      <c r="G125" s="38"/>
+      <c r="H125" s="38"/>
+      <c r="I125" s="38"/>
+      <c r="J125" s="38"/>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B126" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="C126" s="40"/>
-      <c r="D126" s="40"/>
-      <c r="E126" s="40"/>
-      <c r="F126" s="40"/>
-      <c r="G126" s="40"/>
-      <c r="H126" s="40"/>
-      <c r="I126" s="40"/>
-      <c r="J126" s="40"/>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B127" s="40" t="s">
+      <c r="C126" s="38"/>
+      <c r="D126" s="38"/>
+      <c r="E126" s="38"/>
+      <c r="F126" s="38"/>
+      <c r="G126" s="38"/>
+      <c r="H126" s="38"/>
+      <c r="I126" s="38"/>
+      <c r="J126" s="38"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B127" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="C127" s="40"/>
-      <c r="D127" s="40"/>
-      <c r="E127" s="40"/>
-      <c r="F127" s="40"/>
-      <c r="G127" s="40"/>
-      <c r="H127" s="40"/>
-      <c r="I127" s="40"/>
-      <c r="J127" s="40"/>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="40" t="s">
+      <c r="C127" s="38"/>
+      <c r="D127" s="38"/>
+      <c r="E127" s="38"/>
+      <c r="F127" s="38"/>
+      <c r="G127" s="38"/>
+      <c r="H127" s="38"/>
+      <c r="I127" s="38"/>
+      <c r="J127" s="38"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B128" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C128" s="40"/>
-      <c r="D128" s="40"/>
-      <c r="E128" s="40"/>
-      <c r="F128" s="40"/>
-      <c r="G128" s="40"/>
-      <c r="H128" s="40"/>
-      <c r="I128" s="40"/>
-      <c r="J128" s="40"/>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B129" s="40" t="s">
+      <c r="C128" s="38"/>
+      <c r="D128" s="38"/>
+      <c r="E128" s="38"/>
+      <c r="F128" s="38"/>
+      <c r="G128" s="38"/>
+      <c r="H128" s="38"/>
+      <c r="I128" s="38"/>
+      <c r="J128" s="38"/>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B129" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="C129" s="40"/>
-      <c r="D129" s="40"/>
-      <c r="E129" s="40"/>
-      <c r="F129" s="40"/>
-      <c r="G129" s="40"/>
-      <c r="H129" s="40"/>
-      <c r="I129" s="40"/>
-      <c r="J129" s="40"/>
-    </row>
-    <row r="131" customFormat="false" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C131" s="41" t="s">
+      <c r="C129" s="38"/>
+      <c r="D129" s="38"/>
+      <c r="E129" s="38"/>
+      <c r="F129" s="38"/>
+      <c r="G129" s="38"/>
+      <c r="H129" s="38"/>
+      <c r="I129" s="38"/>
+      <c r="J129" s="38"/>
+    </row>
+    <row r="131" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B131" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C131" s="39" t="s">
         <v>113</v>
       </c>
-      <c r="D131" s="41" t="s">
+      <c r="D131" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="E131" s="41" t="s">
+      <c r="E131" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="F131" s="41" t="s">
+      <c r="F131" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="G131" s="41" t="s">
+      <c r="G131" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="H131" s="41" t="s">
+      <c r="H131" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="I131" s="41" t="s">
+      <c r="I131" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="J131" s="41" t="s">
+      <c r="J131" s="39" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B132" s="42" t="n">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B132" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="C132" s="43" t="n">
-        <f aca="false">C15</f>
+      <c r="C132" s="41" t="n">
+        <f aca="false">C16</f>
         <v>7.2</v>
       </c>
-      <c r="D132" s="43" t="n">
-        <f aca="false">D15</f>
+      <c r="D132" s="41" t="n">
+        <f aca="false">D16</f>
         <v>200</v>
       </c>
-      <c r="E132" s="43" t="n">
-        <f aca="false">IF(ISNUMBER(E15),E15,"—")</f>
-        <v>0</v>
-      </c>
-      <c r="F132" s="43" t="n">
+      <c r="E132" s="41" t="n">
+        <f aca="false">IF(ISNUMBER(E16),E16,"—")</f>
+        <v>0</v>
+      </c>
+      <c r="F132" s="41" t="n">
         <f aca="false">IF(ISNUMBER(E78),E78,"—")</f>
         <v>0</v>
       </c>
-      <c r="G132" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D15),D15&gt;0),IF(($C$7*IF(ISNUMBER(E15),E15,0)/D78)&gt;0,($C$7*IF(ISNUMBER(E15),E15,0)/D78)/(2*PI()*C15*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H132" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D15),D15&gt;0),IF(($C$7*IF(ISNUMBER(E15),E15,0)/D78)&lt;0,1/((2*PI()*C15*1000000)*ABS(($C$7*IF(ISNUMBER(E15),E15,0)/D78)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I132" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D15),D15&gt;0),IF((D78*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))&lt;0,-1/((2*PI()*C15*1000000)*(D78*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J132" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H15="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D15),D15&gt;0),IF((D78*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))&gt;0,(D78*IF(ISNUMBER(E15),E15,0)/($C$7*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))/(2*PI()*C15*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B133" s="45" t="n">
+      <c r="G132" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$7*IF(ISNUMBER(E16),E16,0)/D78)&lt;0,ABS($C$7*IF(ISNUMBER(E16),E16,0)/D78)/(2*PI()*C16*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H132" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$7*IF(ISNUMBER(E16),E16,0)/D78)&gt;0,1/((2*PI()*C16*1000000)*ABS($C$7*IF(ISNUMBER(E16),E16,0)/D78))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I132" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF((D78*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&lt;0,-1/((2*PI()*C16*1000000)*(D78*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J132" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF((D78*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&gt;0,(D78*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))/(2*PI()*C16*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B133" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="C133" s="46" t="n">
-        <f aca="false">C16</f>
+      <c r="C133" s="41" t="n">
+        <f aca="false">C17</f>
         <v>10</v>
       </c>
-      <c r="D133" s="46" t="n">
-        <f aca="false">D16</f>
+      <c r="D133" s="41" t="n">
+        <f aca="false">D17</f>
         <v>300</v>
       </c>
-      <c r="E133" s="46" t="n">
-        <f aca="false">IF(ISNUMBER(E16),E16,"—")</f>
+      <c r="E133" s="41" t="n">
+        <f aca="false">IF(ISNUMBER(E17),E17,"—")</f>
         <v>100</v>
       </c>
-      <c r="F133" s="46" t="n">
+      <c r="F133" s="41" t="n">
         <f aca="false">IF(ISNUMBER(E79),E79,"—")</f>
         <v>18.434948822922</v>
       </c>
-      <c r="G133" s="47" t="str">
-        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$7*IF(ISNUMBER(E16),E16,0)/D79)&gt;0,($C$7*IF(ISNUMBER(E16),E16,0)/D79)/(2*PI()*C16*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H133" s="46" t="str">
-        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$7*IF(ISNUMBER(E16),E16,0)/D79)&lt;0,1/((2*PI()*C16*1000000)*ABS(($C$7*IF(ISNUMBER(E16),E16,0)/D79)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I133" s="47" t="str">
-        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D16),D16&gt;0),IF((D79*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&lt;0,-1/((2*PI()*C16*1000000)*(D79*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J133" s="46" t="str">
-        <f aca="false">IFERROR(IF(AND(H16="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D16),D16&gt;0),IF((D79*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&gt;0,(D79*IF(ISNUMBER(E16),E16,0)/($C$7*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))/(2*PI()*C16*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="42" t="n">
+      <c r="G133" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F17="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$7*IF(ISNUMBER(E17),E17,0)/D79)&lt;0,ABS($C$7*IF(ISNUMBER(E17),E17,0)/D79)/(2*PI()*C17*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H133" s="41" t="n">
+        <f aca="false">IFERROR(IF(AND(F17="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$7*IF(ISNUMBER(E17),E17,0)/D79)&gt;0,1/((2*PI()*C17*1000000)*ABS($C$7*IF(ISNUMBER(E17),E17,0)/D79))*1000000000000,"—"),"—"),"—")</f>
+        <v>1006.58424208974</v>
+      </c>
+      <c r="I133" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F17="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D17),D17&gt;0),IF((D79*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&lt;0,-1/((2*PI()*C17*1000000)*(D79*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J133" s="41" t="n">
+        <f aca="false">IFERROR(IF(AND(F17="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D17),D17&gt;0),IF((D79*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&gt;0,(D79*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))/(2*PI()*C17*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>100.658424208974</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B134" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="C134" s="43" t="n">
-        <f aca="false">C17</f>
+      <c r="C134" s="41" t="n">
+        <f aca="false">C18</f>
         <v>18</v>
       </c>
-      <c r="D134" s="43" t="n">
-        <f aca="false">D17</f>
+      <c r="D134" s="41" t="n">
+        <f aca="false">D18</f>
         <v>450</v>
       </c>
-      <c r="E134" s="43" t="n">
-        <f aca="false">IF(ISNUMBER(E17),E17,"—")</f>
+      <c r="E134" s="41" t="n">
+        <f aca="false">IF(ISNUMBER(E18),E18,"—")</f>
         <v>-80</v>
       </c>
-      <c r="F134" s="43" t="n">
+      <c r="F134" s="41" t="n">
         <f aca="false">IF(ISNUMBER(E80),E80,"—")</f>
         <v>-10.0805979875423</v>
       </c>
-      <c r="G134" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$7*IF(ISNUMBER(E17),E17,0)/D80)&gt;0,($C$7*IF(ISNUMBER(E17),E17,0)/D80)/(2*PI()*C17*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H134" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$7*IF(ISNUMBER(E17),E17,0)/D80)&lt;0,1/((2*PI()*C17*1000000)*ABS(($C$7*IF(ISNUMBER(E17),E17,0)/D80)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I134" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D17),D17&gt;0),IF((D80*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&lt;0,-1/((2*PI()*C17*1000000)*(D80*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J134" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H17="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D17),D17&gt;0),IF((D80*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&gt;0,(D80*IF(ISNUMBER(E17),E17,0)/($C$7*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))/(2*PI()*C17*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="45" t="n">
+      <c r="G134" s="42" t="n">
+        <f aca="false">IFERROR(IF(AND(F18="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D18),D18&gt;0),IF(($C$7*IF(ISNUMBER(E18),E18,0)/D80)&lt;0,ABS($C$7*IF(ISNUMBER(E18),E18,0)/D80)/(2*PI()*C18*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>0.0773817234059653</v>
+      </c>
+      <c r="H134" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F18="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D18),D18&gt;0),IF(($C$7*IF(ISNUMBER(E18),E18,0)/D80)&gt;0,1/((2*PI()*C18*1000000)*ABS($C$7*IF(ISNUMBER(E18),E18,0)/D80))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I134" s="42" t="n">
+        <f aca="false">IFERROR(IF(AND(F18="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D18),D18&gt;0),IF((D80*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))&lt;0,-1/((2*PI()*C18*1000000)*(D80*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>2.52578781554784</v>
+      </c>
+      <c r="J134" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F18="YES",ISNUMBER(D80),D80&gt;0,ISNUMBER(D18),D18&gt;0),IF((D80*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))&gt;0,(D80*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))/(2*PI()*C18*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B135" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="C135" s="46" t="n">
-        <f aca="false">C18</f>
+      <c r="C135" s="41" t="n">
+        <f aca="false">C19</f>
         <v>28</v>
       </c>
-      <c r="D135" s="46" t="n">
-        <f aca="false">D18</f>
+      <c r="D135" s="41" t="n">
+        <f aca="false">D19</f>
         <v>800</v>
       </c>
-      <c r="E135" s="46" t="n">
-        <f aca="false">IF(ISNUMBER(E18),E18,"—")</f>
-        <v>0</v>
-      </c>
-      <c r="F135" s="46" t="n">
+      <c r="E135" s="41" t="n">
+        <f aca="false">IF(ISNUMBER(E19),E19,"—")</f>
+        <v>0</v>
+      </c>
+      <c r="F135" s="41" t="n">
         <f aca="false">IF(ISNUMBER(E81),E81,"—")</f>
         <v>0</v>
       </c>
-      <c r="G135" s="47" t="str">
-        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D18),D18&gt;0),IF(($C$7*IF(ISNUMBER(E18),E18,0)/D81)&gt;0,($C$7*IF(ISNUMBER(E18),E18,0)/D81)/(2*PI()*C18*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H135" s="46" t="str">
-        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D18),D18&gt;0),IF(($C$7*IF(ISNUMBER(E18),E18,0)/D81)&lt;0,1/((2*PI()*C18*1000000)*ABS(($C$7*IF(ISNUMBER(E18),E18,0)/D81)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I135" s="47" t="str">
-        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D18),D18&gt;0),IF((D81*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))&lt;0,-1/((2*PI()*C18*1000000)*(D81*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J135" s="46" t="str">
-        <f aca="false">IFERROR(IF(AND(H18="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D18),D18&gt;0),IF((D81*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))&gt;0,(D81*IF(ISNUMBER(E18),E18,0)/($C$7*(D18^2+IF(ISNUMBER(E18),E18,0)^2)))/(2*PI()*C18*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="42" t="n">
+      <c r="G135" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F19="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D19),D19&gt;0),IF(($C$7*IF(ISNUMBER(E19),E19,0)/D81)&lt;0,ABS($C$7*IF(ISNUMBER(E19),E19,0)/D81)/(2*PI()*C19*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H135" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F19="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D19),D19&gt;0),IF(($C$7*IF(ISNUMBER(E19),E19,0)/D81)&gt;0,1/((2*PI()*C19*1000000)*ABS($C$7*IF(ISNUMBER(E19),E19,0)/D81))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I135" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F19="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D19),D19&gt;0),IF((D81*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))&lt;0,-1/((2*PI()*C19*1000000)*(D81*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J135" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F19="YES",ISNUMBER(D81),D81&gt;0,ISNUMBER(D19),D19&gt;0),IF((D81*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))&gt;0,(D81*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))/(2*PI()*C19*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B136" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="C136" s="43" t="n">
-        <f aca="false">C19</f>
-        <v>0</v>
-      </c>
-      <c r="D136" s="43" t="n">
-        <f aca="false">D19</f>
-        <v>0</v>
-      </c>
-      <c r="E136" s="43" t="str">
-        <f aca="false">IF(ISNUMBER(E19),E19,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="F136" s="43" t="str">
+      <c r="C136" s="41" t="n">
+        <f aca="false">C20</f>
+        <v>0</v>
+      </c>
+      <c r="D136" s="41" t="n">
+        <f aca="false">D20</f>
+        <v>0</v>
+      </c>
+      <c r="E136" s="41" t="str">
+        <f aca="false">IF(ISNUMBER(E20),E20,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F136" s="41" t="str">
         <f aca="false">IF(ISNUMBER(E82),E82,"—")</f>
         <v>—</v>
       </c>
-      <c r="G136" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D19),D19&gt;0),IF(($C$7*IF(ISNUMBER(E19),E19,0)/D82)&gt;0,($C$7*IF(ISNUMBER(E19),E19,0)/D82)/(2*PI()*C19*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H136" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D19),D19&gt;0),IF(($C$7*IF(ISNUMBER(E19),E19,0)/D82)&lt;0,1/((2*PI()*C19*1000000)*ABS(($C$7*IF(ISNUMBER(E19),E19,0)/D82)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I136" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D19),D19&gt;0),IF((D82*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))&lt;0,-1/((2*PI()*C19*1000000)*(D82*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J136" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H19="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D19),D19&gt;0),IF((D82*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))&gt;0,(D82*IF(ISNUMBER(E19),E19,0)/($C$7*(D19^2+IF(ISNUMBER(E19),E19,0)^2)))/(2*PI()*C19*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="45" t="n">
+      <c r="G136" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F20="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D20),D20&gt;0),IF(($C$7*IF(ISNUMBER(E20),E20,0)/D82)&lt;0,ABS($C$7*IF(ISNUMBER(E20),E20,0)/D82)/(2*PI()*C20*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H136" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F20="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D20),D20&gt;0),IF(($C$7*IF(ISNUMBER(E20),E20,0)/D82)&gt;0,1/((2*PI()*C20*1000000)*ABS($C$7*IF(ISNUMBER(E20),E20,0)/D82))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I136" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F20="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D20),D20&gt;0),IF((D82*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))&lt;0,-1/((2*PI()*C20*1000000)*(D82*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J136" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F20="YES",ISNUMBER(D82),D82&gt;0,ISNUMBER(D20),D20&gt;0),IF((D82*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))&gt;0,(D82*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))/(2*PI()*C20*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B137" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="C137" s="46" t="n">
-        <f aca="false">C20</f>
-        <v>0</v>
-      </c>
-      <c r="D137" s="46" t="n">
-        <f aca="false">D20</f>
-        <v>0</v>
-      </c>
-      <c r="E137" s="46" t="str">
-        <f aca="false">IF(ISNUMBER(E20),E20,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="F137" s="46" t="str">
+      <c r="C137" s="41" t="n">
+        <f aca="false">C21</f>
+        <v>0</v>
+      </c>
+      <c r="D137" s="41" t="n">
+        <f aca="false">D21</f>
+        <v>0</v>
+      </c>
+      <c r="E137" s="41" t="str">
+        <f aca="false">IF(ISNUMBER(E21),E21,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F137" s="41" t="str">
         <f aca="false">IF(ISNUMBER(E83),E83,"—")</f>
         <v>—</v>
       </c>
-      <c r="G137" s="47" t="str">
-        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D20),D20&gt;0),IF(($C$7*IF(ISNUMBER(E20),E20,0)/D83)&gt;0,($C$7*IF(ISNUMBER(E20),E20,0)/D83)/(2*PI()*C20*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H137" s="46" t="str">
-        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D20),D20&gt;0),IF(($C$7*IF(ISNUMBER(E20),E20,0)/D83)&lt;0,1/((2*PI()*C20*1000000)*ABS(($C$7*IF(ISNUMBER(E20),E20,0)/D83)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I137" s="47" t="str">
-        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D20),D20&gt;0),IF((D83*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))&lt;0,-1/((2*PI()*C20*1000000)*(D83*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J137" s="46" t="str">
-        <f aca="false">IFERROR(IF(AND(H20="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D20),D20&gt;0),IF((D83*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))&gt;0,(D83*IF(ISNUMBER(E20),E20,0)/($C$7*(D20^2+IF(ISNUMBER(E20),E20,0)^2)))/(2*PI()*C20*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="42" t="n">
+      <c r="G137" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F21="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D21),D21&gt;0),IF(($C$7*IF(ISNUMBER(E21),E21,0)/D83)&lt;0,ABS($C$7*IF(ISNUMBER(E21),E21,0)/D83)/(2*PI()*C21*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H137" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F21="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D21),D21&gt;0),IF(($C$7*IF(ISNUMBER(E21),E21,0)/D83)&gt;0,1/((2*PI()*C21*1000000)*ABS($C$7*IF(ISNUMBER(E21),E21,0)/D83))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I137" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F21="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D21),D21&gt;0),IF((D83*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))&lt;0,-1/((2*PI()*C21*1000000)*(D83*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J137" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F21="YES",ISNUMBER(D83),D83&gt;0,ISNUMBER(D21),D21&gt;0),IF((D83*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))&gt;0,(D83*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))/(2*PI()*C21*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B138" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="C138" s="43" t="n">
-        <f aca="false">C21</f>
-        <v>0</v>
-      </c>
-      <c r="D138" s="43" t="n">
-        <f aca="false">D21</f>
-        <v>0</v>
-      </c>
-      <c r="E138" s="43" t="str">
-        <f aca="false">IF(ISNUMBER(E21),E21,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="F138" s="43" t="str">
+      <c r="C138" s="41" t="n">
+        <f aca="false">C22</f>
+        <v>0</v>
+      </c>
+      <c r="D138" s="41" t="n">
+        <f aca="false">D22</f>
+        <v>0</v>
+      </c>
+      <c r="E138" s="41" t="str">
+        <f aca="false">IF(ISNUMBER(E22),E22,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F138" s="41" t="str">
         <f aca="false">IF(ISNUMBER(E84),E84,"—")</f>
         <v>—</v>
       </c>
-      <c r="G138" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D21),D21&gt;0),IF(($C$7*IF(ISNUMBER(E21),E21,0)/D84)&gt;0,($C$7*IF(ISNUMBER(E21),E21,0)/D84)/(2*PI()*C21*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H138" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D21),D21&gt;0),IF(($C$7*IF(ISNUMBER(E21),E21,0)/D84)&lt;0,1/((2*PI()*C21*1000000)*ABS(($C$7*IF(ISNUMBER(E21),E21,0)/D84)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I138" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D21),D21&gt;0),IF((D84*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))&lt;0,-1/((2*PI()*C21*1000000)*(D84*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J138" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H21="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D21),D21&gt;0),IF((D84*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))&gt;0,(D84*IF(ISNUMBER(E21),E21,0)/($C$7*(D21^2+IF(ISNUMBER(E21),E21,0)^2)))/(2*PI()*C21*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="45" t="n">
+      <c r="G138" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F22="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D22),D22&gt;0),IF(($C$7*IF(ISNUMBER(E22),E22,0)/D84)&lt;0,ABS($C$7*IF(ISNUMBER(E22),E22,0)/D84)/(2*PI()*C22*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H138" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F22="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D22),D22&gt;0),IF(($C$7*IF(ISNUMBER(E22),E22,0)/D84)&gt;0,1/((2*PI()*C22*1000000)*ABS($C$7*IF(ISNUMBER(E22),E22,0)/D84))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I138" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F22="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D22),D22&gt;0),IF((D84*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))&lt;0,-1/((2*PI()*C22*1000000)*(D84*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J138" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F22="YES",ISNUMBER(D84),D84&gt;0,ISNUMBER(D22),D22&gt;0),IF((D84*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))&gt;0,(D84*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))/(2*PI()*C22*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B139" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="C139" s="46" t="n">
-        <f aca="false">C22</f>
-        <v>0</v>
-      </c>
-      <c r="D139" s="46" t="n">
-        <f aca="false">D22</f>
-        <v>0</v>
-      </c>
-      <c r="E139" s="46" t="str">
-        <f aca="false">IF(ISNUMBER(E22),E22,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="F139" s="46" t="str">
+      <c r="C139" s="41" t="n">
+        <f aca="false">C23</f>
+        <v>0</v>
+      </c>
+      <c r="D139" s="41" t="n">
+        <f aca="false">D23</f>
+        <v>0</v>
+      </c>
+      <c r="E139" s="41" t="str">
+        <f aca="false">IF(ISNUMBER(E23),E23,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F139" s="41" t="str">
         <f aca="false">IF(ISNUMBER(E85),E85,"—")</f>
         <v>—</v>
       </c>
-      <c r="G139" s="47" t="str">
-        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D22),D22&gt;0),IF(($C$7*IF(ISNUMBER(E22),E22,0)/D85)&gt;0,($C$7*IF(ISNUMBER(E22),E22,0)/D85)/(2*PI()*C22*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H139" s="46" t="str">
-        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D22),D22&gt;0),IF(($C$7*IF(ISNUMBER(E22),E22,0)/D85)&lt;0,1/((2*PI()*C22*1000000)*ABS(($C$7*IF(ISNUMBER(E22),E22,0)/D85)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I139" s="47" t="str">
-        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D22),D22&gt;0),IF((D85*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))&lt;0,-1/((2*PI()*C22*1000000)*(D85*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J139" s="46" t="str">
-        <f aca="false">IFERROR(IF(AND(H22="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D22),D22&gt;0),IF((D85*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))&gt;0,(D85*IF(ISNUMBER(E22),E22,0)/($C$7*(D22^2+IF(ISNUMBER(E22),E22,0)^2)))/(2*PI()*C22*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="42" t="n">
+      <c r="G139" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F23="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D23),D23&gt;0),IF(($C$7*IF(ISNUMBER(E23),E23,0)/D85)&lt;0,ABS($C$7*IF(ISNUMBER(E23),E23,0)/D85)/(2*PI()*C23*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H139" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F23="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D23),D23&gt;0),IF(($C$7*IF(ISNUMBER(E23),E23,0)/D85)&gt;0,1/((2*PI()*C23*1000000)*ABS($C$7*IF(ISNUMBER(E23),E23,0)/D85))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I139" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F23="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D23),D23&gt;0),IF((D85*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))&lt;0,-1/((2*PI()*C23*1000000)*(D85*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J139" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F23="YES",ISNUMBER(D85),D85&gt;0,ISNUMBER(D23),D23&gt;0),IF((D85*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))&gt;0,(D85*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))/(2*PI()*C23*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B140" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="C140" s="43" t="n">
-        <f aca="false">C23</f>
-        <v>0</v>
-      </c>
-      <c r="D140" s="43" t="n">
-        <f aca="false">D23</f>
-        <v>0</v>
-      </c>
-      <c r="E140" s="43" t="str">
-        <f aca="false">IF(ISNUMBER(E23),E23,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="F140" s="43" t="str">
+      <c r="C140" s="41" t="n">
+        <f aca="false">C24</f>
+        <v>0</v>
+      </c>
+      <c r="D140" s="41" t="n">
+        <f aca="false">D24</f>
+        <v>0</v>
+      </c>
+      <c r="E140" s="41" t="str">
+        <f aca="false">IF(ISNUMBER(E24),E24,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F140" s="41" t="str">
         <f aca="false">IF(ISNUMBER(E86),E86,"—")</f>
         <v>—</v>
       </c>
-      <c r="G140" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D23),D23&gt;0),IF(($C$7*IF(ISNUMBER(E23),E23,0)/D86)&gt;0,($C$7*IF(ISNUMBER(E23),E23,0)/D86)/(2*PI()*C23*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H140" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D23),D23&gt;0),IF(($C$7*IF(ISNUMBER(E23),E23,0)/D86)&lt;0,1/((2*PI()*C23*1000000)*ABS(($C$7*IF(ISNUMBER(E23),E23,0)/D86)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I140" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D23),D23&gt;0),IF((D86*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))&lt;0,-1/((2*PI()*C23*1000000)*(D86*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J140" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H23="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D23),D23&gt;0),IF((D86*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))&gt;0,(D86*IF(ISNUMBER(E23),E23,0)/($C$7*(D23^2+IF(ISNUMBER(E23),E23,0)^2)))/(2*PI()*C23*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="45" t="n">
+      <c r="G140" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F24="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D24),D24&gt;0),IF(($C$7*IF(ISNUMBER(E24),E24,0)/D86)&lt;0,ABS($C$7*IF(ISNUMBER(E24),E24,0)/D86)/(2*PI()*C24*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H140" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F24="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D24),D24&gt;0),IF(($C$7*IF(ISNUMBER(E24),E24,0)/D86)&gt;0,1/((2*PI()*C24*1000000)*ABS($C$7*IF(ISNUMBER(E24),E24,0)/D86))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I140" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F24="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D24),D24&gt;0),IF((D86*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))&lt;0,-1/((2*PI()*C24*1000000)*(D86*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J140" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F24="YES",ISNUMBER(D86),D86&gt;0,ISNUMBER(D24),D24&gt;0),IF((D86*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))&gt;0,(D86*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))/(2*PI()*C24*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B141" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="C141" s="46" t="n">
-        <f aca="false">C24</f>
-        <v>0</v>
-      </c>
-      <c r="D141" s="46" t="n">
-        <f aca="false">D24</f>
-        <v>0</v>
-      </c>
-      <c r="E141" s="46" t="str">
-        <f aca="false">IF(ISNUMBER(E24),E24,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="F141" s="46" t="str">
+      <c r="C141" s="41" t="n">
+        <f aca="false">C25</f>
+        <v>0</v>
+      </c>
+      <c r="D141" s="41" t="n">
+        <f aca="false">D25</f>
+        <v>0</v>
+      </c>
+      <c r="E141" s="41" t="str">
+        <f aca="false">IF(ISNUMBER(E25),E25,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F141" s="41" t="str">
         <f aca="false">IF(ISNUMBER(E87),E87,"—")</f>
         <v>—</v>
       </c>
-      <c r="G141" s="47" t="str">
-        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D24),D24&gt;0),IF(($C$7*IF(ISNUMBER(E24),E24,0)/D87)&gt;0,($C$7*IF(ISNUMBER(E24),E24,0)/D87)/(2*PI()*C24*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H141" s="46" t="str">
-        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D24),D24&gt;0),IF(($C$7*IF(ISNUMBER(E24),E24,0)/D87)&lt;0,1/((2*PI()*C24*1000000)*ABS(($C$7*IF(ISNUMBER(E24),E24,0)/D87)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I141" s="47" t="str">
-        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D24),D24&gt;0),IF((D87*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))&lt;0,-1/((2*PI()*C24*1000000)*(D87*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J141" s="46" t="str">
-        <f aca="false">IFERROR(IF(AND(H24="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D24),D24&gt;0),IF((D87*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))&gt;0,(D87*IF(ISNUMBER(E24),E24,0)/($C$7*(D24^2+IF(ISNUMBER(E24),E24,0)^2)))/(2*PI()*C24*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="42" t="n">
+      <c r="G141" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F25="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D25),D25&gt;0),IF(($C$7*IF(ISNUMBER(E25),E25,0)/D87)&lt;0,ABS($C$7*IF(ISNUMBER(E25),E25,0)/D87)/(2*PI()*C25*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H141" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F25="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D25),D25&gt;0),IF(($C$7*IF(ISNUMBER(E25),E25,0)/D87)&gt;0,1/((2*PI()*C25*1000000)*ABS($C$7*IF(ISNUMBER(E25),E25,0)/D87))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I141" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F25="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D25),D25&gt;0),IF((D87*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))&lt;0,-1/((2*PI()*C25*1000000)*(D87*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J141" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F25="YES",ISNUMBER(D87),D87&gt;0,ISNUMBER(D25),D25&gt;0),IF((D87*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))&gt;0,(D87*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))/(2*PI()*C25*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B142" s="40" t="n">
         <v>11</v>
       </c>
-      <c r="C142" s="43" t="n">
-        <f aca="false">C25</f>
-        <v>0</v>
-      </c>
-      <c r="D142" s="43" t="n">
-        <f aca="false">D25</f>
-        <v>0</v>
-      </c>
-      <c r="E142" s="43" t="str">
-        <f aca="false">IF(ISNUMBER(E25),E25,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="F142" s="43" t="str">
+      <c r="C142" s="41" t="n">
+        <f aca="false">C26</f>
+        <v>0</v>
+      </c>
+      <c r="D142" s="41" t="n">
+        <f aca="false">D26</f>
+        <v>0</v>
+      </c>
+      <c r="E142" s="41" t="str">
+        <f aca="false">IF(ISNUMBER(E26),E26,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="F142" s="41" t="str">
         <f aca="false">IF(ISNUMBER(E88),E88,"—")</f>
         <v>—</v>
       </c>
-      <c r="G142" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D25),D25&gt;0),IF(($C$7*IF(ISNUMBER(E25),E25,0)/D88)&gt;0,($C$7*IF(ISNUMBER(E25),E25,0)/D88)/(2*PI()*C25*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="H142" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D25),D25&gt;0),IF(($C$7*IF(ISNUMBER(E25),E25,0)/D88)&lt;0,1/((2*PI()*C25*1000000)*ABS(($C$7*IF(ISNUMBER(E25),E25,0)/D88)))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I142" s="44" t="str">
-        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D25),D25&gt;0),IF((D88*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))&lt;0,-1/((2*PI()*C25*1000000)*(D88*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="J142" s="43" t="str">
-        <f aca="false">IFERROR(IF(AND(H25="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D25),D25&gt;0),IF((D88*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))&gt;0,(D88*IF(ISNUMBER(E25),E25,0)/($C$7*(D25^2+IF(ISNUMBER(E25),E25,0)^2)))/(2*PI()*C25*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="39" t="s">
+      <c r="G142" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F26="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D26),D26&gt;0),IF(($C$7*IF(ISNUMBER(E26),E26,0)/D88)&lt;0,ABS($C$7*IF(ISNUMBER(E26),E26,0)/D88)/(2*PI()*C26*1000000)*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="H142" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F26="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D26),D26&gt;0),IF(($C$7*IF(ISNUMBER(E26),E26,0)/D88)&gt;0,1/((2*PI()*C26*1000000)*ABS($C$7*IF(ISNUMBER(E26),E26,0)/D88))*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="I142" s="42" t="str">
+        <f aca="false">IFERROR(IF(AND(F26="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D26),D26&gt;0),IF((D88*IF(ISNUMBER(E26),E26,0)/($C$7*(D26^2+IF(ISNUMBER(E26),E26,0)^2)))&lt;0,-1/((2*PI()*C26*1000000)*(D88*IF(ISNUMBER(E26),E26,0)/($C$7*(D26^2+IF(ISNUMBER(E26),E26,0)^2))))*1000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="J142" s="41" t="str">
+        <f aca="false">IFERROR(IF(AND(F26="YES",ISNUMBER(D88),D88&gt;0,ISNUMBER(D26),D26&gt;0),IF((D88*IF(ISNUMBER(E26),E26,0)/($C$7*(D26^2+IF(ISNUMBER(E26),E26,0)^2)))&gt;0,(D88*IF(ISNUMBER(E26),E26,0)/($C$7*(D26^2+IF(ISNUMBER(E26),E26,0)^2)))/(2*PI()*C26*1000000)*1000000000000,"—"),"—"),"—")</f>
+        <v>—</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B144" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="C144" s="39"/>
-      <c r="D144" s="39"/>
-      <c r="E144" s="39"/>
-      <c r="F144" s="39"/>
-      <c r="G144" s="39"/>
-      <c r="H144" s="39"/>
-      <c r="I144" s="39"/>
-      <c r="J144" s="39"/>
-    </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="48" t="s">
+      <c r="C144" s="37"/>
+      <c r="D144" s="37"/>
+      <c r="E144" s="37"/>
+      <c r="F144" s="37"/>
+      <c r="G144" s="37"/>
+      <c r="H144" s="37"/>
+      <c r="I144" s="37"/>
+      <c r="J144" s="37"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B145" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="C145" s="40" t="s">
+      <c r="C145" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="D145" s="40"/>
-      <c r="E145" s="40"/>
-      <c r="F145" s="40"/>
-      <c r="G145" s="40"/>
-      <c r="H145" s="40"/>
-      <c r="I145" s="40"/>
-      <c r="J145" s="40"/>
-    </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="48" t="s">
+      <c r="D145" s="38"/>
+      <c r="E145" s="38"/>
+      <c r="F145" s="38"/>
+      <c r="G145" s="38"/>
+      <c r="H145" s="38"/>
+      <c r="I145" s="38"/>
+      <c r="J145" s="38"/>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B146" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="C146" s="40" t="s">
+      <c r="C146" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="D146" s="40"/>
-      <c r="E146" s="40"/>
-      <c r="F146" s="40"/>
-      <c r="G146" s="40"/>
-      <c r="H146" s="40"/>
-      <c r="I146" s="40"/>
-      <c r="J146" s="40"/>
-    </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="48" t="s">
+      <c r="D146" s="38"/>
+      <c r="E146" s="38"/>
+      <c r="F146" s="38"/>
+      <c r="G146" s="38"/>
+      <c r="H146" s="38"/>
+      <c r="I146" s="38"/>
+      <c r="J146" s="38"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B147" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="C147" s="40" t="s">
+      <c r="C147" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="D147" s="40"/>
-      <c r="E147" s="40"/>
-      <c r="F147" s="40"/>
-      <c r="G147" s="40"/>
-      <c r="H147" s="40"/>
-      <c r="I147" s="40"/>
-      <c r="J147" s="40"/>
-    </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="48" t="s">
+      <c r="D147" s="38"/>
+      <c r="E147" s="38"/>
+      <c r="F147" s="38"/>
+      <c r="G147" s="38"/>
+      <c r="H147" s="38"/>
+      <c r="I147" s="38"/>
+      <c r="J147" s="38"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B148" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="C148" s="40" t="s">
+      <c r="C148" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="D148" s="40"/>
-      <c r="E148" s="40"/>
-      <c r="F148" s="40"/>
-      <c r="G148" s="40"/>
-      <c r="H148" s="40"/>
-      <c r="I148" s="40"/>
-      <c r="J148" s="40"/>
-    </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="48" t="s">
+      <c r="D148" s="38"/>
+      <c r="E148" s="38"/>
+      <c r="F148" s="38"/>
+      <c r="G148" s="38"/>
+      <c r="H148" s="38"/>
+      <c r="I148" s="38"/>
+      <c r="J148" s="38"/>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B149" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="C149" s="40" t="s">
+      <c r="C149" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="D149" s="40"/>
-      <c r="E149" s="40"/>
-      <c r="F149" s="40"/>
-      <c r="G149" s="40"/>
-      <c r="H149" s="40"/>
-      <c r="I149" s="40"/>
-      <c r="J149" s="40"/>
-    </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="48" t="s">
+      <c r="D149" s="38"/>
+      <c r="E149" s="38"/>
+      <c r="F149" s="38"/>
+      <c r="G149" s="38"/>
+      <c r="H149" s="38"/>
+      <c r="I149" s="38"/>
+      <c r="J149" s="38"/>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B150" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="C150" s="40" t="s">
+      <c r="C150" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="D150" s="40"/>
-      <c r="E150" s="40"/>
-      <c r="F150" s="40"/>
-      <c r="G150" s="40"/>
-      <c r="H150" s="40"/>
-      <c r="I150" s="40"/>
-      <c r="J150" s="40"/>
+      <c r="D150" s="38"/>
+      <c r="E150" s="38"/>
+      <c r="F150" s="38"/>
+      <c r="G150" s="38"/>
+      <c r="H150" s="38"/>
+      <c r="I150" s="38"/>
+      <c r="J150" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="62">
@@ -3954,10 +3959,10 @@
     <mergeCell ref="E9:H9"/>
     <mergeCell ref="E10:H10"/>
     <mergeCell ref="E11:I11"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B14:E14"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B40:J40"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="B55:I55"/>

--- a/Autotransformer_UnUn_AirCore_Calculator.xlsx
+++ b/Autotransformer_UnUn_AirCore_Calculator.xlsx
@@ -1185,7 +1185,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>11</v>
@@ -1236,7 +1236,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D11" s="10" t="n">
         <f aca="false">IFERROR(CEILING(5/MIN(D59:D69),1),5)</f>
@@ -1255,7 +1255,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="12"/>
@@ -1310,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="15" t="str">
-        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <f aca="false">IF(ROW()-15&lt;=$C$10,"YES","NO")</f>
         <v>YES</v>
       </c>
       <c r="G16" s="18"/>
@@ -1331,7 +1331,7 @@
         <v>100</v>
       </c>
       <c r="F17" s="15" t="str">
-        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <f aca="false">IF(ROW()-15&lt;=$C$10,"YES","NO")</f>
         <v>YES</v>
       </c>
       <c r="G17" s="18"/>
@@ -1352,7 +1352,7 @@
         <v>-80</v>
       </c>
       <c r="F18" s="15" t="str">
-        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <f aca="false">IF(ROW()-15&lt;=$C$10,"YES","NO")</f>
         <v>YES</v>
       </c>
       <c r="G18" s="18"/>
@@ -1373,8 +1373,8 @@
         <v>0</v>
       </c>
       <c r="F19" s="15" t="str">
-        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
-        <v>NO</v>
+        <f aca="false">IF(ROW()-15&lt;=$C$10,"YES","NO")</f>
+        <v>YES</v>
       </c>
       <c r="G19" s="18"/>
       <c r="H19" s="8"/>
@@ -1388,7 +1388,7 @@
       <c r="D20" s="16"/>
       <c r="E20" s="17"/>
       <c r="F20" s="15" t="str">
-        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <f aca="false">IF(ROW()-15&lt;=$C$10,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G20" s="18"/>
@@ -1403,7 +1403,7 @@
       <c r="D21" s="16"/>
       <c r="E21" s="17"/>
       <c r="F21" s="15" t="str">
-        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <f aca="false">IF(ROW()-15&lt;=$C$10,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G21" s="18"/>
@@ -1418,7 +1418,7 @@
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
       <c r="F22" s="15" t="str">
-        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <f aca="false">IF(ROW()-15&lt;=$C$10,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G22" s="18"/>
@@ -1433,7 +1433,7 @@
       <c r="D23" s="16"/>
       <c r="E23" s="17"/>
       <c r="F23" s="15" t="str">
-        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <f aca="false">IF(ROW()-15&lt;=$C$10,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G23" s="18"/>
@@ -1448,7 +1448,7 @@
       <c r="D24" s="16"/>
       <c r="E24" s="17"/>
       <c r="F24" s="15" t="str">
-        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <f aca="false">IF(ROW()-15&lt;=$C$10,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G24" s="18"/>
@@ -1463,7 +1463,7 @@
       <c r="D25" s="16"/>
       <c r="E25" s="17"/>
       <c r="F25" s="15" t="str">
-        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <f aca="false">IF(ROW()-15&lt;=$C$10,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G25" s="18"/>
@@ -1478,7 +1478,7 @@
       <c r="D26" s="16"/>
       <c r="E26" s="17"/>
       <c r="F26" s="15" t="str">
-        <f aca="false">IF(ROW()-14&lt;=$C$10,"YES","NO")</f>
+        <f aca="false">IF(ROW()-15&lt;=$C$10,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G26" s="18"/>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C33" s="20" t="n">
         <f aca="false">C8</f>
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>11</v>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C34" s="20" t="n">
         <f aca="false">C11</f>
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>33</v>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C36" s="21" t="n">
         <f aca="false">I71</f>
-        <v>4134.33593212417</v>
+        <v>6836.10561421139</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>11</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C37" s="22" t="n">
         <f aca="false">IFERROR(C115,"—")</f>
-        <v>3.88816824074988</v>
+        <v>17.7438014422954</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>37</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C38" s="20" t="str">
         <f aca="false">IFERROR(C118,"—")</f>
-        <v>—</v>
+        <v>✔ YES</v>
       </c>
       <c r="D38" s="8"/>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G42" s="10" t="n">
         <f aca="false">E59</f>
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="H42" s="27" t="n">
         <f aca="false">F78</f>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G43" s="10" t="n">
         <f aca="false">E60</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H43" s="27" t="n">
         <f aca="false">F79</f>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="G44" s="10" t="n">
         <f aca="false">E61</f>
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="H44" s="27" t="n">
         <f aca="false">F80</f>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G45" s="10" t="n">
         <f aca="false">E62</f>
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="H45" s="27" t="n">
         <f aca="false">F81</f>
@@ -2129,23 +2129,23 @@
       </c>
       <c r="E59" s="10" t="n">
         <f aca="false">IF(D59&lt;&gt;"",MAX(1,ROUND(C11*D59,0)),"")</f>
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F59" s="10" t="n">
         <f aca="false">IF(E59&lt;&gt;"",E59,"")</f>
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="G59" s="21" t="n">
         <f aca="false">IF(F59&lt;&gt;"",F59*PI()*($C$9+$C$8),"")</f>
-        <v>2067.16796606208</v>
+        <v>3418.0528071057</v>
       </c>
       <c r="H59" s="24" t="n">
         <f aca="false">IF(G59&lt;&gt;"",G59*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
-        <v>224.077432098765</v>
+        <v>75.02848</v>
       </c>
       <c r="I59" s="21" t="n">
         <f aca="false">IF(G59&lt;&gt;"",G59,"")</f>
-        <v>2067.16796606208</v>
+        <v>3418.0528071057</v>
       </c>
       <c r="J59" s="8"/>
     </row>
@@ -2163,23 +2163,23 @@
       </c>
       <c r="E60" s="10" t="n">
         <f aca="false">IF(D60&lt;&gt;"",MAX(1,ROUND(C11*D60,0)),"")</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F60" s="10" t="n">
         <f aca="false">IF(AND(E60&lt;&gt;"",E59&lt;&gt;""),E60-E59,IF(E60&lt;&gt;"",E60,""))</f>
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G60" s="21" t="n">
         <f aca="false">IF(F60&lt;&gt;"",F60*PI()*($C$9+$C$8),"")</f>
-        <v>516.791991515521</v>
+        <v>854.513201776424</v>
       </c>
       <c r="H60" s="24" t="n">
         <f aca="false">IF(G60&lt;&gt;"",G60*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
-        <v>56.0193580246914</v>
+        <v>18.75712</v>
       </c>
       <c r="I60" s="21" t="n">
         <f aca="false">IF(G60&lt;&gt;"",SUM(G59:G60),"")</f>
-        <v>2583.9599575776</v>
+        <v>4272.56600888212</v>
       </c>
       <c r="J60" s="8"/>
     </row>
@@ -2197,23 +2197,23 @@
       </c>
       <c r="E61" s="10" t="n">
         <f aca="false">IF(D61&lt;&gt;"",MAX(1,ROUND(C11*D61,0)),"")</f>
-        <v>60</v>
+        <v>97</v>
       </c>
       <c r="F61" s="10" t="n">
         <f aca="false">IF(AND(E61&lt;&gt;"",E60&lt;&gt;""),E61-E60,IF(E61&lt;&gt;"",E61,""))</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G61" s="21" t="n">
         <f aca="false">IF(F61&lt;&gt;"",F61*PI()*($C$9+$C$8),"")</f>
-        <v>516.791991515521</v>
+        <v>907.92027688745</v>
       </c>
       <c r="H61" s="24" t="n">
         <f aca="false">IF(G61&lt;&gt;"",G61*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
-        <v>56.0193580246914</v>
+        <v>19.92944</v>
       </c>
       <c r="I61" s="21" t="n">
         <f aca="false">IF(G61&lt;&gt;"",SUM(G59:G61),"")</f>
-        <v>3100.75194909313</v>
+        <v>5180.48628576957</v>
       </c>
       <c r="J61" s="8"/>
     </row>
@@ -2231,23 +2231,23 @@
       </c>
       <c r="E62" s="10" t="n">
         <f aca="false">IF(D62&lt;&gt;"",MAX(1,ROUND(C11*D62,0)),"")</f>
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="F62" s="10" t="n">
         <f aca="false">IF(AND(E62&lt;&gt;"",E61&lt;&gt;""),E62-E61,IF(E62&lt;&gt;"",E62,""))</f>
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G62" s="21" t="n">
         <f aca="false">IF(F62&lt;&gt;"",F62*PI()*($C$9+$C$8),"")</f>
-        <v>1033.58398303104</v>
+        <v>1655.61932844182</v>
       </c>
       <c r="H62" s="24" t="n">
         <f aca="false">IF(G62&lt;&gt;"",G62*4*0.00000001724*1000000/(PI()*$C$8^2),"")</f>
-        <v>112.038716049383</v>
+        <v>36.34192</v>
       </c>
       <c r="I62" s="21" t="n">
         <f aca="false">IF(G62&lt;&gt;"",SUM(G59:G62),"")</f>
-        <v>4134.33593212417</v>
+        <v>6836.10561421139</v>
       </c>
       <c r="J62" s="8"/>
     </row>
@@ -2497,15 +2497,15 @@
       <c r="D71" s="29"/>
       <c r="E71" s="10" t="n">
         <f aca="false">IFERROR(MAX(E59:E69),"")</f>
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="H71" s="30" t="n">
         <f aca="false">IFERROR(SUM(H59:H69),"")</f>
-        <v>448.154864197531</v>
+        <v>150.05696</v>
       </c>
       <c r="I71" s="31" t="n">
         <f aca="false">IFERROR(MAX(I59:I69),"")</f>
-        <v>4134.33593212417</v>
+        <v>6836.10561421139</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="C105" s="34" t="n">
         <f aca="false">C8</f>
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>11</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C106" s="34" t="n">
         <f aca="false">$C$8+$C$12</f>
-        <v>5.45</v>
+        <v>2</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>11</v>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="C107" s="20" t="n">
         <f aca="false">IFERROR(IF(E71&lt;&gt;"",VALUE(E71),10),10)</f>
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>33</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C111" s="22" t="n">
         <f aca="false">IFERROR(IF(C107&gt;0,(C107-1)*C106+C105,""),"")</f>
-        <v>431</v>
+        <v>255</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>11</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="C112" s="22" t="n">
         <f aca="false">(C104+C105)/2</f>
-        <v>8.225</v>
+        <v>8.5</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>11</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="C113" s="22" t="n">
         <f aca="false">((C104+C105)/2)/25.4</f>
-        <v>0.323818897637795</v>
+        <v>0.334645669291339</v>
       </c>
       <c r="D113" s="8" t="s">
         <v>93</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C114" s="22" t="n">
         <f aca="false">IFERROR(C111/25.4,"")</f>
-        <v>16.9685039370079</v>
+        <v>10.0393700787402</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>93</v>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C115" s="22" t="n">
         <f aca="false">IFERROR((C113^2*C107^2)/(9*C113+10*C114),"")</f>
-        <v>3.88816824074988</v>
+        <v>17.7438014422954</v>
       </c>
       <c r="D115" s="8" t="s">
         <v>37</v>
@@ -3258,9 +3258,9 @@
       <c r="B116" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C116" s="22" t="str">
-        <f aca="false">IFERROR(2*PI()*minifs($C$16:$C$26,$F$16:$F$26,"YES")*1000000*C115/1000000,"")</f>
-        <v/>
+      <c r="C116" s="22" t="n">
+        <f aca="true">IFERROR(2*PI()*MIN($C$16:OFFSET($C$16,$C$10-1,0))*C115,"")</f>
+        <v>802.710666113347</v>
       </c>
       <c r="D116" s="8" t="s">
         <v>8</v>
@@ -3275,9 +3275,9 @@
       <c r="B117" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C117" s="22" t="str">
-        <f aca="false">IFERROR(4*MIN(D78:D88)/(2*PI()*minifs($C$16:$C$26,$F$16:$F$26,"YES")*1000000)*1000000,"")</f>
-        <v/>
+      <c r="C117" s="22" t="n">
+        <f aca="true">IFERROR(4*MIN(OFFSET(D78,0,0,$C$10))/(2*PI()*MIN($C$16:OFFSET($C$16,$C$10-1,0))),"")</f>
+        <v>17.6838825657661</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>37</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="C118" s="22" t="str">
         <f aca="false">IFERROR(IF(AND(ISNUMBER(C115),ISNUMBER(C117)),IF(C115&gt;=C117,"✔ YES","✘ INCREASE TURNS"),"—"),"")</f>
-        <v>—</v>
+        <v>✔ YES</v>
       </c>
       <c r="D118" s="8" t="s">
         <v>103</v>

--- a/Autotransformer_UnUn_AirCore_Calculator.xlsx
+++ b/Autotransformer_UnUn_AirCore_Calculator.xlsx
@@ -76,10 +76,10 @@
     <t xml:space="preserve">Enter 1–11  (rows below auto-activate)</t>
   </si>
   <si>
-    <t xml:space="preserve">T_ref  (turns at 50Ω tap)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suggested T_ref (min 5 turns at lowest-Z tap)</t>
+    <t xml:space="preserve">Turns at 50Ω tap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min turns</t>
   </si>
   <si>
     <t xml:space="preserve">Space between coil turns</t>
@@ -1239,8 +1239,8 @@
         <v>32</v>
       </c>
       <c r="D11" s="10" t="n">
-        <f aca="false">IFERROR(CEILING(5/MIN(D59:D69),1),5)</f>
-        <v>3</v>
+        <f aca="false">IFERROR(MAX(CEILING(5/MIN(D59:D69),1),CEILING((5*C117*(C106/25.4)+SQRT(C117*(25*C117*(C106/25.4)^2+C113^2*(9*C113-10*(C106/25.4)+10*(C8/25.4)))))/(C113^2*MAX(D59:D69)),1)),5)</f>
+        <v>18</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>19</v>
@@ -1255,7 +1255,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="12"/>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="C37" s="22" t="n">
         <f aca="false">IFERROR(C115,"—")</f>
-        <v>17.7438014422954</v>
+        <v>34.356133054323</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>37</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C106" s="34" t="n">
         <f aca="false">$C$8+$C$12</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>11</v>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C111" s="22" t="n">
         <f aca="false">IFERROR(IF(C107&gt;0,(C107-1)*C106+C105,""),"")</f>
-        <v>255</v>
+        <v>128</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>11</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C114" s="22" t="n">
         <f aca="false">IFERROR(C111/25.4,"")</f>
-        <v>10.0393700787402</v>
+        <v>5.03937007874016</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>93</v>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C115" s="22" t="n">
         <f aca="false">IFERROR((C113^2*C107^2)/(9*C113+10*C114),"")</f>
-        <v>17.7438014422954</v>
+        <v>34.356133054323</v>
       </c>
       <c r="D115" s="8" t="s">
         <v>37</v>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="C116" s="22" t="n">
         <f aca="true">IFERROR(2*PI()*MIN($C$16:OFFSET($C$16,$C$10-1,0))*C115,"")</f>
-        <v>802.710666113347</v>
+        <v>1554.23484301269</v>
       </c>
       <c r="D116" s="8" t="s">
         <v>8</v>
